--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1422E268-3834-4D65-AC17-045E7237BB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95732D67-50CA-480B-890D-3138A8022C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1553,10 +1553,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Always use 10yrs to identify the HGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Use Excel Goal Seek to find the HGR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2331,6 +2327,10 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4029,10 +4029,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4061,13 +4061,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
+        <v>410</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>411</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>14.58</v>
+        <v>13.52</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>20165.07433014</v>
+        <v>18699.026402160001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="338" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C12" s="338"/>
       <c r="D12" s="338"/>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7605000000000004</v>
+        <v>7.7590000000000003</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4183,7 +4183,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>10.177519059641918</v>
+        <v>10.175590600126672</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4214,11 +4214,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1010567723303204</v>
+        <v>0.13057514345777688</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="338" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C25" s="338"/>
       <c r="D25" s="338"/>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="341" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C26" s="341"/>
       <c r="D26" s="341"/>
@@ -4358,11 +4358,11 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0185794669646606</v>
+        <v>7.0182060826082004</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4373,7 +4373,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.98142053303533</v>
+        <v>-144.9817939173918</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03439195279446</v>
+        <v>-102.03429860670536</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="339" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C50" s="340"/>
       <c r="D50" s="340"/>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="338" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C53" s="338"/>
       <c r="D53" s="338"/>
@@ -4472,7 +4472,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="338" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C54" s="338"/>
       <c r="D54" s="338"/>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.21857946696451</v>
+        <v>342.21820608260811</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.65141070522242</v>
+        <v>273.65113066695511</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4507,11 +4507,11 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10531435381835931</v>
+        <v>0.11354918043217686</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.7165823045267489E-2</v>
+        <v>6.1635843195266271E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4539,7 +4539,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="338" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="338"/>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4606,13 +4606,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="338" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C73" s="338"/>
       <c r="D73" s="338"/>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="338" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C74" s="338"/>
       <c r="D74" s="338"/>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>19.19354098339598</v>
+        <v>19.18981149303789</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="338" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C81" s="338"/>
       <c r="D81" s="338"/>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="338" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C85" s="338"/>
       <c r="D85" s="338"/>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>13.034567032422894</v>
+        <v>13.032047626386086</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.28049312439703</v>
+        <v>327.29906075971127</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.8364010013062304</v>
+        <v>1.8361502143314641</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="338" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C98" s="338"/>
       <c r="D98" s="338"/>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9953749522793185</v>
+        <v>7.9939140809832665</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4815,7 +4815,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="339" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C104" s="339"/>
       <c r="D104" s="339"/>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.23 HKD</v>
+        <v>86.22 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>8 HKD</v>
+        <v>7.99 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>16.70033318211312</v>
+        <v>16.697180853372405</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="342" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C115" s="342"/>
       <c r="D115" s="342"/>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="343" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C119" s="343"/>
       <c r="D119" s="343"/>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="338" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C120" s="338"/>
       <c r="D120" s="338"/>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83347769999999999</v>
+        <v>0.83331659999999996</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>1.6269484703999999</v>
+        <v>1.6266340031999997</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>8.5505705892419179</v>
+        <v>8.5489565969266721</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>10.177519059641918</v>
+        <v>10.175590600126672</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,12 +5089,12 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.39057987953542495</v>
+        <v>0.39058032074489624</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="247" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B134" s="337" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C134" s="338"/>
       <c r="D134" s="338"/>
@@ -5113,12 +5113,12 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B137" s="340" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C137" s="340"/>
       <c r="D137" s="340"/>
@@ -5127,27 +5127,27 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="238" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="238" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="238" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B143" s="339" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C143" s="339"/>
       <c r="D143" s="339"/>
@@ -5156,12 +5156,12 @@
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="336" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C146" s="336"/>
       <c r="D146" s="336"/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="336" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C147" s="336"/>
       <c r="D147" s="336"/>
@@ -5179,22 +5179,22 @@
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="238" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="238" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="238" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -5691,7 +5691,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C22" s="181">
         <v>56480</v>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C23" s="181">
         <v>-11150</v>
@@ -5743,7 +5743,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C24" s="181">
         <v>-45970</v>
@@ -5774,11 +5774,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83347769999999999</v>
+        <v>0.83331659999999996</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79622729999999997</v>
+        <v>0.79607340000000004</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -5801,7 +5801,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7056,7 +7056,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7109,11 +7109,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83347769999999999</v>
+        <v>0.83331659999999996</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79622729999999997</v>
+        <v>0.79607340000000004</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8460,11 +8460,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2830942114776906</v>
+        <v>8.281493201063773</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.138138952741498</v>
+        <v>-12.135792814164201</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.28049312439703</v>
+        <v>327.29906075971127</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8706,7 +8706,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8718,52 +8718,52 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.41275590428739</v>
+        <v>-342.3941882689731</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.01950687560293</v>
+        <v>-349.00093924028869</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9751016524309686</v>
+        <v>1.9752087598774368</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9377140437054308</v>
+        <v>1.9378171344529374</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.01950687560293</v>
+        <v>349.00093924028869</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8771,7 +8771,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8870,11 +8870,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18027.641500000002</v>
+        <v>-18024.156999999999</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-13.034567032422894</v>
+        <v>-13.032047626386086</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8887,11 +8887,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2539.8602668918834</v>
+        <v>2539.5134124346</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.8364010013062304</v>
+        <v>1.8361502143314641</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8921,11 +8921,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15487.781233108119</v>
+        <v>-15484.643587565399</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.198166031116664</v>
+        <v>-11.195897412054622</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9505,24 +9505,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.98142053303533</v>
+        <v>-144.9817939173918</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.98142053303533</v>
+        <v>-144.9817939173918</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.6201701192945</v>
+        <v>-165.62056272196344</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75856622725817</v>
+        <v>-133.75880782890059</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.14214072933288</v>
+        <v>-167.14223956636843</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9560,24 +9560,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.13756781117786</v>
+        <v>408.13719442682145</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.4185794669645</v>
+        <v>487.41820608260809</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.87982988070576</v>
+        <v>497.87943727803679</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44143377274168</v>
+        <v>286.44119217109926</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.542140729332743</v>
+        <v>-53.542239566368295</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03439195279446</v>
+        <v>-102.03429860670536</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9727,26 +9727,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.65141070522242</v>
+        <v>273.65113066695511</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.21857946696451</v>
+        <v>342.21820608260811</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.97982988070572</v>
+        <v>329.97943727803676</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54143377274167</v>
+        <v>236.54119217109925</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5421407293327398</v>
+        <v>-6.5422395663682913</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -9835,26 +9835,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.65141070522242</v>
+        <v>273.65113066695511</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.21857946696451</v>
+        <v>342.21820608260811</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.97982988070572</v>
+        <v>329.97943727803676</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54143377274167</v>
+        <v>236.54119217109925</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5421407293327398</v>
+        <v>-6.5422395663682913</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10325,7 +10325,7 @@
         <v>-227.20000000000005</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10691,24 +10691,24 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270720276886357</v>
+        <v>0.24270738869354092</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27034636055100036</v>
+        <v>0.2703465737325354</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4834095682118582E-2</v>
+        <v>8.4834167236271449E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496405118372707</v>
+        <v>1.0496385742388918</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -10830,28 +10830,28 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0185794669646606</v>
+        <v>7.0182060826082004</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>7.0185794669646606</v>
+        <v>7.0182060826082004</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>7.379829880705489</v>
+        <v>7.3794372780365647</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5414337727418399</v>
+        <v>4.5411921710994241</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8578592706671162</v>
+        <v>1.8577604336315825</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -10885,7 +10885,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10946,24 +10946,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.98142053303533</v>
+        <v>-144.9817939173918</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.98142053303533</v>
+        <v>-144.9817939173918</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.6201701192945</v>
+        <v>-165.62056272196344</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75856622725817</v>
+        <v>-133.75880782890059</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.14214072933288</v>
+        <v>-167.14223956636843</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -11018,7 +11018,7 @@
         <v>2.0109418896939228E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11045,7 +11045,7 @@
         <v>6.5432630219543694E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11360,7 +11360,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12033,26 +12033,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0400551895735201E-2</v>
+        <v>4.0400655943095304E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0400551895735201E-2</v>
+        <v>4.0400655943095304E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4976148739760614E-2</v>
+        <v>4.4976255355736322E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6450398050860597E-2</v>
+        <v>4.6450481951972704E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.271087724135634E-2</v>
+        <v>8.2710926151211617E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12090,26 +12090,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373169698801144</v>
+        <v>0.11373159294065135</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582415969095596</v>
+        <v>0.13582405564359587</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520525469278344</v>
+        <v>0.13520514807680772</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9472646816482047E-2</v>
+        <v>9.9472562915369933E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6495516987991262E-2</v>
+        <v>-2.6495565897846542E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8432924247002861E-2</v>
+        <v>2.8432898235162839E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12262,26 +12262,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6255757316285575E-2</v>
+        <v>7.6255679280765515E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5362698396857973E-2</v>
+        <v>9.5362594349497884E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9609990734495354E-2</v>
+        <v>8.9609884118519653E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2143851150417307E-2</v>
+        <v>8.2143767249305208E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2374013902082047E-3</v>
+        <v>3.2374503000634856E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12369,26 +12369,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6255757316285575E-2</v>
+        <v>7.6255679280765515E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5362698396857973E-2</v>
+        <v>9.5362594349497884E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9609990734495354E-2</v>
+        <v>8.9609884118519653E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2143851150417307E-2</v>
+        <v>8.2143767249305208E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2374013902082047E-3</v>
+        <v>3.2374503000634856E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12438,16 +12438,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83347769999999999</v>
+        <v>0.83331659999999996</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83347769999999999</v>
+        <v>0.83331659999999996</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79622729999999997</v>
+        <v>0.79607340000000004</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12494,16 +12494,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>1152.7530708514489</v>
+        <v>1152.5302592276778</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>1152.7530708514489</v>
+        <v>1152.5302592276778</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1101.2333805340659</v>
+        <v>1101.0205269716923</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12549,16 +12549,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>4.2124872219028902</v>
+        <v>4.2116773149033877</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>3.3684701533358097</v>
+        <v>3.367822748008527</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3372748295924137</v>
+        <v>3.3366337492235472</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12604,16 +12604,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.7165823045267489E-2</v>
+        <v>6.1635843195266271E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.7165823045267489E-2</v>
+        <v>6.1635843195266271E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.4610925925925924E-2</v>
+        <v>5.8881168639053259E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -12741,26 +12741,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265488226256675</v>
+        <v>-0.16265500686355161</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.101159714834766E-2</v>
+        <v>-2.1011575116701819E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815576651426795</v>
+        <v>0.73815586195661265</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3498315508295775</v>
+        <v>-6.3498171628783107</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82817028007274462</v>
+        <v>-0.82816996288071787</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13294,7 +13294,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13346,25 +13346,25 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.04071780080602</v>
+        <v>165.04089787194513</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88868276982987</v>
+        <v>161.8888753816164</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.40015081958184</v>
+        <v>117.40027073133588</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5917.0234333904637</v>
+        <v>-5916.9340418221009</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13460,24 +13460,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373169698801144</v>
+        <v>0.11373159294065135</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582415969095596</v>
+        <v>0.13582405564359587</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520525469278344</v>
+        <v>0.13520514807680772</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9472646816482047E-2</v>
+        <v>9.9472562915369933E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6495516987991262E-2</v>
+        <v>-2.6495565897846542E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13746,30 +13746,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5354832786716786</v>
+        <v>1.5351849194430311</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9202199801130824</v>
+        <v>1.9198467327959354</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8515472285525447</v>
+        <v>1.8511871469373467</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3272557789307886</v>
+        <v>1.3269978828996596</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.670855440035798E-2</v>
+        <v>-3.6702013608325028E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.218729211985472</v>
+        <v>-1.2184936480633048</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13803,30 +13803,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10531435381835931</v>
+        <v>0.11354918043217686</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13170233059760511</v>
+        <v>0.14200049798786504</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12699226533282199</v>
+        <v>0.13692212625276234</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.1032632299779745E-2</v>
+        <v>9.8150730983702639E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.5177334979669397E-3</v>
+        <v>-2.7146459769471177E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.3589109189675714E-2</v>
+        <v>-9.0125269827167523E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13855,28 +13855,28 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8477492019113879E-2</v>
+        <v>1.9926171127121327E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2330688825032152E-2</v>
+        <v>2.4081467682616032E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.677653126695176E-2</v>
+        <v>1.8091851026047091E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1653812733472253E-3</v>
+        <v>1.2567499234765196E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.3872811917924516E-2</v>
+        <v>-6.8880591550542866E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.65141070522242</v>
+        <v>273.65113066695511</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6426338152801</v>
+        <v>3420.6391333369388</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.28049312439703</v>
+        <v>327.29906075971127</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.9231269396771</v>
+        <v>1424.93819409665</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14758,7 +14758,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7605000000000004</v>
+        <v>7.7590000000000003</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>7.9953749522793185</v>
+        <v>7.9939140809832665</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>16.700673036487409</v>
+        <v>16.697520641709705</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.08467011401342</v>
+        <v>304.08435893219303</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.55987973519757</v>
+        <v>281.55959160388238</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90246635327759</v>
+        <v>337.90212056437429</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.69690188038203</v>
+        <v>289.6966054221316</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.48119977510873</v>
+        <v>375.48081553040737</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.06908227841654</v>
+        <v>298.0687772525842</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.23913088327055</v>
+        <v>417.23870390603344</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68321695405047</v>
+        <v>306.68290311303468</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.64103567501058</v>
+        <v>463.64056121287661</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.54629833573904</v>
+        <v>315.54597542478302</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.20337871170534</v>
+        <v>515.2028514837948</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.66552093167013</v>
+        <v>324.6651886886545</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14992,7 +14992,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.50006149587966</v>
+        <v>572.49947563401679</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.04828716982678</v>
+        <v>334.04794532505684</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.16881013544378</v>
+        <v>636.16815911884248</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70221340682542</v>
+        <v>343.70186168281242</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.91827339141525</v>
+        <v>706.91754997410158</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.63513611040986</v>
+        <v>353.6347742216459</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.53591011213473</v>
+        <v>785.53510624229671</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.85511822061665</v>
+        <v>363.85474587334244</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.0583764251678</v>
+        <v>3801.0544866524128</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6254877898803</v>
+        <v>1760.62368607247</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.087142813014</v>
+        <v>4972.082054680398</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15564,7 +15564,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.087142813014</v>
+        <v>4972.082054680398</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15594,19 +15594,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.6426338152796</v>
+        <v>3420.6391333369384</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.0104713289875</v>
+        <v>3531.0068579068902</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.8076067083507</v>
+        <v>3761.8037571024543</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.68264946196</v>
+        <v>4335.6782125871287</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.0674649139346</v>
+        <v>5077.0622693508194</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15615,19 +15615,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.6426338152787</v>
+        <v>3420.6391333369374</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.4799401801788</v>
+        <v>3641.4762137103235</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.2051255203041</v>
+        <v>4152.2008764052498</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.7681569611996</v>
+        <v>5750.76227197363</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.414153208365</v>
+        <v>8648.4053029455135</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15636,19 +15636,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6426338152778</v>
+        <v>3420.6391333369374</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.2165381969876</v>
+        <v>3778.212671799186</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.2119746285489</v>
+        <v>4689.2071759732344</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.4865423021729</v>
+        <v>8276.4780726474928</v>
       </c>
       <c r="F58" s="124">
-        <v>17363.980350894159</v>
+        <v>17363.962581649124</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15657,19 +15657,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6426338152773</v>
+        <v>3420.6391333369379</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.5292034637805</v>
+        <v>3917.5251945018404</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.7908234540182</v>
+        <v>5301.7853979226393</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.532642624526</v>
+        <v>12134.520224879314</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.369501172769</v>
+        <v>36349.332303431212</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15678,19 +15678,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6426338152773</v>
+        <v>3420.6391333369384</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.0977126230318</v>
+        <v>4047.0935710685335</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.7548316257707</v>
+        <v>5943.7487491473357</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.43815070752</v>
+        <v>17688.420049432039</v>
       </c>
       <c r="F60" s="124">
-        <v>76382.760182325903</v>
+        <v>76382.682016838793</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15699,19 +15699,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6426338152778</v>
+        <v>3420.6391333369384</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.395161740912</v>
+        <v>4161.3909032213323</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.6372587379474</v>
+        <v>6585.6305193959424</v>
       </c>
       <c r="E61" s="124">
-        <v>25476.712221652746</v>
+        <v>25476.686150329642</v>
       </c>
       <c r="F61" s="124">
-        <v>159940.28901416445</v>
+        <v>159940.12534096689</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15761,23 +15761,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9953749522793185</v>
+        <v>7.9939140809832665</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9953749522793185</v>
+        <v>7.9939140809832665</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9953749522793185</v>
+        <v>7.9939140809832665</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9953749522793185</v>
+        <v>7.9939140809832665</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9953749522793185</v>
+        <v>7.9939140809832665</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15788,23 +15788,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>7.9953749522793167</v>
+        <v>7.9939140809832629</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6146590574433208</v>
+        <v>8.6130778532654286</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9096830488309635</v>
+        <v>9.9078502089859715</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.129748788394664</v>
+        <v>13.127290258681478</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.289727296284994</v>
+        <v>17.286460442576331</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15815,23 +15815,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>7.9953749522793114</v>
+        <v>7.9939140809832585</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2345134254058721</v>
+        <v>9.2328117775385827</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.100239496633797</v>
+        <v>12.097981010517596</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.069923951592688</v>
+        <v>21.065922569169917</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.328882614664366</v>
+        <v>37.321721959566524</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15842,23 +15842,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>7.9953749522793061</v>
+        <v>7.9939140809832585</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>10.001755075270511</v>
+        <v>9.9999043449416831</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.113434404757612</v>
+        <v>15.110590425773443</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.241962521868125</v>
+        <v>35.235207375496934</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.232727569143293</v>
+        <v>86.216064424724237</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15869,23 +15869,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>7.9953749522793025</v>
+        <v>7.9939140809832603</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.783451275823893</v>
+        <v>10.781448654374737</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.55067076621264</v>
+        <v>18.547158899011304</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>56.88981465653427</v>
+        <v>56.878853123447932</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>192.76149533321598</v>
+        <v>192.72413262051094</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15896,23 +15896,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>7.9953749522793025</v>
+        <v>7.9939140809832629</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.510472118668217</v>
+        <v>11.508328230048726</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.152789964196963</v>
+        <v>22.14857817045111</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.053290178209039</v>
+        <v>88.036273280894534</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>417.39253897017886</v>
+        <v>417.31152827651499</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15922,23 +15922,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>7.9953749522793061</v>
+        <v>7.9939140809832629</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.151805636602765</v>
+        <v>12.149537130687614</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.754451403339441</v>
+        <v>25.749539771996034</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>131.75401357236171</v>
+        <v>131.72850520248983</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>886.2415319199024</v>
+        <v>886.06941933940516</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.232727569143293</v>
+        <v>86.216064424724237</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.069923951592688</v>
+        <v>21.065922569169917</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.100239496633797</v>
+        <v>12.097981010517596</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2345134254058721</v>
+        <v>9.2328117775385827</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.9953749522793061</v>
+        <v>7.9939140809832585</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.58</v>
+        <v>-13.52</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83347769999999999</v>
+        <v>0.83331659999999996</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83347769999999999</v>
+        <v>0.83331659999999996</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.533810882113119</v>
+        <v>17.530497453372405</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.21857946696451</v>
+        <v>342.21820608260811</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.65141070522242</v>
+        <v>273.65113066695511</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7399107139611019</v>
+        <v>-4.7398905201088688</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16373,7 +16373,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16384,7 +16384,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.58</v>
+        <v>13.52</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16420,7 +16420,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9953749522793185</v>
+        <v>7.9939140809832665</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.100239496633797</v>
+        <v>12.097981010517596</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2345134254058721</v>
+        <v>9.2328117775385827</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.069923951592688</v>
+        <v>21.065922569169917</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.321031173379991</v>
+        <v>13.318535475652258</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>7.9953749522793061</v>
+        <v>7.9939140809832585</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16706,7 +16706,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.232727569143293</v>
+        <v>86.216064424724237</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.70033318211312</v>
+        <v>16.697180853372405</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16784,7 +16784,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16804,11 +16804,12 @@
         <v>135</v>
       </c>
       <c r="C64" s="167">
+        <f>C18</f>
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>323</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16820,7 +16821,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16829,22 +16830,22 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.700673036487409</v>
+        <v>16.697520641709705</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
@@ -16888,11 +16889,11 @@
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67053548626864834</v>
+        <v>-0.67052621100365795</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16925,7 +16926,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83347769999999999</v>
+        <v>0.83331659999999996</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16952,7 +16953,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6269484703999999</v>
+        <v>1.6266340031999997</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16964,7 +16965,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.5505705892419179</v>
+        <v>8.5489565969266721</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16974,7 +16975,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>10.177519059641918</v>
+        <v>10.175590600126672</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16985,7 +16986,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.39057987953542495</v>
+        <v>0.39058032074489624</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17002,7 +17003,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.58</v>
+        <v>13.52</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17015,7 +17016,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1010567723303204</v>
+        <v>0.13057514345777688</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -17023,7 +17024,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="320" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F89" s="317"/>
       <c r="G89" s="2"/>
@@ -17031,30 +17032,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="313" t="s">
+        <v>337</v>
+      </c>
+      <c r="F90" s="318" t="s">
         <v>338</v>
-      </c>
-      <c r="F90" s="318" t="s">
-        <v>339</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="316"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="314" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F91" s="318" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="316"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="315" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F92" s="319" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="316"/>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95732D67-50CA-480B-890D-3138A8022C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F8D8F1-5DAB-4E45-A79D-05A64EC2E7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2310,6 +2310,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>新秀麗</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2327,10 +2331,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4064,10 +4064,10 @@
         <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>13.52</v>
+        <v>13.48</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>18699.026402160001</v>
+        <v>18643.70383884</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4160,7 +4160,7 @@
         <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7590000000000003</v>
+        <v>7.7610000000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4183,7 +4183,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>10.175590600126672</v>
+        <v>10.178161876153645</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13057514345777688</v>
+        <v>0.13185476539875873</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0182060826082004</v>
+        <v>7.0187039284168149</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.9817939173918</v>
+        <v>-144.98129607158319</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03429860670536</v>
+        <v>-102.03442306815751</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.21820608260811</v>
+        <v>342.21870392841669</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.65113066695511</v>
+        <v>273.65150405131158</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11354918043217686</v>
+        <v>0.11391563292899698</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.1635843195266271E-2</v>
+        <v>6.1834673590504444E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>19.18981149303789</v>
+        <v>19.194784148535987</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>13.032047626386086</v>
+        <v>13.035406834435161</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.29906075971127</v>
+        <v>327.27430391262556</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.8361502143314641</v>
+        <v>1.8364845880144853</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9939140809832665</v>
+        <v>7.9958619021153128</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.22 HKD</v>
+        <v>86.24 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>9.23 HKD</v>
+        <v>9.24 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.99 HKD</v>
+        <v>8 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>16.697180853372405</v>
+        <v>16.701383951862589</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83331659999999996</v>
+        <v>0.83353139999999992</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>1.6266340031999997</v>
+        <v>1.6270532927999999</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>8.5489565969266721</v>
+        <v>8.5511085833536455</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>10.175590600126672</v>
+        <v>10.178161876153645</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.39058032074489624</v>
+        <v>0.39057973246471311</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,6 +5199,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5215,17 +5226,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5774,11 +5774,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83331659999999996</v>
+        <v>0.83353139999999992</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79607340000000004</v>
+        <v>0.79627859999999995</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -5801,7 +5801,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7109,11 +7109,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83331659999999996</v>
+        <v>0.83353139999999992</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79607340000000004</v>
+        <v>0.79627859999999995</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8460,11 +8460,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.281493201063773</v>
+        <v>8.2836278816156632</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.135792814164201</v>
+        <v>-12.13892099893393</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.29906075971127</v>
+        <v>327.27430391262556</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8722,11 +8722,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.3941882689731</v>
+        <v>-342.41894511605886</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.00093924028869</v>
+        <v>-349.0256960873744</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>363</v>
@@ -8738,11 +8738,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9752087598774368</v>
+        <v>1.9750659525300975</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9378171344529374</v>
+        <v>1.9376796825603819</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>330</v>
@@ -8755,7 +8755,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.00093924028869</v>
+        <v>349.0256960873744</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>364</v>
@@ -8870,11 +8870,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18024.156999999999</v>
+        <v>-18028.803</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-13.032047626386086</v>
+        <v>-13.035406834435161</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8887,11 +8887,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2539.5134124346</v>
+        <v>2539.975872665887</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.8361502143314641</v>
+        <v>1.8364845880144853</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8921,11 +8921,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15484.643587565399</v>
+        <v>-15488.827127334112</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.195897412054622</v>
+        <v>-11.198922246420675</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9505,24 +9505,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.9817939173918</v>
+        <v>-144.98129607158319</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.9817939173918</v>
+        <v>-144.98129607158319</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.62056272196344</v>
+        <v>-165.62003925173821</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75880782890059</v>
+        <v>-133.75848569337737</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.14223956636843</v>
+        <v>-167.14210778365438</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9560,24 +9560,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.13719442682145</v>
+        <v>408.13769227263003</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.41820608260809</v>
+        <v>487.41870392841668</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.87943727803679</v>
+        <v>497.87996074826202</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44119217109926</v>
+        <v>286.44151430662248</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.542239566368295</v>
+        <v>-53.542107783654245</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03429860670536</v>
+        <v>-102.03442306815751</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9727,26 +9727,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.65113066695511</v>
+        <v>273.65150405131158</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.21820608260811</v>
+        <v>342.21870392841669</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.97943727803676</v>
+        <v>329.97996074826204</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54119217109925</v>
+        <v>236.54151430662247</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5422395663682913</v>
+        <v>-6.5421077836542416</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -9835,26 +9835,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.65113066695511</v>
+        <v>273.65150405131158</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.21820608260811</v>
+        <v>342.21870392841669</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.97943727803676</v>
+        <v>329.97996074826204</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54119217109925</v>
+        <v>236.54151430662247</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5422395663682913</v>
+        <v>-6.5421077836542416</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10696,19 +10696,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270738869354092</v>
+        <v>0.24270714079403441</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2703465737325354</v>
+        <v>0.27034628949056344</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4834167236271449E-2</v>
+        <v>8.4834071830761124E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496385742388918</v>
+        <v>1.0496411577049864</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -10834,24 +10834,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0182060826082004</v>
+        <v>7.0187039284168149</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
-        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>7.0182060826082004</v>
+        <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
+        <v>7.018703928416814</v>
       </c>
       <c r="H48" s="328">
-        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>7.3794372780365647</v>
+        <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
+        <v>7.3799607482617979</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5411921710994241</v>
+        <v>4.5415143066226449</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8577604336315825</v>
+        <v>1.8578922163456275</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -10946,24 +10946,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.9817939173918</v>
+        <v>-144.98129607158319</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.9817939173918</v>
+        <v>-144.98129607158319</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.62056272196344</v>
+        <v>-165.62003925173821</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75880782890059</v>
+        <v>-133.75848569337737</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.14223956636843</v>
+        <v>-167.14210778365438</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -11137,7 +11137,7 @@
         <v>169</v>
       </c>
       <c r="C58" s="191">
-        <f>BS!$C79*C66</f>
+        <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="302"/>
@@ -11247,7 +11247,7 @@
         <v>160</v>
       </c>
       <c r="C60" s="191">
-        <f>BS!$C81*C68</f>
+        <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="302"/>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="E68" s="302"/>
       <c r="G68" s="23">
-        <f>IFERROR(G60/BS!$C$81,0)</f>
+        <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
       </c>
       <c r="H68" s="176"/>
@@ -12033,26 +12033,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0400655943095304E-2</v>
+        <v>4.0400517213281834E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0400655943095304E-2</v>
+        <v>4.0400517213281834E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4976255355736322E-2</v>
+        <v>4.4976113201102057E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6450481951972704E-2</v>
+        <v>4.6450370083823231E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2710926151211617E-2</v>
+        <v>8.2710860938071257E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12090,26 +12090,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373159294065135</v>
+        <v>0.11373173167046481</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582405564359587</v>
+        <v>0.13582419437340931</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520514807680772</v>
+        <v>0.13520529023144201</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9472562915369933E-2</v>
+        <v>9.9472674783519413E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6495565897846542E-2</v>
+        <v>-2.6495500684706179E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8432898235162839E-2</v>
+        <v>2.8432932917616203E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12262,26 +12262,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6255679280765515E-2</v>
+        <v>7.6255783328125618E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5362594349497884E-2</v>
+        <v>9.536273307931134E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9609884118519653E-2</v>
+        <v>8.9610026273153925E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2143767249305208E-2</v>
+        <v>8.2143879117454674E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2374503000634856E-3</v>
+        <v>3.2373850869231204E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12369,26 +12369,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6255679280765515E-2</v>
+        <v>7.6255783328125618E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5362594349497884E-2</v>
+        <v>9.536273307931134E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9609884118519653E-2</v>
+        <v>8.9610026273153925E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2143767249305208E-2</v>
+        <v>8.2143879117454674E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2374503000634856E-3</v>
+        <v>3.2373850869231204E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12438,16 +12438,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83331659999999996</v>
+        <v>0.83353139999999992</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83331659999999996</v>
+        <v>0.83353139999999992</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79607340000000004</v>
+        <v>0.79627859999999995</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12494,16 +12494,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>1152.5302592276778</v>
+        <v>1152.8273413927061</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>1152.5302592276778</v>
+        <v>1152.8273413927061</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1101.0205269716923</v>
+        <v>1101.3043317215238</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12549,16 +12549,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>4.2116773149033877</v>
+        <v>4.2127571905343633</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>3.367822748008527</v>
+        <v>3.3686859547976309</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3366337492235472</v>
+        <v>3.3374885227097053</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12604,16 +12604,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.1635843195266271E-2</v>
+        <v>6.1834673590504444E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.1635843195266271E-2</v>
+        <v>6.1834673590504444E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.8881168639053259E-2</v>
+        <v>5.9071112759643912E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -12741,26 +12741,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265500686355161</v>
+        <v>-0.16265484072894754</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1011575116701819E-2</v>
+        <v>-2.1011604492221725E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815586195661265</v>
+        <v>0.7381557347001888</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3498171628783107</v>
+        <v>-6.3498363468251355</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82816996288071787</v>
+        <v>-0.82817038580342017</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13352,19 +13352,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.04089787194513</v>
+        <v>165.04065777718029</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.8888753816164</v>
+        <v>161.88861856600289</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.40027073133588</v>
+        <v>117.40011084905159</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5916.9340418221009</v>
+        <v>-5917.0532311801289</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13460,24 +13460,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373159294065135</v>
+        <v>0.11373173167046481</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582405564359587</v>
+        <v>0.13582419437340931</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520514807680772</v>
+        <v>0.13520529023144201</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9472562915369933E-2</v>
+        <v>9.9472674783519413E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6495565897846542E-2</v>
+        <v>-2.6495500684706179E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13746,30 +13746,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5351849194430311</v>
+        <v>1.535582731882879</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9198467327959354</v>
+        <v>1.9203443960654438</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8511871469373467</v>
+        <v>1.8516672559468541</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3269978828996596</v>
+        <v>1.3273417443909554</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.6702013608325028E-2</v>
+        <v>-3.6710734616727497E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2184936480633048</v>
+        <v>-1.2188077332928611</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13803,30 +13803,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11354918043217686</v>
+        <v>0.11391563292899698</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14200049798786504</v>
+        <v>0.14245878309090829</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13692212625276234</v>
+        <v>0.1373640397586687</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.8150730983702639E-2</v>
+        <v>9.8467488456302321E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.7146459769471177E-3</v>
+        <v>-2.7233482653358679E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-9.0125269827167523E-2</v>
+        <v>-9.0416003953476334E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13860,23 +13860,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9926171127121327E-2</v>
+        <v>1.9985299231356109E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4081467682616032E-2</v>
+        <v>2.4152926043692045E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8091851026047091E-2</v>
+        <v>1.8145536043928535E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2567499234765196E-3</v>
+        <v>1.2604791517360939E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.8880591550542866E-2</v>
+        <v>-6.9084984997280371E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.65113066695511</v>
+        <v>273.65150405131158</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6391333369388</v>
+        <v>3420.6438006413946</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.29906075971127</v>
+        <v>327.27430391262556</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.93819409665</v>
+        <v>1424.9181045540201</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14758,7 +14758,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7590000000000003</v>
+        <v>7.7610000000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>7.9939140809832665</v>
+        <v>7.9958619021153128</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>16.697520641709705</v>
+        <v>16.701723828249243</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.08435893219303</v>
+        <v>304.08477384128696</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.55959160388238</v>
+        <v>281.55997577896937</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90212056437429</v>
+        <v>337.90258161624547</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.6966054221316</v>
+        <v>289.69700069979893</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.48081553040737</v>
+        <v>375.48132785667599</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.0687772525842</v>
+        <v>298.06918395369411</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.23870390603344</v>
+        <v>417.23927320901635</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68290311303468</v>
+        <v>306.68332156772243</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.64056121287661</v>
+        <v>463.64119382905534</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.54597542478302</v>
+        <v>315.54640597272447</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.2028514837948</v>
+        <v>515.20355445434234</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.6651886886545</v>
+        <v>324.66563167934214</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14992,7 +14992,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.49947563401679</v>
+        <v>572.50025678316752</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.04794532505684</v>
+        <v>334.04840111808358</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.16815911884248</v>
+        <v>636.16902714097762</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70186168281242</v>
+        <v>343.70233064816313</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.91754997410158</v>
+        <v>706.91851453051993</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.6347742216459</v>
+        <v>353.63525673999794</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.53510624229671</v>
+        <v>785.53617806874752</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.85474587334244</v>
+        <v>363.85524233637483</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.0544866524128</v>
+        <v>3801.0596730160869</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.62368607247</v>
+        <v>1760.6260883623506</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.082054680398</v>
+        <v>4972.0888388572221</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15564,7 +15564,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.082054680398</v>
+        <v>4972.0888388572221</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15594,19 +15594,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.6391333369384</v>
+        <v>3420.6438006413941</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.0068579068902</v>
+        <v>3531.0116758030208</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.8037571024543</v>
+        <v>3761.8088899103172</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.6782125871287</v>
+        <v>4335.6841284202383</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.0622693508194</v>
+        <v>5077.0691967683078</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15615,19 +15615,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.6391333369374</v>
+        <v>3420.6438006413937</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.4762137103235</v>
+        <v>3641.4811823367982</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.2008764052498</v>
+        <v>4152.2065418919901</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.76227197363</v>
+        <v>5750.7701186237236</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.4053029455135</v>
+        <v>8648.4171032959839</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15636,19 +15636,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6391333369374</v>
+        <v>3420.6438006413932</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.212671799186</v>
+        <v>3778.217826996256</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.2071759732344</v>
+        <v>4689.2135741803213</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.4780726474928</v>
+        <v>8276.4893655203996</v>
       </c>
       <c r="F58" s="124">
-        <v>17363.962581649124</v>
+        <v>17363.986273975839</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15657,19 +15657,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6391333369379</v>
+        <v>3420.6438006413928</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.5251945018404</v>
+        <v>3917.5305397844277</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.7853979226393</v>
+        <v>5301.7926319644785</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.520224879314</v>
+        <v>12134.536781872936</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.332303431212</v>
+        <v>36349.381900419961</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15678,19 +15678,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6391333369384</v>
+        <v>3420.6438006413932</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.0935710685335</v>
+        <v>4047.0990931411989</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.7487491473357</v>
+        <v>5943.7568591185827</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.420049432039</v>
+        <v>17688.444184466021</v>
       </c>
       <c r="F60" s="124">
-        <v>76382.682016838793</v>
+        <v>76382.786237488282</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15699,19 +15699,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6391333369384</v>
+        <v>3420.6438006413928</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.3909032213323</v>
+        <v>4161.3965812474407</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.6305193959424</v>
+        <v>6585.6395051852842</v>
       </c>
       <c r="E61" s="124">
-        <v>25476.686150329642</v>
+        <v>25476.720912093791</v>
       </c>
       <c r="F61" s="124">
-        <v>159940.12534096689</v>
+        <v>159940.34357189698</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15761,23 +15761,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9939140809832665</v>
+        <v>7.9958619021153128</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9939140809832665</v>
+        <v>7.9958619021153128</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9939140809832665</v>
+        <v>7.9958619021153128</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9939140809832665</v>
+        <v>7.9958619021153128</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9939140809832665</v>
+        <v>7.9958619021153128</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15788,23 +15788,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>7.9939140809832629</v>
+        <v>7.995861902115311</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6130778532654286</v>
+        <v>8.6151861182943694</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9078502089859715</v>
+        <v>9.9102939883515582</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.127290258681478</v>
+        <v>13.130568291487732</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.286460442576331</v>
+        <v>17.290816241075596</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15815,23 +15815,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>7.9939140809832585</v>
+        <v>7.9958619021153083</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2328117775385827</v>
+        <v>9.2350806342078791</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.097981010517596</v>
+        <v>12.100992318437369</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.065922569169917</v>
+        <v>21.0712577396203</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.321721959566524</v>
+        <v>37.331269495012997</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15842,23 +15842,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>7.9939140809832585</v>
+        <v>7.9958619021153048</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>9.9999043449416831</v>
+        <v>10.002371978293814</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.110590425773443</v>
+        <v>15.114382391115392</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.235207375496934</v>
+        <v>35.244214232457736</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.216064424724237</v>
+        <v>86.238281950231496</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15869,23 +15869,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>7.9939140809832603</v>
+        <v>7.995861902115303</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.781448654374737</v>
+        <v>10.784118809289353</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.547158899011304</v>
+        <v>18.551841382278308</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>56.878853123447932</v>
+        <v>56.893468497932027</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>192.72413262051094</v>
+        <v>192.77394957976449</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15896,23 +15896,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>7.9939140809832629</v>
+        <v>7.9958619021153048</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.508328230048726</v>
+        <v>11.511186741254368</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.14857817045111</v>
+        <v>22.154193889427468</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.036273280894534</v>
+        <v>88.058962477089125</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>417.31152827651499</v>
+        <v>417.41954256346088</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15922,23 +15922,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>7.9939140809832629</v>
+        <v>7.995861902115303</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.149537130687614</v>
+        <v>12.152561798343852</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.749539771996034</v>
+        <v>25.756088608085761</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>131.72850520248983</v>
+        <v>131.76251636593602</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>886.06941933940516</v>
+        <v>886.29890285001227</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.216064424724237</v>
+        <v>86.238281950231496</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.065922569169917</v>
+        <v>21.0712577396203</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.097981010517596</v>
+        <v>12.100992318437369</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2328117775385827</v>
+        <v>9.2350806342078791</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.9939140809832585</v>
+        <v>7.9958619021153048</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-13.52</v>
+        <v>-13.48</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83331659999999996</v>
+        <v>0.83353139999999992</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83331659999999996</v>
+        <v>0.83353139999999992</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.530497453372405</v>
+        <v>17.534915351862587</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.21820608260811</v>
+        <v>342.21870392841669</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.65113066695511</v>
+        <v>273.65150405131158</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7398905201088688</v>
+        <v>-4.7399174453323072</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>13.52</v>
+        <v>13.48</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16420,7 +16420,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9939140809832665</v>
+        <v>7.9958619021153128</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.097981010517596</v>
+        <v>12.100992318437369</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2328117775385827</v>
+        <v>9.2350806342078791</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.065922569169917</v>
+        <v>21.0712577396203</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.318535475652258</v>
+        <v>13.321863065828058</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>7.9939140809832585</v>
+        <v>7.9958619021153048</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.216064424724237</v>
+        <v>86.238281950231496</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.697180853372405</v>
+        <v>16.701383951862589</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16830,7 +16830,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.697520641709705</v>
+        <v>16.701723828249243</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67052621100365795</v>
+        <v>-0.67053857804231476</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83331659999999996</v>
+        <v>0.83353139999999992</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6266340031999997</v>
+        <v>1.6270532927999999</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.5489565969266721</v>
+        <v>8.5511085833536455</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>10.175590600126672</v>
+        <v>10.178161876153645</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.39058032074489624</v>
+        <v>0.39057973246471311</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>13.52</v>
+        <v>13.48</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13057514345777688</v>
+        <v>0.13185476539875873</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F8D8F1-5DAB-4E45-A79D-05A64EC2E7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74647956-4153-43E5-AC43-83EE28632B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>13.48</v>
+        <v>14.24</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>18643.70383884</v>
+        <v>19694.832541920001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7610000000000001</v>
+        <v>7.7594000000000003</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>10.178161876153645</v>
+        <v>10.176104857461148</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13185476539875873</v>
+        <v>0.11016267230709409</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0187039284168149</v>
+        <v>7.0183056517699232</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.98129607158319</v>
+        <v>-144.98169434823006</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03442306815751</v>
+        <v>-102.03432349899579</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.21870392841669</v>
+        <v>342.21830565176981</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.65150405131158</v>
+        <v>273.6512053438264</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11391563292899698</v>
+        <v>0.10781351698346985</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.1834673590504444E-2</v>
+        <v>5.8522441011235951E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>19.194784148535987</v>
+        <v>19.190806023057636</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>13.035406834435161</v>
+        <v>13.032719467995902</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.27430391262556</v>
+        <v>327.29410939029412</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.8364845880144853</v>
+        <v>1.8362170947960685</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9958619021153128</v>
+        <v>7.9943036498578008</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.24 HKD</v>
+        <v>86.22 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>9.24 HKD</v>
+        <v>9.23 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>8 HKD</v>
+        <v>7.99 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>16.701383951862589</v>
+        <v>16.698021477228806</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83353139999999992</v>
+        <v>0.83335956</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>1.6270532927999999</v>
+        <v>1.6267178611199999</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>8.5511085833536455</v>
+        <v>8.5493869963411484</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>10.178161876153645</v>
+        <v>10.176104857461148</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.39057973246471311</v>
+        <v>0.39058020308942809</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,17 +5199,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5226,6 +5215,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5774,11 +5774,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83353139999999992</v>
+        <v>0.83335956</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79627859999999995</v>
+        <v>0.79611443999999998</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -7109,11 +7109,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83353139999999992</v>
+        <v>0.83335956</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79627859999999995</v>
+        <v>0.79611443999999998</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8460,11 +8460,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2836278816156632</v>
+        <v>8.2819201371741507</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.13892099893393</v>
+        <v>-12.136418451118146</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.27430391262556</v>
+        <v>327.29410939029412</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8722,11 +8722,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.41894511605886</v>
+        <v>-342.3991396383903</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.0256960873744</v>
+        <v>-349.00589060970583</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>363</v>
@@ -8738,11 +8738,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9750659525300975</v>
+        <v>1.9751801967558806</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9376796825603819</v>
+        <v>1.9377896425143952</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>330</v>
@@ -8755,7 +8755,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.0256960873744</v>
+        <v>349.00589060970583</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>364</v>
@@ -8870,11 +8870,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18028.803</v>
+        <v>-18025.086200000002</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-13.035406834435161</v>
+        <v>-13.032719467995902</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8887,11 +8887,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2539.975872665887</v>
+        <v>2539.6059124030485</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.8364845880144853</v>
+        <v>1.8362170947960685</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8921,11 +8921,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15488.827127334112</v>
+        <v>-15485.480287596953</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.198922246420675</v>
+        <v>-11.196502373199833</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9505,24 +9505,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.98129607158319</v>
+        <v>-144.98169434823006</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.98129607158319</v>
+        <v>-144.98169434823006</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.62003925173821</v>
+        <v>-165.6204580279184</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75848569337737</v>
+        <v>-133.75874340179595</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.14210778365438</v>
+        <v>-167.1422132098256</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9560,24 +9560,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.13769227263003</v>
+        <v>408.13729399598316</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.41870392841668</v>
+        <v>487.4183056517698</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.87996074826202</v>
+        <v>497.87954197208182</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44151430662248</v>
+        <v>286.44125659820384</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.542107783654245</v>
+        <v>-53.542213209825462</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03442306815751</v>
+        <v>-102.03432349899579</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9727,26 +9727,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.65150405131158</v>
+        <v>273.6512053438264</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.21870392841669</v>
+        <v>342.21830565176981</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.97996074826204</v>
+        <v>329.97954197208179</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54151430662247</v>
+        <v>236.54125659820383</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5421077836542416</v>
+        <v>-6.5422132098254586</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -9835,26 +9835,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.65150405131158</v>
+        <v>273.6512053438264</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.21870392841669</v>
+        <v>342.21830565176981</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.97996074826204</v>
+        <v>329.97954197208179</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54151430662247</v>
+        <v>236.54125659820383</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5421077836542416</v>
+        <v>-6.5422132098254586</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10696,19 +10696,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270714079403441</v>
+        <v>0.24270733911359912</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27034628949056344</v>
+        <v>0.27034651688409317</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4834071830761124E-2</v>
+        <v>8.4834148155152236E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496411577049864</v>
+        <v>1.0496390909310938</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -10834,24 +10834,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0187039284168149</v>
+        <v>7.0183056517699232</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.018703928416814</v>
+        <v>7.0183056517699232</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.3799607482617979</v>
+        <v>7.3795419720816113</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5415143066226449</v>
+        <v>4.5412565982040691</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8578922163456275</v>
+        <v>1.8577867901743916</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -10946,24 +10946,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.98129607158319</v>
+        <v>-144.98169434823006</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.98129607158319</v>
+        <v>-144.98169434823006</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.62003925173821</v>
+        <v>-165.6204580279184</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75848569337737</v>
+        <v>-133.75874340179595</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.14210778365438</v>
+        <v>-167.1422132098256</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12033,26 +12033,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0400517213281834E-2</v>
+        <v>4.0400628197132603E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0400517213281834E-2</v>
+        <v>4.0400628197132603E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4976113201102057E-2</v>
+        <v>4.4976226924809473E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6450370083823231E-2</v>
+        <v>4.6450459578342811E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2710860938071257E-2</v>
+        <v>8.2710913108583528E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12090,26 +12090,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373173167046481</v>
+        <v>0.11373162068661405</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582419437340931</v>
+        <v>0.13582408338955854</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520529023144201</v>
+        <v>0.13520517650773459</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9472674783519413E-2</v>
+        <v>9.9472585288999812E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6495500684706179E-2</v>
+        <v>-2.6495552855218461E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8432932917616203E-2</v>
+        <v>2.8432905171653512E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12262,26 +12262,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6255783328125618E-2</v>
+        <v>7.6255700090237535E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.536273307931134E-2</v>
+        <v>9.5362622095460578E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9610026273153925E-2</v>
+        <v>8.9609912549446502E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2143879117454674E-2</v>
+        <v>8.2143789622935073E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2373850869231204E-3</v>
+        <v>3.2374372574354012E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12369,26 +12369,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6255783328125618E-2</v>
+        <v>7.6255700090237535E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.536273307931134E-2</v>
+        <v>9.5362622095460578E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9610026273153925E-2</v>
+        <v>8.9609912549446502E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2143879117454674E-2</v>
+        <v>8.2143789622935073E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2373850869231204E-3</v>
+        <v>3.2374372574354012E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12438,16 +12438,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83353139999999992</v>
+        <v>0.83335956</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83353139999999992</v>
+        <v>0.83335956</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79627859999999995</v>
+        <v>0.79611443999999998</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12494,16 +12494,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>1152.8273413927061</v>
+        <v>1152.5896756606835</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>1152.8273413927061</v>
+        <v>1152.5896756606835</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1101.3043317215238</v>
+        <v>1101.0772879216586</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12549,16 +12549,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>4.2127571905343633</v>
+        <v>4.2118932902653334</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>3.3686859547976309</v>
+        <v>3.3679953895672696</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3374885227097053</v>
+        <v>3.3368047041377373</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12604,16 +12604,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.1834673590504444E-2</v>
+        <v>5.8522441011235951E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.1834673590504444E-2</v>
+        <v>5.8522441011235951E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.9071112759643912E-2</v>
+        <v>5.5906912921348313E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -12741,26 +12741,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265484072894754</v>
+        <v>-0.16265497363660364</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1011604492221725E-2</v>
+        <v>-2.1011580991810774E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.7381557347001888</v>
+        <v>0.73815583650530536</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3498363468251355</v>
+        <v>-6.349820999660122</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82817038580342017</v>
+        <v>-0.82817004746525846</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13352,19 +13352,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.04065777718029</v>
+        <v>165.0408498529363</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88861856600289</v>
+        <v>161.88882401842852</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.40011084905159</v>
+        <v>117.40023875484422</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5917.0532311801289</v>
+        <v>-5916.9578793095852</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13460,24 +13460,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373173167046481</v>
+        <v>0.11373162068661405</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582419437340931</v>
+        <v>0.13582408338955854</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520529023144201</v>
+        <v>0.13520517650773459</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9472674783519413E-2</v>
+        <v>9.9472585288999812E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6495500684706179E-2</v>
+        <v>-2.6495552855218461E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13746,30 +13746,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.535582731882879</v>
+        <v>1.5352644818446108</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9203443960654438</v>
+        <v>1.9199462653346504</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8516672559468541</v>
+        <v>1.8512831686181324</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3273417443909554</v>
+        <v>1.3270666551233861</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.6710734616727497E-2</v>
+        <v>-3.670375784049601E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2188077332928611</v>
+        <v>-1.218556465109216</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13803,30 +13803,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11391563292899698</v>
+        <v>0.10781351698346985</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14245878309090829</v>
+        <v>0.13482768717237714</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1373640397586687</v>
+        <v>0.13000584049284636</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.8467488456302321E-2</v>
+        <v>9.3192883084507447E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.7233482653358679E-3</v>
+        <v>-2.577511084304495E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-9.0416003953476334E-2</v>
+        <v>-8.557278547115281E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13860,23 +13860,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9985299231356109E-2</v>
+        <v>1.8918668092603955E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4152926043692045E-2</v>
+        <v>2.2863865384056794E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8145536043928535E-2</v>
+        <v>1.7177094513494143E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2604791517360939E-3</v>
+        <v>1.1932063880198416E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.9084984997280371E-2</v>
+        <v>-6.5397865011470463E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.65150405131158</v>
+        <v>273.6512053438264</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6438006413946</v>
+        <v>3420.6400667978301</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.27430391262556</v>
+        <v>327.29410939029412</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.9181045540201</v>
+        <v>1424.9341761881242</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14758,7 +14758,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7610000000000001</v>
+        <v>7.7594000000000003</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>7.9958619021153128</v>
+        <v>7.9943036498578008</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>16.701723828249243</v>
+        <v>16.698361283175959</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.08477384128696</v>
+        <v>304.08444191401185</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.55997577896937</v>
+        <v>281.55966843889985</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90258161624547</v>
+        <v>337.90221277474853</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.69700069979893</v>
+        <v>289.69668447766503</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.48132785667599</v>
+        <v>375.48091799566112</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.06918395369411</v>
+        <v>298.06885859280618</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.23927320901635</v>
+        <v>417.23881776663006</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68332156772243</v>
+        <v>306.68298680397231</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.64119382905534</v>
+        <v>463.6406877361124</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.54640597272447</v>
+        <v>315.54606153437135</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.20355445434234</v>
+        <v>515.20299207790436</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.66563167934214</v>
+        <v>324.66527728679205</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14992,7 +14992,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.50025678316752</v>
+        <v>572.49963186384696</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.04840111808358</v>
+        <v>334.0480364836622</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.16902714097762</v>
+        <v>636.1683327232696</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70233064816313</v>
+        <v>343.70195547588264</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.91851453051993</v>
+        <v>706.91774288538534</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.63525673999794</v>
+        <v>353.63487072531638</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.53617806874752</v>
+        <v>785.53532060758698</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.85524233637483</v>
+        <v>363.85484516594897</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.0596730160869</v>
+        <v>3801.055523925148</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6260883623506</v>
+        <v>1760.6241665304462</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.0888388572221</v>
+        <v>4972.0834115157631</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15564,7 +15564,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.0888388572221</v>
+        <v>4972.0834115157631</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15594,19 +15594,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.6438006413941</v>
+        <v>3420.6400667978291</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.0116758030208</v>
+        <v>3531.0078214861169</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.8088899103172</v>
+        <v>3761.8047836640276</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.6841284202383</v>
+        <v>4335.6793957537502</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.0691967683078</v>
+        <v>5077.0636548343173</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15615,19 +15615,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.6438006413937</v>
+        <v>3420.6400667978287</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.4811823367982</v>
+        <v>3641.4772074356179</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.2065418919901</v>
+        <v>4152.2020095025982</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.7701186237236</v>
+        <v>5750.7638413036493</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.4171032959839</v>
+        <v>8648.4076630156069</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15636,19 +15636,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6438006413932</v>
+        <v>3420.6400667978278</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.217826996256</v>
+        <v>3778.2137028385996</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.2135741803213</v>
+        <v>4689.208455614651</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.4893655203996</v>
+        <v>8276.4803312220756</v>
       </c>
       <c r="F58" s="124">
-        <v>17363.986273975839</v>
+        <v>17363.967320114465</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15657,19 +15657,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6438006413928</v>
+        <v>3420.6400667978273</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.5305397844277</v>
+        <v>3917.5262635583581</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.7926319644785</v>
+        <v>5301.7868447310057</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.536781872936</v>
+        <v>12134.523536278039</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.381900419961</v>
+        <v>36349.342222828964</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15678,19 +15678,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6438006413932</v>
+        <v>3420.6400667978273</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.0990931411989</v>
+        <v>4047.0946754830661</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.7568591185827</v>
+        <v>5943.7503711415848</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.444184466021</v>
+        <v>17688.424876438836</v>
       </c>
       <c r="F60" s="124">
-        <v>76382.786237488282</v>
+        <v>76382.702860968697</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15699,19 +15699,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6438006413928</v>
+        <v>3420.6400667978269</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.3965812474407</v>
+        <v>4161.3920388265542</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.6395051852842</v>
+        <v>6585.6323165538088</v>
       </c>
       <c r="E61" s="124">
-        <v>25476.720912093791</v>
+        <v>25476.693102682471</v>
       </c>
       <c r="F61" s="124">
-        <v>159940.34357189698</v>
+        <v>159940.16898715289</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15761,23 +15761,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9958619021153128</v>
+        <v>7.9943036498578008</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9958619021153128</v>
+        <v>7.9943036498578008</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9958619021153128</v>
+        <v>7.9943036498578008</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9958619021153128</v>
+        <v>7.9943036498578008</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9958619021153128</v>
+        <v>7.9943036498578008</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15788,23 +15788,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>7.995861902115311</v>
+        <v>7.9943036498577955</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6151861182943694</v>
+        <v>8.6134995108845036</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9102939883515582</v>
+        <v>9.9083389693995141</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.130568291487732</v>
+        <v>13.127945869601978</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.290816241075596</v>
+        <v>17.287331606401384</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15815,23 +15815,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>7.9958619021153083</v>
+        <v>7.994303649857792</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2350806342078791</v>
+        <v>9.2332655534508454</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.100992318437369</v>
+        <v>12.098583276518728</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.0712577396203</v>
+        <v>21.066989607172516</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.331269495012997</v>
+        <v>37.323631469653563</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15842,23 +15842,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>7.9958619021153048</v>
+        <v>7.9943036498577866</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>10.002371978293814</v>
+        <v>10.000397876147346</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.114382391115392</v>
+        <v>15.111348823089473</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.244214232457736</v>
+        <v>35.237008750004257</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.238281950231496</v>
+        <v>86.220507930071975</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15869,23 +15869,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>7.995861902115303</v>
+        <v>7.9943036498577849</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.784118809289353</v>
+        <v>10.781982689848922</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.551841382278308</v>
+        <v>18.548095399718957</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>56.893468497932027</v>
+        <v>56.881776200241951</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>192.77394957976449</v>
+        <v>192.73409600661438</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15896,23 +15896,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>7.9958619021153048</v>
+        <v>7.9943036498577849</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.511186741254368</v>
+        <v>11.508899936740207</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.154193889427468</v>
+        <v>22.149701318097975</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.058962477089125</v>
+        <v>88.040811120277311</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>417.41954256346088</v>
+        <v>417.33313111551865</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15922,23 +15922,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>7.995861902115303</v>
+        <v>7.9943036498577813</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.152561798343852</v>
+        <v>12.150142068633137</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.756088608085761</v>
+        <v>25.750849542862916</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>131.76251636593602</v>
+        <v>131.7353074328642</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>886.29890285001227</v>
+        <v>886.11531599676232</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.238281950231496</v>
+        <v>86.220507930071975</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.0712577396203</v>
+        <v>21.066989607172516</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.100992318437369</v>
+        <v>12.098583276518728</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2350806342078791</v>
+        <v>9.2332655534508454</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.9958619021153048</v>
+        <v>7.9943036498577866</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-13.48</v>
+        <v>-14.24</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83353139999999992</v>
+        <v>0.83335956</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83353139999999992</v>
+        <v>0.83335956</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.534915351862587</v>
+        <v>17.531381037228808</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.21870392841669</v>
+        <v>342.21830565176981</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.65150405131158</v>
+        <v>273.6512053438264</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7399174453323072</v>
+        <v>-4.7398959050977965</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>13.48</v>
+        <v>14.24</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16420,7 +16420,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9958619021153128</v>
+        <v>7.9943036498578008</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.100992318437369</v>
+        <v>12.098583276518728</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2350806342078791</v>
+        <v>9.2332655534508454</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.0712577396203</v>
+        <v>21.066989607172516</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.321863065828058</v>
+        <v>13.31920099803591</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>7.9958619021153048</v>
+        <v>7.9943036498577866</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.238281950231496</v>
+        <v>86.220507930071975</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.701383951862589</v>
+        <v>16.698021477228806</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.701723828249243</v>
+        <v>16.698361283175959</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67053857804231476</v>
+        <v>-0.67052868439944047</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83353139999999992</v>
+        <v>0.83335956</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6270532927999999</v>
+        <v>1.6267178611199999</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.5511085833536455</v>
+        <v>8.5493869963411484</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>10.178161876153645</v>
+        <v>10.176104857461148</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.39057973246471311</v>
+        <v>0.39058020308942809</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>13.48</v>
+        <v>14.24</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13185476539875873</v>
+        <v>0.11016267230709409</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74647956-4153-43E5-AC43-83EE28632B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE48C52-EBFD-4768-AD84-BC815DB304E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>14.24</v>
+        <v>14.26</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>19694.832541920001</v>
+        <v>19722.493823579996</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7594000000000003</v>
+        <v>7.7579000000000002</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>10.176104857461148</v>
+        <v>10.174176386967826</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11016267230709409</v>
+        <v>0.10954171828338932</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0183056517699232</v>
+        <v>7.0179322674134639</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.98169434823006</v>
+        <v>-144.98206773258653</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03432349899579</v>
+        <v>-102.03423015290667</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.21830565176981</v>
+        <v>342.21793226741335</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.6512053438264</v>
+        <v>273.65092530555904</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10781351698346985</v>
+        <v>0.10764138310388582</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.8522441011235951E-2</v>
+        <v>5.8429064516129031E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>19.190806023057636</v>
+        <v>19.187076538267647</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>13.032719467995902</v>
+        <v>13.030200061959096</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.29410939029412</v>
+        <v>327.31267702560837</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.8362170947960685</v>
+        <v>1.835966278286302</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9943036498578008</v>
+        <v>7.9928427545948519</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.22 HKD</v>
+        <v>86.2 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>21.07 HKD</v>
+        <v>21.06 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>16.698021477228806</v>
+        <v>16.694869127046534</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83335956</v>
+        <v>0.83319845999999997</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>1.6267178611199999</v>
+        <v>1.6264033939199998</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>8.5493869963411484</v>
+        <v>8.5477729930478255</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>10.176104857461148</v>
+        <v>10.174176386967826</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.39058020308942809</v>
+        <v>0.3905806442959685</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,6 +5199,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5215,17 +5226,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5774,11 +5774,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83335956</v>
+        <v>0.83319845999999997</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79611443999999998</v>
+        <v>0.79596054000000005</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -7109,11 +7109,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83335956</v>
+        <v>0.83319845999999997</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79611443999999998</v>
+        <v>0.79596054000000005</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8460,11 +8460,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2819201371741507</v>
+        <v>8.2803191267602312</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.136418451118146</v>
+        <v>-12.13407231254085</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.29410939029412</v>
+        <v>327.31267702560837</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8722,11 +8722,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.3991396383903</v>
+        <v>-342.380572003076</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.00589060970583</v>
+        <v>-348.98732297439159</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>363</v>
@@ -8738,11 +8738,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9751801967558806</v>
+        <v>1.9752873127214823</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9377896425143952</v>
+        <v>1.9378927413063263</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>330</v>
@@ -8755,7 +8755,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.00589060970583</v>
+        <v>348.98732297439159</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>364</v>
@@ -8870,11 +8870,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18025.086200000002</v>
+        <v>-18021.601699999999</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-13.032719467995902</v>
+        <v>-13.030200061959096</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8887,11 +8887,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2539.6059124030485</v>
+        <v>2539.259017096967</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.8362170947960685</v>
+        <v>1.835966278286302</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8921,11 +8921,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15485.480287596953</v>
+        <v>-15482.342682903032</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.196502373199833</v>
+        <v>-11.194233783672795</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9505,24 +9505,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.98169434823006</v>
+        <v>-144.98206773258653</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.98169434823006</v>
+        <v>-144.98206773258653</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.6204580279184</v>
+        <v>-165.62085063058731</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75874340179595</v>
+        <v>-133.75898500343837</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.1422132098256</v>
+        <v>-167.14231204686115</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9560,24 +9560,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.13729399598316</v>
+        <v>408.13692061162669</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.4183056517698</v>
+        <v>487.41793226741333</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.87954197208182</v>
+        <v>497.87914936941291</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44125659820384</v>
+        <v>286.44101499656142</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.542213209825462</v>
+        <v>-53.542312046861014</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03432349899579</v>
+        <v>-102.03423015290667</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9727,26 +9727,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.6512053438264</v>
+        <v>273.65092530555904</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.21830565176981</v>
+        <v>342.21793226741335</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.97954197208179</v>
+        <v>329.97914936941294</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54125659820383</v>
+        <v>236.54101499656142</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5422132098254586</v>
+        <v>-6.5423120468610101</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -9835,26 +9835,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.6512053438264</v>
+        <v>273.65092530555904</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.21830565176981</v>
+        <v>342.21793226741335</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.97954197208179</v>
+        <v>329.97914936941294</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54125659820383</v>
+        <v>236.54101499656142</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5422132098254586</v>
+        <v>-6.5423120468610101</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10696,19 +10696,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270733911359912</v>
+        <v>0.24270752503848539</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27034651688409317</v>
+        <v>0.27034673006587473</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4834148155152236E-2</v>
+        <v>8.4834219709393602E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496390909310938</v>
+        <v>1.0496371533379609</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -10834,24 +10834,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0183056517699232</v>
+        <v>7.0179322674134639</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.0183056517699232</v>
+        <v>7.0179322674134639</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.3795419720816113</v>
+        <v>7.3791493694126862</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5412565982040691</v>
+        <v>4.5410149965616533</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8577867901743916</v>
+        <v>1.8576879531388582</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -10946,24 +10946,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.98169434823006</v>
+        <v>-144.98206773258653</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.98169434823006</v>
+        <v>-144.98206773258653</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.6204580279184</v>
+        <v>-165.62085063058731</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75874340179595</v>
+        <v>-133.75898500343837</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.1422132098256</v>
+        <v>-167.14231204686115</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12033,26 +12033,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0400628197132603E-2</v>
+        <v>4.0400732244492706E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0400628197132603E-2</v>
+        <v>4.0400732244492706E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4976226924809473E-2</v>
+        <v>4.4976333540785167E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6450459578342811E-2</v>
+        <v>4.6450543479454917E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2710913108583528E-2</v>
+        <v>8.2710962018438819E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12090,26 +12090,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373162068661405</v>
+        <v>0.11373151663925395</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582408338955854</v>
+        <v>0.13582397934219845</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520517650773459</v>
+        <v>0.13520506989175887</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9472585288999812E-2</v>
+        <v>9.9472501387887699E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6495552855218461E-2</v>
+        <v>-2.6495601765073741E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8432905171653512E-2</v>
+        <v>2.8432879159813487E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12262,26 +12262,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6255700090237535E-2</v>
+        <v>7.6255622054717448E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5362622095460578E-2</v>
+        <v>9.5362518048100475E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9609912549446502E-2</v>
+        <v>8.9609805933470815E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2143789622935073E-2</v>
+        <v>8.2143705721822974E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2374372574354012E-3</v>
+        <v>3.2374861672906821E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12369,26 +12369,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6255700090237535E-2</v>
+        <v>7.6255622054717448E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5362622095460578E-2</v>
+        <v>9.5362518048100475E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9609912549446502E-2</v>
+        <v>8.9609805933470815E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2143789622935073E-2</v>
+        <v>8.2143705721822974E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2374372574354012E-3</v>
+        <v>3.2374861672906821E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12438,16 +12438,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83335956</v>
+        <v>0.83319845999999997</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83335956</v>
+        <v>0.83319845999999997</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79611443999999998</v>
+        <v>0.79596054000000005</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12494,16 +12494,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>1152.5896756606835</v>
+        <v>1152.3668640369121</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>1152.5896756606835</v>
+        <v>1152.3668640369121</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1101.0772879216586</v>
+        <v>1100.8644343592848</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12549,16 +12549,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>4.2118932902653334</v>
+        <v>4.2110833820502434</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>3.3679953895672696</v>
+        <v>3.367347983203985</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3368047041377373</v>
+        <v>3.3361636226501781</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12604,16 +12604,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.8522441011235951E-2</v>
+        <v>5.8429064516129031E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.8522441011235951E-2</v>
+        <v>5.8429064516129031E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.5906912921348313E-2</v>
+        <v>5.5817709677419357E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -12741,26 +12741,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265497363660364</v>
+        <v>-0.16265509823772861</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1011580991810774E-2</v>
+        <v>-2.101155896013962E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815583650530536</v>
+        <v>0.73815593194776841</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.349820999660122</v>
+        <v>-6.3498066117478089</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82817004746525846</v>
+        <v>-0.8281697302732316</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13352,19 +13352,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.0408498529363</v>
+        <v>165.04102992436358</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88882401842852</v>
+        <v>161.88901663055111</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.40023875484422</v>
+        <v>117.4003586667779</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5916.9578793095852</v>
+        <v>-5916.8684897219155</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13460,24 +13460,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373162068661405</v>
+        <v>0.11373151663925395</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582408338955854</v>
+        <v>0.13582397934219845</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520517650773459</v>
+        <v>0.13520506989175887</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9472585288999812E-2</v>
+        <v>9.9472501387887699E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6495552855218461E-2</v>
+        <v>-2.6495601765073741E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13746,30 +13746,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5352644818446108</v>
+        <v>1.5349661230614118</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9199462653346504</v>
+        <v>1.9195730186114348</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8512831686181324</v>
+        <v>1.8509230876274363</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3270666551233861</v>
+        <v>1.3268087594765656</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.670375784049601E-2</v>
+        <v>-3.6697216891245832E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.218556465109216</v>
+        <v>-1.2183209011870488</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13803,30 +13803,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10781351698346985</v>
+        <v>0.10764138310388582</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13482768717237714</v>
+        <v>0.1346124136473657</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13000584049284636</v>
+        <v>0.12979825298930128</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.3192883084507447E-2</v>
+        <v>9.3044092529913441E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.577511084304495E-3</v>
+        <v>-2.5734373696525829E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.557278547115281E-2</v>
+        <v>-8.5436248330087575E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13860,23 +13860,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8918668092603955E-2</v>
+        <v>1.8892134196260898E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2863865384056794E-2</v>
+        <v>2.2831798251680843E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7177094513494143E-2</v>
+        <v>1.7153003216841281E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1932063880198416E-3</v>
+        <v>1.1915328867743722E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.5397865011470463E-2</v>
+        <v>-6.5306142900654951E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.6512053438264</v>
+        <v>273.65092530555904</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6400667978301</v>
+        <v>3420.6365663194879</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.29410939029412</v>
+        <v>327.31267702560837</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.9341761881242</v>
+        <v>1424.9492433450962</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14758,7 +14758,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7594000000000003</v>
+        <v>7.7579000000000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>7.9943036498578008</v>
+        <v>7.9928427545948519</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>16.698361283175959</v>
+        <v>16.695208866956804</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.08444191401185</v>
+        <v>304.0841307321914</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.55966843889985</v>
+        <v>281.5593803075846</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90221277474853</v>
+        <v>337.90186698584517</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.69668447766503</v>
+        <v>289.69638801941454</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.48091799566112</v>
+        <v>375.48053375095964</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.06885859280618</v>
+        <v>298.06855356697372</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.23881776663006</v>
+        <v>417.23839078939289</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68298680397231</v>
+        <v>306.68267296295653</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.6406877361124</v>
+        <v>463.64021327397836</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.54606153437135</v>
+        <v>315.54573862341528</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.20299207790436</v>
+        <v>515.2024648499937</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.66527728679205</v>
+        <v>324.6649450437763</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14992,7 +14992,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.49963186384696</v>
+        <v>572.49904600198397</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.0480364836622</v>
+        <v>334.04769463889221</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.1683327232696</v>
+        <v>636.1676817066683</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70195547588264</v>
+        <v>343.70160375186964</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.91774288538534</v>
+        <v>706.91701946807154</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.63487072531638</v>
+        <v>353.6345088365523</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.53532060758698</v>
+        <v>785.53451673774885</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.85484516594897</v>
+        <v>363.85447281867465</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.055523925148</v>
+        <v>3801.0516341523926</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6241665304462</v>
+        <v>1760.6223648130358</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.0834115157631</v>
+        <v>4972.0783233831462</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15564,7 +15564,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.0834115157631</v>
+        <v>4972.0783233831462</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15594,19 +15594,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.6400667978291</v>
+        <v>3420.6365663194874</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.0078214861169</v>
+        <v>3531.0042080640196</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.8047836640276</v>
+        <v>3761.8009340581302</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.6793957537502</v>
+        <v>4335.674958878918</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.0636548343173</v>
+        <v>5077.0584592712003</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15615,19 +15615,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.6400667978287</v>
+        <v>3420.6365663194865</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.4772074356179</v>
+        <v>3641.4734809657621</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.2020095025982</v>
+        <v>4152.1977603875421</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.7638413036493</v>
+        <v>5750.7579563160789</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.4076630156069</v>
+        <v>8648.3988127527537</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15636,19 +15636,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6400667978278</v>
+        <v>3420.6365663194865</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.2137028385996</v>
+        <v>3778.2098364407966</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.208455614651</v>
+        <v>4689.2036569593356</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.4803312220756</v>
+        <v>8276.4718615673955</v>
       </c>
       <c r="F58" s="124">
-        <v>17363.967320114465</v>
+        <v>17363.949550869431</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15657,19 +15657,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6400667978273</v>
+        <v>3420.6365663194856</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.5262635583581</v>
+        <v>3917.522254596418</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.7868447310057</v>
+        <v>5301.7814191996249</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.523536278039</v>
+        <v>12134.511118532821</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.342222828964</v>
+        <v>36349.3050250874</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15678,19 +15678,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6400667978273</v>
+        <v>3420.6365663194852</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.0946754830661</v>
+        <v>4047.0905339285673</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.7503711415848</v>
+        <v>5943.7442886631488</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.424876438836</v>
+        <v>17688.406775163352</v>
       </c>
       <c r="F60" s="124">
-        <v>76382.702860968697</v>
+        <v>76382.624695481587</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15699,19 +15699,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6400667978269</v>
+        <v>3420.6365663194852</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.3920388265542</v>
+        <v>4161.3877803069736</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.6323165538088</v>
+        <v>6585.6255772118038</v>
       </c>
       <c r="E61" s="124">
-        <v>25476.693102682471</v>
+        <v>25476.667031359368</v>
       </c>
       <c r="F61" s="124">
-        <v>159940.16898715289</v>
+        <v>159940.00531395525</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15761,23 +15761,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9943036498578008</v>
+        <v>7.9928427545948519</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9943036498578008</v>
+        <v>7.9928427545948519</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9943036498578008</v>
+        <v>7.9928427545948519</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9943036498578008</v>
+        <v>7.9928427545948519</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9943036498578008</v>
+        <v>7.9928427545948519</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15788,23 +15788,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>7.9943036498577955</v>
+        <v>7.9928427545948484</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6134995108845036</v>
+        <v>8.6119182829193797</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9083389693995141</v>
+        <v>9.9065061061429756</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.127945869601978</v>
+        <v>13.1254873174114</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.287331606401384</v>
+        <v>17.284064731422148</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15815,23 +15815,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>7.994303649857792</v>
+        <v>7.9928427545948448</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2332655534508454</v>
+        <v>9.2315638819761414</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.098583276518728</v>
+        <v>12.096324767626463</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.066989607172516</v>
+        <v>21.062988204575827</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.323631469653563</v>
+        <v>37.316470799098582</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15842,23 +15842,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>7.9943036498577866</v>
+        <v>7.9928427545948448</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>10.000397876147346</v>
+        <v>9.9985471224336777</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.111348823089473</v>
+        <v>15.108504822203381</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.237008750004257</v>
+        <v>35.230253587570509</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.220507930071975</v>
+        <v>86.203844784382937</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15869,23 +15869,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>7.9943036498577849</v>
+        <v>7.9928427545948395</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.781982689848922</v>
+        <v>10.779980045241706</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.548095399718957</v>
+        <v>18.544583511612846</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>56.881776200241951</v>
+        <v>56.870814657373131</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>192.73409600661438</v>
+        <v>192.6967333235437</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15896,23 +15896,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>7.9943036498577849</v>
+        <v>7.992842754594836</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.508899936740207</v>
+        <v>11.506756025173566</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.149701318097975</v>
+        <v>22.145489504492332</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.040811120277311</v>
+        <v>88.023794222220971</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>417.33313111551865</v>
+        <v>417.25212051665545</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15922,23 +15922,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>7.9943036498577813</v>
+        <v>7.992842754594836</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.150142068633137</v>
+        <v>12.147873539956889</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.750849542862916</v>
+        <v>25.745937892704589</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>131.7353074328642</v>
+        <v>131.70979907492818</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>886.11531599676232</v>
+        <v>885.94320364707971</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.220507930071975</v>
+        <v>86.203844784382937</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.066989607172516</v>
+        <v>21.062988204575827</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.098583276518728</v>
+        <v>12.096324767626463</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2332655534508454</v>
+        <v>9.2315638819761414</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.9943036498577866</v>
+        <v>7.9928427545948448</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.24</v>
+        <v>-14.26</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83335956</v>
+        <v>0.83319845999999997</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83335956</v>
+        <v>0.83319845999999997</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.531381037228808</v>
+        <v>17.528067587046532</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.21830565176981</v>
+        <v>342.21793226741335</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.6512053438264</v>
+        <v>273.65092530555904</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7398959050977965</v>
+        <v>-4.7398757115330907</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.24</v>
+        <v>14.26</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16420,7 +16420,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9943036498578008</v>
+        <v>7.9928427545948519</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.098583276518728</v>
+        <v>12.096324767626463</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2332655534508454</v>
+        <v>9.2315638819761414</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.066989607172516</v>
+        <v>21.062988204575827</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.31920099803591</v>
+        <v>13.316705277886271</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>7.9943036498577866</v>
+        <v>7.9928427545948448</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.220507930071975</v>
+        <v>86.203844784382937</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.698021477228806</v>
+        <v>16.694869127046534</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.698361283175959</v>
+        <v>16.695208866956804</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67052868439944047</v>
+        <v>-0.67051940919606068</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83335956</v>
+        <v>0.83319845999999997</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6267178611199999</v>
+        <v>1.6264033939199998</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.5493869963411484</v>
+        <v>8.5477729930478255</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>10.176104857461148</v>
+        <v>10.174176386967826</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.39058020308942809</v>
+        <v>0.3905806442959685</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.24</v>
+        <v>14.26</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11016267230709409</v>
+        <v>0.10954171828338932</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE48C52-EBFD-4768-AD84-BC815DB304E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9405176D-275D-4A13-8A13-8AB889D23916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1821,14 +1817,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2311,6 +2299,45 @@
   </si>
   <si>
     <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3004,7 +3031,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3697,29 +3724,32 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4009,7 +4039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4029,15 +4059,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4061,13 +4091,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4094,7 +4124,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4104,7 +4134,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4130,24 +4160,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
-        <v>374</v>
-      </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="B12" s="339" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4157,10 +4187,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4183,18 +4213,23 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4206,7 +4241,7 @@
         <v>10.174176386967826</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4214,7 +4249,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4229,7 +4264,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4238,22 +4273,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
-        <v>375</v>
-      </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="B25" s="339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="B26" s="342" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4300,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="340" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4326,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="340" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4361,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="340" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,17 +4383,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4373,7 +4408,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4406,7 +4441,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4418,13 +4453,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="340" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,13 +4475,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="340" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4462,26 +4497,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="B53" s="339" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
-        <v>376</v>
-      </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="B54" s="339" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4507,7 +4542,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4516,7 +4551,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4525,7 +4560,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4538,22 +4573,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
-        <v>377</v>
-      </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="B63" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="342" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4562,7 +4597,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4570,26 +4605,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4606,27 +4641,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
-        <v>378</v>
-      </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="B73" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
-        <v>379</v>
-      </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="B74" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4638,7 +4673,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4651,7 +4686,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4663,13 +4698,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
-        <v>380</v>
-      </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="B81" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4717,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="B85" s="339" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4705,7 +4740,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4723,7 +4758,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4736,7 +4771,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4749,7 +4784,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4780,7 +4815,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4792,17 +4827,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
-        <v>381</v>
-      </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="B98" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
@@ -4815,7 +4850,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4824,13 +4859,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
-        <v>382</v>
-      </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="B104" s="340" t="s">
+        <v>379</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4973,17 +5008,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
-        <v>385</v>
-      </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="B115" s="343" t="s">
+        <v>382</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>372</v>
+        <v>417</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4992,22 +5027,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="B119" s="344" t="s">
+        <v>380</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
-        <v>384</v>
-      </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="B120" s="339" t="s">
+        <v>381</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5016,7 +5051,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5025,7 +5060,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5047,7 +5082,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>265</v>
+        <v>414</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5092,124 +5127,160 @@
         <v>0.3905806442959685</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>2.3365509275951246</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>15.07965945407336</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>416</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>17.416210381668485</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>-4.3207362042349873E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>386</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="338" t="s">
+        <v>388</v>
+      </c>
+      <c r="C140" s="339"/>
+      <c r="D140" s="339"/>
+      <c r="E140" s="339"/>
+      <c r="F140" s="339"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>392</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="340" t="s">
+        <v>393</v>
+      </c>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="337" t="s">
+        <v>394</v>
+      </c>
+      <c r="C152" s="337"/>
+      <c r="D152" s="337"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="337" t="s">
         <v>395</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="337"/>
+      <c r="D153" s="337"/>
+      <c r="E153" s="337"/>
+      <c r="F153" s="337"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
-        <v>396</v>
-      </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
-        <v>397</v>
-      </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
-        <v>398</v>
-      </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>403</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5226,9 +5297,20 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B143:F143"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5691,7 +5773,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C22" s="181">
         <v>56480</v>
@@ -5717,7 +5799,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C23" s="181">
         <v>-11150</v>
@@ -5743,7 +5825,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C24" s="181">
         <v>-45970</v>
@@ -5801,7 +5883,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7056,7 +7138,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8427,13 +8509,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8441,7 +8523,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8594,7 +8676,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8617,7 +8699,7 @@
         <v>4.6606150928058525E-2</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8639,7 +8721,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8706,7 +8788,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8718,7 +8800,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8729,12 +8811,12 @@
         <v>-348.98732297439159</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8745,12 +8827,12 @@
         <v>1.9378927413063263</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8758,12 +8840,12 @@
         <v>348.98732297439159</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8771,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8847,7 +8929,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8858,15 +8940,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>299</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8883,7 +8965,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8917,7 +8999,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9788,7 +9870,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9813,7 +9895,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10141,7 +10223,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10201,7 +10283,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10325,7 +10407,7 @@
         <v>-227.20000000000005</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10383,7 +10465,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10691,7 +10773,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10830,7 +10912,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10885,7 +10967,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11018,7 +11100,7 @@
         <v>2.0109418896939228E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11045,7 +11127,7 @@
         <v>6.5432630219543694E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11360,7 +11442,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11921,7 +12003,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12600,7 +12682,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13294,7 +13376,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13346,7 +13428,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13799,7 +13881,7 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13855,7 +13937,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14684,10 +14766,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14702,8 +14784,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14718,8 +14800,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14734,8 +14816,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16080,7 +16162,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16132,7 +16214,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16152,7 +16234,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16206,7 +16288,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16219,7 +16301,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16229,11 +16311,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 新秀麗(1910.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16254,8 +16336,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16276,8 +16358,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16287,8 +16369,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16299,10 +16381,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>281</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16320,8 +16402,8 @@
         <v>0.21097145624674352</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16338,8 +16420,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.77230247224880189</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16356,8 +16438,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-4.7398757115330907</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16373,7 +16455,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16383,25 +16465,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>342</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>312</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16411,12 +16493,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16426,8 +16508,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16447,8 +16529,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16458,8 +16540,8 @@
         <v>0.06</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16473,8 +16555,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16484,8 +16566,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16505,8 +16587,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16516,8 +16598,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16531,8 +16613,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16542,8 +16624,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16563,8 +16645,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16574,8 +16656,8 @@
         <v>0.15</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16589,8 +16671,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16601,8 +16683,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16664,8 +16746,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16675,8 +16757,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16690,8 +16772,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16701,12 +16783,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16722,8 +16804,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16733,8 +16815,8 @@
         <v>0.25</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16748,8 +16830,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16759,8 +16841,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16775,7 +16857,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16784,7 +16866,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16793,10 +16875,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16809,7 +16891,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16821,7 +16903,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16837,20 +16919,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16860,19 +16942,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16882,14 +16964,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16912,7 +16994,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16935,12 +17017,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -16994,12 +17076,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17012,7 +17094,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17022,43 +17104,99 @@
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>411</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>2.3365509275951246</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>15.07965945407336</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>412</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>17.416210381668485</v>
+      </c>
+      <c r="D93" t="s">
+        <v>409</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>-4.3207362042349873E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>335</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>336</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>337</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>336</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>337</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>336</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>339</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>337</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>340</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9405176D-275D-4A13-8A13-8AB889D23916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C268274-9746-47DC-AAD3-7EACC9D6BC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1357,10 +1357,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2313,31 +2309,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3031,7 +3043,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3727,6 +3739,11 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4039,7 +4056,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4059,10 +4076,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4091,13 +4108,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4124,7 +4141,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4160,24 +4177,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="342" t="s">
+        <v>370</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4187,10 +4204,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4213,19 +4230,19 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4237,11 +4254,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>10.174176386967826</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4249,7 +4266,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4264,7 +4281,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4273,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="342" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>350</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="345" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4300,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="343" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4326,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="343" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4361,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="343" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4383,17 +4400,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4408,7 +4425,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4453,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="343" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4475,13 +4492,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>349</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="343" t="s">
+        <v>348</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4497,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>354</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="342" t="s">
+        <v>353</v>
+      </c>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>373</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4559,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4551,7 +4568,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4560,7 +4577,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4573,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>374</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4597,7 +4614,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4605,26 +4622,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4641,27 +4658,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="342" t="s">
+        <v>374</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="342" t="s">
         <v>375</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>376</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4673,7 +4690,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4686,7 +4703,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4698,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>377</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="342" t="s">
+        <v>376</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4717,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
-        <v>355</v>
-      </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="B85" s="342" t="s">
+        <v>354</v>
+      </c>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4740,7 +4757,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4751,537 +4768,577 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="337" t="s">
+        <v>417</v>
+      </c>
+      <c r="C88" s="338">
+        <f>BS!G30/BS!G27</f>
+        <v>2.2875080906148866</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="337" t="s">
+        <v>418</v>
+      </c>
+      <c r="C89" s="338">
+        <f>BS!G31/BS!G27</f>
+        <v>1.5035598705501618</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="337" t="s">
+        <v>420</v>
+      </c>
+      <c r="C90" s="339">
+        <f>BS!C50</f>
+        <v>4.1998196571663646</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>676.3</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>327.31267702560837</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>1.835966278286302</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>0</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
-      </c>
-      <c r="D96" s="1" t="str">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
+      </c>
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>7.9928427545948519</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>370</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>379</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="337" t="s">
+        <v>419</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>-12.13407231254085</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>369</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="343" t="s">
+        <v>378</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>261</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.25</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>86.2 HKD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.15</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>21.06 HKD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.06</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>12.1 HKD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>9.23 HKD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>7.99 HKD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>16.694869127046534</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="343" t="s">
-        <v>382</v>
-      </c>
-      <c r="C115" s="343"/>
-      <c r="D115" s="343"/>
-      <c r="E115" s="343"/>
-      <c r="F115" s="343"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>417</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="346" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>415</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="347" t="s">
+        <v>379</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="342" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>263</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>0.83319845999999997</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>1.6264033939199998</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>8.5477729930478255</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>10.174176386967826</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.3905806442959685</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>2.3365509275951246</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>2.2385297827832122</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>15.07965945407336</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>416</v>
-      </c>
-      <c r="C135" s="239">
+        <v>14.126999749572944</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>414</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>17.416210381668485</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>16.365529532356156</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>-4.3207362042349873E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>1.9726994694245992E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>385</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>386</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="338" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="344" t="s">
+        <v>391</v>
+      </c>
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>388</v>
       </c>
-      <c r="C140" s="339"/>
-      <c r="D140" s="339"/>
-      <c r="E140" s="339"/>
-      <c r="F140" s="339"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="340" t="s">
-        <v>393</v>
-      </c>
-      <c r="C149" s="340"/>
-      <c r="D149" s="340"/>
-      <c r="E149" s="340"/>
-      <c r="F149" s="340"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="337" t="s">
-        <v>394</v>
-      </c>
-      <c r="C152" s="337"/>
-      <c r="D152" s="337"/>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="337" t="s">
-        <v>395</v>
-      </c>
-      <c r="C153" s="337"/>
-      <c r="D153" s="337"/>
-      <c r="E153" s="337"/>
-      <c r="F153" s="337"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="340" t="s">
+        <v>393</v>
+      </c>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>399</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5290,24 +5347,24 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5773,7 +5830,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C22" s="181">
         <v>56480</v>
@@ -5799,7 +5856,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C23" s="181">
         <v>-11150</v>
@@ -5825,7 +5882,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C24" s="181">
         <v>-45970</v>
@@ -5883,7 +5940,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7138,7 +7195,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8515,7 +8572,7 @@
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>419</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8523,7 +8580,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8676,7 +8733,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8699,7 +8756,7 @@
         <v>4.6606150928058525E-2</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8721,7 +8778,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8788,7 +8845,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8800,7 +8857,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8811,12 +8868,12 @@
         <v>-348.98732297439159</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8827,12 +8884,12 @@
         <v>1.9378927413063263</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8840,12 +8897,12 @@
         <v>348.98732297439159</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8853,7 +8910,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8929,7 +8986,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8940,15 +8997,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>298</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8965,7 +9022,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8999,7 +9056,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9870,7 +9927,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9895,7 +9952,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10223,7 +10280,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10283,7 +10340,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10407,7 +10464,7 @@
         <v>-227.20000000000005</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10465,7 +10522,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10773,7 +10830,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10912,7 +10969,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10967,7 +11024,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11100,7 +11157,7 @@
         <v>2.0109418896939228E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11127,7 +11184,7 @@
         <v>6.5432630219543694E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11442,7 +11499,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12003,7 +12060,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12682,7 +12739,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13376,7 +13433,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13428,7 +13485,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13937,7 +13994,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14766,10 +14823,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="348" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14784,8 +14841,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14800,8 +14857,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14816,8 +14873,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16162,7 +16219,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16234,7 +16291,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16288,7 +16345,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16301,7 +16358,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16311,11 +16368,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="350" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 新秀麗(1910.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="350"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16336,8 +16393,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="350"/>
+      <c r="F8" s="350"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16358,8 +16415,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="350"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16369,8 +16426,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="350"/>
+      <c r="F10" s="350"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16381,10 +16438,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>281</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>280</v>
+      </c>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16402,8 +16459,8 @@
         <v>0.21097145624674352</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="350"/>
+      <c r="F12" s="350"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16420,8 +16477,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.77230247224880189</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="350"/>
+      <c r="F13" s="350"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16438,8 +16495,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-4.7398757115330907</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="350"/>
+      <c r="F14" s="350"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16455,7 +16512,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16465,25 +16522,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>341</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="350" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18" s="351"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>312</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>311</v>
+      </c>
+      <c r="E20" s="351"/>
+      <c r="F20" s="351"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16493,12 +16550,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="351"/>
+      <c r="F21" s="351"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16508,8 +16565,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="351"/>
+      <c r="F22" s="351"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16529,8 +16586,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="349"/>
+      <c r="F25" s="349"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16540,8 +16597,8 @@
         <v>0.06</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="349"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16555,8 +16612,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="349"/>
+      <c r="F27" s="349"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16566,8 +16623,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16587,8 +16644,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="349"/>
+      <c r="F31" s="349"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16598,8 +16655,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="349"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16613,8 +16670,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="349"/>
+      <c r="F33" s="349"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16624,8 +16681,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="349"/>
+      <c r="F34" s="349"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16645,8 +16702,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16656,8 +16713,8 @@
         <v>0.15</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="349"/>
+      <c r="F38" s="349"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16671,8 +16728,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="349"/>
+      <c r="F39" s="349"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16683,8 +16740,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16746,8 +16803,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="349"/>
+      <c r="F49" s="349"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16757,8 +16814,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16772,8 +16829,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="349"/>
+      <c r="F51" s="349"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16783,12 +16840,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="349"/>
+      <c r="F52" s="349"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16804,8 +16861,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="349"/>
+      <c r="F55" s="349"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16815,8 +16872,8 @@
         <v>0.25</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="349"/>
+      <c r="F56" s="349"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16830,8 +16887,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="349"/>
+      <c r="F57" s="349"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16841,8 +16898,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16857,7 +16914,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16866,7 +16923,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16875,10 +16932,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16891,7 +16948,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16903,7 +16960,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16919,20 +16976,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16942,19 +16999,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16964,14 +17021,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16994,7 +17051,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17017,15 +17074,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C123</f>
+        <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
@@ -17076,12 +17133,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17094,7 +17151,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17106,16 +17163,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C90" s="135">
-        <f>Thesis!E19</f>
-        <v>3.4500000000000003E-2</v>
+        <f>(Thesis!E19+Thesis!C67)/2</f>
+        <v>5.7250000000000002E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
@@ -17124,7 +17181,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.3365509275951246</v>
+        <v>2.2385297827832122</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17134,27 +17191,27 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>15.07965945407336</v>
+        <v>14.126999749572944</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>17.416210381668485</v>
+        <v>16.365529532356156</v>
       </c>
       <c r="D93" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>128</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>-4.3207362042349873E-2</v>
+        <v>1.9726994694245992E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
@@ -17162,7 +17219,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17170,30 +17227,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>335</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>336</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>337</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C268274-9746-47DC-AAD3-7EACC9D6BC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18FE529A-F1C2-42FA-A5CE-EE93DFD7A129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
     <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -180,10 +181,6 @@
   </si>
   <si>
     <t>Total Liabilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HKD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1581,10 +1578,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1789,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2353,23 +2342,34 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>Target Return</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>新秀麗</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1910.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>USD</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>CNS_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -2377,26 +2377,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="18">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00\x"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="182" formatCode="#,##0_ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="185" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="187" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.000_ "/>
-    <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="192" formatCode="0.0\x"/>
-    <numFmt numFmtId="193" formatCode="0\x"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
+    <numFmt numFmtId="181" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3071,7 +3071,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3113,23 +3113,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3138,13 +3138,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3215,10 +3215,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3229,7 +3229,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3267,7 +3267,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3277,7 +3277,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3288,29 +3288,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3326,7 +3326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3340,38 +3340,38 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="187" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3391,17 +3391,17 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3416,11 +3416,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3429,51 +3429,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3489,7 +3489,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -3523,21 +3523,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3546,7 +3546,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3556,13 +3556,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3573,7 +3573,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3592,9 +3592,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3603,23 +3603,23 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3637,13 +3637,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3651,7 +3651,7 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3688,7 +3688,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3710,21 +3710,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3735,7 +3735,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3743,30 +3743,30 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4057,7 +4057,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
@@ -4067,24 +4067,24 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="44">
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="247" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4096,7 +4096,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
         <v>1910.HK Stock Information</v>
@@ -4106,9 +4106,9 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
         <v>421</v>
@@ -4117,19 +4117,19 @@
         <v>422</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="50">
         <v>14.26</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>41</v>
+        <v>405</v>
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
@@ -4139,9 +4139,9 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="B8" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4149,9 +4149,9 @@
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4160,7 +4160,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="B10" s="4" t="str">
         <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
         <v>Capitalization (HKD):</v>
@@ -4172,29 +4172,29 @@
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="342" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1">
+      <c r="B12" s="340" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4202,9 +4202,9 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>423</v>
@@ -4212,7 +4212,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="B17" s="4" t="s">
         <v>1</v>
       </c>
@@ -4225,30 +4225,30 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="B18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="B20" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
@@ -4258,15 +4258,15 @@
         <v>10.174176386967826</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4275,13 +4275,13 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4289,45 +4289,45 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="345" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B25" s="340" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
+    </row>
+    <row r="26" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B26" s="342" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="108">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C28" s="108">
-        <f>Data!C3</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="343" t="s">
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="B30" s="47" t="s">
         <v>233</v>
-      </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="47" t="s">
-        <v>234</v>
       </c>
       <c r="C30" s="188">
         <f>Normalized_FCF!C8</f>
@@ -4338,22 +4338,22 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="B31" s="47"/>
       <c r="C31" s="76"/>
     </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="343" t="s">
+    <row r="32" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B32" s="341" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="47" t="s">
         <v>235</v>
-      </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="47" t="s">
-        <v>236</v>
       </c>
       <c r="C33" s="188">
         <f>Normalized_FCF!C9</f>
@@ -4364,9 +4364,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C34" s="188">
         <f>Normalized_FCF!C10</f>
@@ -4377,18 +4377,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="341" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="47" t="s">
         <v>238</v>
-      </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="47" t="s">
-        <v>239</v>
       </c>
       <c r="C37" s="188">
         <f>Normalized_FCF!C11</f>
@@ -4399,18 +4399,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="343" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
+      <c r="B39" s="341" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4423,9 +4423,9 @@
       <c r="E40" s="321"/>
       <c r="F40" s="321"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6">
       <c r="B41" s="47" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4438,9 +4438,9 @@
       <c r="E41" s="321"/>
       <c r="F41" s="321"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
@@ -4451,14 +4451,14 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6">
       <c r="B44" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4469,18 +4469,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="343" t="s">
-        <v>243</v>
-      </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6">
+      <c r="B47" s="341" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
@@ -4491,18 +4491,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="343" t="s">
-        <v>348</v>
+    <row r="50" spans="1:6">
+      <c r="B50" s="341" t="s">
+        <v>346</v>
       </c>
       <c r="C50" s="344"/>
       <c r="D50" s="344"/>
       <c r="E50" s="344"/>
       <c r="F50" s="344"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="B51" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4513,27 +4513,27 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="342" t="s">
-        <v>353</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B53" s="340" t="s">
+        <v>351</v>
+      </c>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
+    </row>
+    <row r="54" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B54" s="340" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4544,9 +4544,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="B57" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
@@ -4557,27 +4557,27 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.10764138310388582</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6">
       <c r="B59" s="254" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
         <v>5.8429064516129031E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4585,115 +4585,115 @@
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" s="233"/>
     </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="345" t="s">
-        <v>254</v>
-      </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B63" s="340" t="s">
+        <v>370</v>
+      </c>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="342" t="s">
+        <v>253</v>
+      </c>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
+    </row>
+    <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="B68" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="B69" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="B70" s="80" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C70" s="263">
         <f>SUM(C67:C69)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="C71" s="122"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C72" s="122"/>
     </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B73" s="340" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B74" s="340" t="s">
+        <v>372</v>
+      </c>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C76" s="263">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="B77" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C77" s="248">
-        <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
+        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>19.187076538267647</v>
       </c>
       <c r="D77" s="1" t="str">
@@ -4701,9 +4701,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4711,40 +4711,40 @@
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" s="233"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6">
+      <c r="B81" s="340" t="s">
+        <v>373</v>
+      </c>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
       <c r="B84" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B85" s="340" t="s">
+        <v>352</v>
+      </c>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C86" s="188">
         <f>Valuation_Model!C7</f>
@@ -4755,12 +4755,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6">
       <c r="B87" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C87" s="248">
-        <f>C86*C28*Exchange_Rate/Common_Shares</f>
+        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>13.030200061959096</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4768,41 +4768,41 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6">
       <c r="B88" s="337" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C88" s="338">
         <f>BS!G30/BS!G27</f>
         <v>2.2875080906148866</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6">
       <c r="B89" s="337" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C89" s="338">
         <f>BS!G31/BS!G27</f>
         <v>1.5035598705501618</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6">
       <c r="B90" s="337" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C90" s="339">
         <f>BS!C50</f>
         <v>4.1998196571663646</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6">
       <c r="B92" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
       <c r="B93" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C93" s="188">
         <f>BS!C66</f>
@@ -4813,9 +4813,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6">
       <c r="B94" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
@@ -4826,12 +4826,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6">
       <c r="B95" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C95" s="248">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
+        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.835966278286302</v>
       </c>
       <c r="D95" s="1" t="str">
@@ -4839,14 +4839,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="B97" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B98" s="47" t="s">
-        <v>259</v>
       </c>
       <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
@@ -4857,12 +4857,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C99" s="248">
-        <f>C98*C28*Exchange_Rate/Common_Shares</f>
+        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0</v>
       </c>
       <c r="D99" s="1" t="str">
@@ -4870,18 +4870,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B101" s="340" t="s">
+        <v>374</v>
+      </c>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
+    </row>
+    <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
@@ -4892,9 +4892,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6">
       <c r="B104" s="337" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4905,9 +4905,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4915,33 +4915,33 @@
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
     </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="343" t="s">
-        <v>378</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B108" s="341" t="s">
+        <v>375</v>
+      </c>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C110" s="260" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D110" s="260" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E110" s="260" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F110" s="260" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
@@ -4963,7 +4963,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6">
       <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
@@ -4985,7 +4985,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
@@ -5007,7 +5007,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
@@ -5029,7 +5029,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
@@ -5051,9 +5051,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="B117" s="235" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
@@ -5064,18 +5064,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="346" t="s">
-        <v>381</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B119" s="345" t="s">
+        <v>378</v>
+      </c>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5083,50 +5083,50 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="347" t="s">
-        <v>379</v>
-      </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="342" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6">
+      <c r="B123" s="343" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="340" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
+    </row>
+    <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="B126" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="B127" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="B128" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
@@ -5137,12 +5137,19 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+      <c r="C130" s="338">
+        <f>C19</f>
+        <v>0.25</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5152,7 +5159,7 @@
         <v>1.6264033939199998</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5162,9 +5169,9 @@
         <v>8.5477729930478255</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6">
       <c r="B133" s="80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
@@ -5175,65 +5182,72 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="B134" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.3905806442959685</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!C90</f>
+        <v>0.06</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>2.2385297827832122</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2.2271494398530356</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>14.126999749572944</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+        <v>14.017334046768918</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>16.365529532356156</v>
+        <v>16.244483486621952</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6">
       <c r="B140" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>1.9726994694245992E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+        <v>2.6977488532385907E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9">
       <c r="A142" s="247" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
@@ -5241,103 +5255,114 @@
       <c r="E142" s="36"/>
       <c r="F142" s="36"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6">
+      <c r="B144" s="347" t="s">
+        <v>384</v>
+      </c>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
+    </row>
+    <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
       <c r="B147" s="344" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C147" s="344"/>
       <c r="D147" s="344"/>
       <c r="E147" s="344"/>
       <c r="F147" s="344"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:6">
       <c r="B148" s="238" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
       <c r="B149" s="238" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6">
+      <c r="B152" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
+    </row>
+    <row r="155" spans="2:6">
+      <c r="B155" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="1" t="s">
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B157" s="346" t="s">
+        <v>391</v>
+      </c>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
+    </row>
+    <row r="159" spans="2:6">
+      <c r="B159" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
+      <c r="B160" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="343" t="s">
-        <v>392</v>
-      </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B155" s="1" t="s">
+    <row r="162" spans="2:2">
+      <c r="B162" s="238" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="340" t="s">
-        <v>393</v>
-      </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B159" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B160" s="238" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B161" s="238" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B162" s="238" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5354,17 +5379,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5389,7 +5403,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
@@ -5397,7 +5411,7 @@
     <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>USD</v>
@@ -5446,9 +5460,9 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -5462,7 +5476,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5470,7 +5484,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5496,9 +5510,9 @@
       <c r="L4" s="181"/>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="181">
         <v>1436.4</v>
@@ -5522,9 +5536,9 @@
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="181">
         <f>230.7+C7</f>
@@ -5553,9 +5567,9 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="189">
         <f>1062.1+227</f>
@@ -5580,9 +5594,9 @@
       <c r="L7" s="189"/>
       <c r="M7" s="189"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="181"/>
       <c r="D8" s="181"/>
@@ -5596,9 +5610,9 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C9" s="181"/>
       <c r="D9" s="181"/>
@@ -5612,9 +5626,9 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10" s="181"/>
       <c r="D10" s="181"/>
@@ -5628,9 +5642,9 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="181"/>
       <c r="D11" s="181"/>
@@ -5644,7 +5658,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -5670,9 +5684,9 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="181">
         <v>13.6</v>
@@ -5696,9 +5710,9 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="181">
         <v>118.3</v>
@@ -5722,9 +5736,9 @@
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="182">
         <v>372.6</v>
@@ -5748,9 +5762,9 @@
       <c r="L15" s="182"/>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="181">
         <v>26.9</v>
@@ -5774,15 +5788,15 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="181"/>
       <c r="D19" s="181"/>
@@ -5796,9 +5810,9 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="181"/>
       <c r="D20" s="181"/>
@@ -5812,9 +5826,9 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="181"/>
       <c r="D21" s="181"/>
@@ -5828,9 +5842,9 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>56480</v>
@@ -5854,9 +5868,9 @@
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-11150</v>
@@ -5880,9 +5894,9 @@
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-45970</v>
@@ -5906,7 +5920,7 @@
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -5935,7 +5949,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -5943,7 +5957,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -5970,7 +5984,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -5997,7 +6011,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6024,7 +6038,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6051,9 +6065,9 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C32" s="183">
         <f>BS!G28</f>
@@ -6078,9 +6092,9 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6094,12 +6108,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6148,9 +6162,9 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="183">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -6197,9 +6211,9 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C38" s="184">
         <f>IF(C36="","",C36+C37)</f>
@@ -6246,9 +6260,9 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="183">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -6295,9 +6309,9 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="185">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -6344,9 +6358,9 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C41" s="185">
         <f>IF(C$4="","",C39-C40)</f>
@@ -6393,9 +6407,9 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" s="183">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -6442,9 +6456,9 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="186">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -6491,9 +6505,9 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C44" s="187">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -6540,9 +6554,9 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C45" s="188">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -6589,9 +6603,9 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" s="183">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -6638,9 +6652,9 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="186">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -6687,9 +6701,9 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="183">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6736,12 +6750,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -6790,9 +6804,9 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" s="183">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6839,14 +6853,14 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C55" s="188">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6893,9 +6907,9 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C56" s="188">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6942,9 +6956,9 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C57" s="188">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -6991,9 +7005,9 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C58" s="188">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7040,15 +7054,15 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C61" s="183">
         <f>IF(C$4="","",-C19)</f>
@@ -7095,9 +7109,9 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" s="183">
         <f>IF(C$4="","",-C20)</f>
@@ -7144,9 +7158,9 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C63" s="183">
         <f>IF(C$4="","",-C21)</f>
@@ -7193,9 +7207,9 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7242,7 +7256,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7291,12 +7305,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7346,9 +7360,9 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -7395,7 +7409,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7445,9 +7459,9 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -7494,7 +7508,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -7544,9 +7558,9 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -7560,13 +7574,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -7615,9 +7629,9 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" s="185">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -7649,9 +7663,9 @@
       <c r="L77" s="335"/>
       <c r="M77" s="335"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C78" s="185">
         <f t="shared" si="40"/>
@@ -7683,7 +7697,7 @@
       <c r="L78" s="335"/>
       <c r="M78" s="335"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -7732,7 +7746,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -7813,7 +7827,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -7824,7 +7838,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -7836,13 +7850,13 @@
         <v>FY Report</v>
       </c>
       <c r="H1" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7851,27 +7865,27 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D3" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H3" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -7883,7 +7897,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="19">
         <v>676.3</v>
@@ -7892,7 +7906,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -7913,7 +7927,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -7925,7 +7939,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -7934,9 +7948,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -7946,7 +7960,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7955,9 +7969,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7967,7 +7981,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7976,7 +7990,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -7988,7 +8002,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7997,7 +8011,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8009,7 +8023,7 @@
       </c>
       <c r="H10" s="295"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8021,9 +8035,9 @@
       </c>
       <c r="H11" s="295"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8034,7 +8048,7 @@
         <v>529.84</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8045,34 +8059,34 @@
         <v>608.66999999999996</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H14" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8081,7 +8095,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8090,7 +8104,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8101,7 +8115,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8110,9 +8124,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8121,7 +8135,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8130,9 +8144,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8141,7 +8155,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8150,7 +8164,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8162,7 +8176,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8171,7 +8185,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8182,7 +8196,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8191,7 +8205,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8202,7 +8216,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8211,7 +8225,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8223,7 +8237,7 @@
       </c>
       <c r="H22" s="295"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8236,9 +8250,9 @@
       </c>
       <c r="H23" s="295"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -8249,7 +8263,7 @@
         <v>301.25</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -8260,24 +8274,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F26" s="205" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G26" s="206" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H26" s="207" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8297,7 +8311,7 @@
         <v>-2094.4399999999996</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8305,14 +8319,14 @@
         <v>145.4</v>
       </c>
       <c r="F28" s="210" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G28" s="181">
         <v>68.8</v>
       </c>
       <c r="H28" s="209"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8320,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="211" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -8331,7 +8345,7 @@
         <v>-2163.2399999999998</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8347,16 +8361,16 @@
       </c>
       <c r="H30" s="209"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>229.4</v>
       </c>
       <c r="F31" s="211" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G31" s="212">
         <f>C31+C40</f>
@@ -8364,7 +8378,7 @@
       </c>
       <c r="H31" s="209"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8373,7 +8387,7 @@
         <v>860.9</v>
       </c>
       <c r="F32" s="213" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G32" s="214">
         <f>G35+G40</f>
@@ -8384,7 +8398,7 @@
         <v>1439.76</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8395,25 +8409,25 @@
       <c r="G33" s="2"/>
       <c r="H33" s="216"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G34" s="218" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H34" s="219" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C35" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="220" t="s">
         <v>31</v>
@@ -8427,7 +8441,7 @@
         <v>831.09</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8435,7 +8449,7 @@
         <v>1687</v>
       </c>
       <c r="F36" s="211" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G36" s="212">
         <f>C4+C15</f>
@@ -8443,7 +8457,7 @@
       </c>
       <c r="H36" s="216"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -8451,7 +8465,7 @@
         <v>406.6</v>
       </c>
       <c r="F37" s="211" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" s="212">
         <f>C6</f>
@@ -8459,7 +8473,7 @@
       </c>
       <c r="H37" s="216"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -8467,7 +8481,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G38" s="212">
         <f>C7+C17</f>
@@ -8475,7 +8489,7 @@
       </c>
       <c r="H38" s="216"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -8483,7 +8497,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="211" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G39" s="212">
         <f>C7+C17+C19+C20</f>
@@ -8494,16 +8508,16 @@
         <v>76.13</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>2093.6</v>
       </c>
       <c r="F40" s="220" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G40" s="214">
         <f>G12+G24</f>
@@ -8514,7 +8528,7 @@
         <v>608.66999999999996</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -8523,7 +8537,7 @@
         <v>350.30000000000018</v>
       </c>
       <c r="F41" s="211" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G41" s="212">
         <f>C70</f>
@@ -8534,7 +8548,7 @@
         <v>608.66999999999996</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -8542,7 +8556,7 @@
         <v>2443.9</v>
       </c>
       <c r="F42" s="222" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G42" s="223">
         <f>C82</f>
@@ -8553,9 +8567,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8564,23 +8578,23 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C45" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F45" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8592,7 +8606,7 @@
       </c>
       <c r="F46" s="283"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -8607,25 +8621,25 @@
       </c>
       <c r="F47" s="283"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="283"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C49" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="283"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -8637,9 +8651,9 @@
       </c>
       <c r="F50" s="283"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C51" s="202"/>
       <c r="D51" s="92">
@@ -8648,24 +8662,24 @@
       </c>
       <c r="F51" s="283"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="283"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C53" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F53" s="283"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -8677,9 +8691,9 @@
       </c>
       <c r="F54" s="283"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -8691,24 +8705,24 @@
       </c>
       <c r="F55" s="283"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="283"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C57" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F57" s="283"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -8717,9 +8731,9 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -8728,24 +8742,24 @@
       </c>
       <c r="F59" s="283"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="283"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" s="262" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F61" s="283"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -8756,12 +8770,12 @@
         <v>4.6606150928058525E-2</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8770,23 +8784,23 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C65" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8797,12 +8811,12 @@
         <v>327.31267702560837</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8810,9 +8824,9 @@
       </c>
       <c r="F67" s="283"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8820,9 +8834,9 @@
       </c>
       <c r="F68" s="283"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8830,9 +8844,9 @@
       </c>
       <c r="F69" s="283"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -8840,24 +8854,24 @@
       </c>
       <c r="F70" s="283"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="283"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F72" s="283"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8868,12 +8882,12 @@
         <v>-348.98732297439159</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8884,12 +8898,12 @@
         <v>1.9378927413063263</v>
       </c>
       <c r="F74" s="283" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="15" customHeight="1">
+      <c r="B75" s="80" t="s">
         <v>328</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="80" t="s">
-        <v>329</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8897,12 +8911,12 @@
         <v>348.98732297439159</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8910,27 +8924,27 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="283"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C78" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F78" s="283"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8942,9 +8956,9 @@
       </c>
       <c r="F79" s="283"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8956,9 +8970,9 @@
       </c>
       <c r="F80" s="283"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8970,9 +8984,9 @@
       </c>
       <c r="F81" s="283"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -8984,9 +8998,9 @@
       </c>
       <c r="F82" s="283"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8995,24 +9009,24 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>297</v>
       </c>
-      <c r="D85" s="270" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-18021.601699999999</v>
       </c>
       <c r="D86" s="248">
-        <f>C86*$H$1/Common_Shares</f>
+        <f>C86*scaling_factor/Common_Shares</f>
         <v>-13.030200061959096</v>
       </c>
       <c r="E86" s="269" t="str">
@@ -9020,16 +9034,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>2539.259017096967</v>
       </c>
       <c r="D87" s="248">
-        <f>C87*$H$1/Common_Shares</f>
+        <f>C87*scaling_factor/Common_Shares</f>
         <v>1.835966278286302</v>
       </c>
       <c r="E87" s="269" t="str">
@@ -9037,16 +9051,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="268" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>0</v>
       </c>
       <c r="D88" s="248">
-        <f>C88*$H$1/Common_Shares</f>
+        <f>C88*scaling_factor/Common_Shares</f>
         <v>0</v>
       </c>
       <c r="E88" s="269" t="str">
@@ -9054,9 +9068,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9085,7 +9099,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
@@ -9097,14 +9111,14 @@
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -9154,15 +9168,15 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -9177,13 +9191,13 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
@@ -9191,7 +9205,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9248,10 +9262,10 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="191">
         <f>C25</f>
@@ -9303,10 +9317,10 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="184">
         <f>C4+C5</f>
@@ -9358,10 +9372,10 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="191">
         <f>C35</f>
@@ -9413,10 +9427,10 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="192">
         <f>C6+C7</f>
@@ -9470,10 +9484,10 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="191">
         <f>BS!$G$39*BS!D58</f>
@@ -9525,10 +9539,10 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="191">
         <f>-C4*C78</f>
@@ -9580,10 +9594,10 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C11" s="193">
         <f>C63</f>
@@ -9637,10 +9651,10 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="191">
         <f>C50</f>
@@ -9692,10 +9706,10 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
@@ -9747,10 +9761,10 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9802,10 +9816,10 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C15" s="191">
         <f>-C4*C83</f>
@@ -9859,10 +9873,10 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
@@ -9916,10 +9930,10 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="191">
         <f>-C4*C85</f>
@@ -9927,7 +9941,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9942,17 +9956,17 @@
       <c r="P17" s="195"/>
       <c r="Q17" s="195"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="191">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -9967,10 +9981,10 @@
       <c r="P18" s="196"/>
       <c r="Q18" s="196"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
@@ -10024,7 +10038,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10043,15 +10057,15 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10066,10 +10080,10 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10087,10 +10101,10 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="197">
         <f>-C4*C28</f>
@@ -10144,10 +10158,10 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="191">
         <f>-C4*C29</f>
@@ -10201,10 +10215,10 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="184">
         <f>C23+C24</f>
@@ -10258,21 +10272,21 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="302"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E27" s="302"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:J28)</f>
@@ -10280,7 +10294,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10328,7 +10342,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10340,7 +10354,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10388,10 +10402,10 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -10443,28 +10457,28 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="302"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" s="302"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C33" s="198">
         <f>AVERAGE(G33:J33)</f>
         <v>-227.20000000000005</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10511,10 +10525,10 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="198">
         <f>AVERAGE(G34:J34)</f>
@@ -10522,7 +10536,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10570,10 +10584,10 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="184">
         <f>C33+C34</f>
@@ -10627,18 +10641,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="302"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E37" s="302"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -10696,7 +10710,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -10754,10 +10768,10 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -10809,28 +10823,28 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="302"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E42" s="302"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C43" s="296">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10878,18 +10892,18 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10904,14 +10918,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E46" s="302"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -10966,10 +10980,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11021,10 +11035,10 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11078,10 +11092,10 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
@@ -11133,31 +11147,31 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="302"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E52" s="302"/>
       <c r="G52" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="87">
         <f>G53</f>
         <v>2.0109418896939228E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11174,17 +11188,17 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>6.5432630219543694E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11201,10 +11215,10 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -11256,24 +11270,24 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="302"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E57" s="302"/>
       <c r="G57" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="191">
         <f>BS!$C67*C66</f>
@@ -11325,10 +11339,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C59" s="191">
         <f>BS!$C68*C67</f>
@@ -11380,10 +11394,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" s="191">
         <f>BS!$C69*C68</f>
@@ -11435,10 +11449,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C61" s="184">
         <f>SUM(C58:C60)</f>
@@ -11490,16 +11504,16 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C62" s="297">
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11546,10 +11560,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C63" s="184">
         <f>C61+C62</f>
@@ -11601,24 +11615,24 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="302"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E65" s="302"/>
       <c r="G65" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C66" s="177">
         <f>G66</f>
@@ -11640,10 +11654,10 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C67" s="177">
         <f>G67</f>
@@ -11665,10 +11679,10 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C68" s="177">
         <f>G68</f>
@@ -11690,10 +11704,10 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -11717,18 +11731,18 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>60</v>
+        <v>426</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11743,10 +11757,10 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -11764,10 +11778,10 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -11821,10 +11835,10 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -11878,10 +11892,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -11935,10 +11949,10 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -11992,10 +12006,10 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12049,10 +12063,10 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12060,7 +12074,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12108,10 +12122,10 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12165,10 +12179,10 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -12222,10 +12236,10 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -12279,10 +12293,10 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -12336,7 +12350,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12394,10 +12408,10 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -12451,10 +12465,10 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C85" s="298">
         <v>0</v>
@@ -12477,10 +12491,10 @@
       <c r="P85" s="253"/>
       <c r="Q85" s="253"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -12501,10 +12515,10 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -12558,18 +12572,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="302"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E89" s="302"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -12625,19 +12639,19 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
         <v>Dividend (HKD)</v>
       </c>
       <c r="C91" s="74">
-        <f>C90*Common_Shares/$C$3</f>
+        <f>C90*Common_Shares/scaling_factor</f>
         <v>1152.3668640369121</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
-        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1152.3668640369121</v>
       </c>
       <c r="H91" s="74">
@@ -12681,18 +12695,18 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C92" s="23">
-        <f>C90/(C19*$C$3/Common_Shares)</f>
+        <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>4.2110833820502434</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
-        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>3.367347983203985</v>
       </c>
       <c r="H92" s="171">
@@ -12736,10 +12750,10 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12791,14 +12805,14 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="302"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
@@ -12816,10 +12830,10 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C96" s="77">
         <f>C4/G4-1</f>
@@ -12873,10 +12887,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
@@ -12930,18 +12944,18 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12956,17 +12970,17 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="302"/>
       <c r="G100" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13023,10 +13037,10 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C102" s="200">
         <f>BS!C4</f>
@@ -13080,10 +13094,10 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C103" s="200">
         <f>BS!C6+BS!C7</f>
@@ -13137,7 +13151,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13194,7 +13208,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13251,21 +13265,21 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="302"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="303"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -13278,10 +13292,10 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C108" s="94">
         <f>C102/C$4</f>
@@ -13335,10 +13349,10 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -13392,10 +13406,10 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C110" s="94">
         <f>BS!$G$38/C$4</f>
@@ -13419,21 +13433,21 @@
       <c r="P110" s="225"/>
       <c r="Q110" s="225"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="302"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E112" s="302"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13482,10 +13496,10 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13534,11 +13548,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="302"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -13592,10 +13606,10 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C117" s="23">
         <f>C81</f>
@@ -13647,9 +13661,9 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C118" s="42">
         <f>C4/C101</f>
@@ -13701,9 +13715,9 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
@@ -13757,10 +13771,10 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C120" s="102">
         <f>C8/C105</f>
@@ -13814,7 +13828,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -13833,15 +13847,15 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C122" s="54"/>
       <c r="D122" s="56"/>
       <c r="E122" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F122" s="56"/>
       <c r="G122" s="37"/>
@@ -13856,10 +13870,10 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
@@ -13877,7 +13891,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -13935,10 +13949,10 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13992,9 +14006,9 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14042,688 +14056,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14745,7 +14759,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
@@ -14754,34 +14768,34 @@
     <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="131" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3" s="107">
-        <f>Normalized_FCF!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
@@ -14792,7 +14806,7 @@
         <v>USD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F4" s="135">
         <f>Thesis!C76</f>
@@ -14800,9 +14814,9 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8">
       <c r="B5" s="227" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="228">
         <f>Thesis!C70</f>
@@ -14811,9 +14825,9 @@
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
       <c r="B6" s="150" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -14824,14 +14838,14 @@
         <v>USD</v>
       </c>
       <c r="E6" s="348" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C7" s="226">
         <f>BS!G31</f>
@@ -14845,9 +14859,9 @@
       <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
@@ -14861,9 +14875,9 @@
       <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8">
       <c r="B9" s="227" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C9" s="229">
         <f>BS!H42</f>
@@ -14877,9 +14891,9 @@
       <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
@@ -14891,9 +14905,9 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="230" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
@@ -14905,12 +14919,12 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="112">
-        <f>(C10*C3)/Common_Shares*C11</f>
+        <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
         <v>7.9928427545948519</v>
       </c>
       <c r="D12" t="str">
@@ -14919,12 +14933,12 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14932,15 +14946,15 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
@@ -14948,9 +14962,9 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
@@ -14958,12 +14972,12 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="141">
-        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
+        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
         <v>16.695208866956804</v>
       </c>
       <c r="D18" t="str">
@@ -14972,28 +14986,28 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="129" t="s">
+      <c r="D20" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="129" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="129" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="129" t="s">
+      <c r="F20" s="130" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="130" t="s">
-        <v>112</v>
-      </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15015,7 +15029,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15037,7 +15051,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15059,7 +15073,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15081,7 +15095,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15103,7 +15117,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15125,7 +15139,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15147,7 +15161,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15169,7 +15183,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15191,7 +15205,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15213,7 +15227,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15235,7 +15249,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15257,7 +15271,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15279,7 +15293,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15301,7 +15315,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15323,7 +15337,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15345,7 +15359,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15367,7 +15381,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15389,7 +15403,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15411,7 +15425,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15433,7 +15447,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -15455,7 +15469,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -15477,7 +15491,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -15499,7 +15513,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -15521,7 +15535,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -15543,7 +15557,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -15565,7 +15579,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -15587,7 +15601,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -15609,7 +15623,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -15631,7 +15645,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -15653,9 +15667,9 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -15675,10 +15689,10 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
@@ -15686,13 +15700,13 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C54" s="137"/>
       <c r="D54" s="137"/>
@@ -15700,7 +15714,7 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
         <v>4972.0783233831462</v>
@@ -15727,7 +15741,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
@@ -15749,7 +15763,7 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
@@ -15770,7 +15784,7 @@
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
@@ -15791,7 +15805,7 @@
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
@@ -15812,7 +15826,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
@@ -15833,7 +15847,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
@@ -15854,16 +15868,16 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="115"/>
       <c r="D63" s="115"/>
@@ -15871,7 +15885,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -15894,7 +15908,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
@@ -15920,7 +15934,7 @@
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -15947,7 +15961,7 @@
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -15974,7 +15988,7 @@
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16001,7 +16015,7 @@
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16028,7 +16042,7 @@
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16054,7 +16068,7 @@
         <v>417.25212051665545</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16080,24 +16094,24 @@
         <v>885.94320364707971</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C73" s="172" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D73" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" s="173" t="s">
         <v>114</v>
       </c>
-      <c r="E73" s="173" t="s">
-        <v>115</v>
-      </c>
       <c r="F73" s="173" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16119,7 +16133,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16142,7 +16156,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16165,7 +16179,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16188,7 +16202,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16210,38 +16224,38 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16272,7 +16286,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I98"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -16282,22 +16296,22 @@
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H3" s="276">
         <v>0</v>
@@ -16307,16 +16321,16 @@
         <v>-14.26</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" s="121">
         <v>3</v>
       </c>
       <c r="D4" s="121"/>
       <c r="E4" s="156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F4" s="156"/>
       <c r="H4" s="276">
@@ -16327,7 +16341,7 @@
         <v>0.83319845999999997</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9">
       <c r="H5" s="276">
         <v>2</v>
       </c>
@@ -16336,16 +16350,16 @@
         <v>0.83319845999999997</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="107">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16356,9 +16370,9 @@
         <v>17.528067587046532</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16381,9 +16395,9 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
@@ -16403,9 +16417,9 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
@@ -16425,7 +16439,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9">
       <c r="E10" s="350"/>
       <c r="F10" s="350"/>
       <c r="H10" s="276">
@@ -16436,9 +16450,9 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E11" s="350"/>
       <c r="F11" s="350"/>
@@ -16450,9 +16464,9 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" s="159">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16469,9 +16483,9 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="159">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16487,9 +16501,9 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16498,49 +16512,49 @@
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="151">
         <v>10</v>
       </c>
       <c r="E18" s="350" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F18" s="351"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6">
       <c r="E19" s="351"/>
       <c r="F19" s="351"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E20" s="351"/>
       <c r="F20" s="351"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16553,9 +16567,9 @@
       <c r="E21" s="351"/>
       <c r="F21" s="351"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16568,18 +16582,18 @@
       <c r="E22" s="351"/>
       <c r="F22" s="351"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="167">
         <f>C18</f>
@@ -16589,9 +16603,9 @@
       <c r="E25" s="349"/>
       <c r="F25" s="349"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" s="165">
         <v>0.06</v>
@@ -16600,9 +16614,9 @@
       <c r="E26" s="349"/>
       <c r="F26" s="349"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
@@ -16615,9 +16629,9 @@
       <c r="E27" s="349"/>
       <c r="F27" s="349"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="166">
         <v>0.6</v>
@@ -16626,18 +16640,18 @@
       <c r="E28" s="349"/>
       <c r="F28" s="349"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C31" s="167">
         <f>C18</f>
@@ -16647,9 +16661,9 @@
       <c r="E31" s="349"/>
       <c r="F31" s="349"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C32" s="165">
         <v>0.02</v>
@@ -16658,9 +16672,9 @@
       <c r="E32" s="349"/>
       <c r="F32" s="349"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
@@ -16673,9 +16687,9 @@
       <c r="E33" s="349"/>
       <c r="F33" s="349"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C34" s="166">
         <v>0.2</v>
@@ -16684,18 +16698,18 @@
       <c r="E34" s="349"/>
       <c r="F34" s="349"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" s="167">
         <f>C18</f>
@@ -16705,9 +16719,9 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" s="165">
         <v>0.15</v>
@@ -16716,9 +16730,9 @@
       <c r="E38" s="349"/>
       <c r="F38" s="349"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
@@ -16731,9 +16745,9 @@
       <c r="E39" s="349"/>
       <c r="F39" s="349"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" s="168">
         <f>1-C28-C34</f>
@@ -16743,9 +16757,9 @@
       <c r="E40" s="349"/>
       <c r="F40" s="349"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -16756,23 +16770,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="151">
         <v>15</v>
@@ -16780,23 +16794,23 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E48" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="167">
         <f>C46</f>
@@ -16806,9 +16820,9 @@
       <c r="E49" s="349"/>
       <c r="F49" s="349"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C50" s="165">
         <v>0</v>
@@ -16817,9 +16831,9 @@
       <c r="E50" s="349"/>
       <c r="F50" s="349"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
@@ -16832,9 +16846,9 @@
       <c r="E51" s="349"/>
       <c r="F51" s="349"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52" s="166">
         <v>0.05</v>
@@ -16843,18 +16857,18 @@
       <c r="E52" s="349"/>
       <c r="F52" s="349"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C55" s="167">
         <f>C46</f>
@@ -16864,9 +16878,9 @@
       <c r="E55" s="349"/>
       <c r="F55" s="349"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C56" s="165">
         <v>0.25</v>
@@ -16875,9 +16889,9 @@
       <c r="E56" s="349"/>
       <c r="F56" s="349"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
@@ -16890,9 +16904,9 @@
       <c r="E57" s="349"/>
       <c r="F57" s="349"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="166">
         <v>0.05</v>
@@ -16901,9 +16915,9 @@
       <c r="E58" s="349"/>
       <c r="F58" s="349"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -16914,33 +16928,33 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C64" s="167">
         <f>C18</f>
@@ -16948,24 +16962,24 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C65" s="152">
         <v>0.111211776070739</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
@@ -16976,20 +16990,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="13.15">
+      <c r="B68" s="109" t="s">
+        <v>358</v>
+      </c>
+      <c r="E68" s="282" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B68" s="109" t="s">
-        <v>360</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16997,21 +17011,21 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17019,39 +17033,39 @@
       </c>
       <c r="E71" s="281"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
         <v>-0.67051940919606068</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17059,9 +17073,9 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
@@ -17072,23 +17086,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -17098,9 +17112,9 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
@@ -17108,9 +17122,9 @@
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
@@ -17121,24 +17135,24 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
         <v>0.3905806442959685</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17149,108 +17163,108 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.10954171828338932</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>(Thesis!E19+Thesis!C67)/2</f>
-        <v>5.7250000000000002E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.2385297827832122</v>
+        <v>2.2271494398530356</v>
       </c>
       <c r="D91" s="117"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>14.126999749572944</v>
+        <v>14.017334046768918</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>16.365529532356156</v>
+        <v>16.244483486621952</v>
       </c>
       <c r="D93" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E93" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>1.9726994694245992E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+        <v>2.6977488532385907E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
       <c r="B94" s="100"/>
     </row>
-    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+    <row r="95" spans="2:8" ht="14.65">
       <c r="E95" s="320" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:8" ht="13.9">
       <c r="E96" s="313" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F96" s="318" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="97" spans="5:8" ht="13.9">
       <c r="E97" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>335</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>337</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="98" spans="5:8" ht="13.9">
       <c r="E98" s="315" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18FE529A-F1C2-42FA-A5CE-EE93DFD7A129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719E406A-6CDA-42B8-99BD-9E12D7F3F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719E406A-6CDA-42B8-99BD-9E12D7F3F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4474A370-5636-4A9B-85E6-5F57BB99D69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3744,29 +3744,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4177,13 +4177,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4290,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4317,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4343,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4378,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4470,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4492,7 +4492,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4514,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4590,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4663,22 +4663,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4715,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4734,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4871,13 +4871,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4916,13 +4916,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5065,13 +5065,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5084,22 +5084,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C136" s="92">
         <f>Scenarios!C90</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>418</v>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>2.2271494398530356</v>
+        <v>2.1472332410455732</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>14.017334046768918</v>
+        <v>13.252925372661792</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>16.244483486621952</v>
+        <v>15.400158613707365</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>2.6977488532385907E-2</v>
+        <v>7.755140237917002E-2</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5256,13 +5256,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5299,13 +5299,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5313,22 +5313,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5352,17 +5352,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5379,6 +5368,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17185,8 +17185,8 @@
         <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.06</v>
+        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.2271494398530356</v>
+        <v>2.1472332410455732</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>14.017334046768918</v>
+        <v>13.252925372661792</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17215,7 +17215,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>16.244483486621952</v>
+        <v>15.400158613707365</v>
       </c>
       <c r="D93" t="s">
         <v>405</v>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>2.6977488532385907E-2</v>
+        <v>7.755140237917002E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4474A370-5636-4A9B-85E6-5F57BB99D69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C05505-7869-493F-9B2F-16F586E4296E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="430">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2287,10 +2287,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>in contrast to a cash yield of</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -2346,6 +2342,15 @@
   </si>
   <si>
     <t>Target Return</t>
+  </si>
+  <si>
+    <t>in contrast to a position yield of</t>
+  </si>
+  <si>
+    <t>Position Price Output</t>
+  </si>
+  <si>
+    <t>@ Position Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -3736,37 +3741,37 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4084,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4111,10 +4116,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4125,7 +4130,7 @@
         <v>14.26</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4177,13 +4182,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4207,7 +4212,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4230,7 +4235,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4242,10 +4247,10 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E19" s="336">
-        <v>3.4500000000000003E-2</v>
+        <v>419</v>
+      </c>
+      <c r="E19" s="339">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4266,7 +4271,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4290,22 +4295,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4317,13 +4322,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4343,13 +4348,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4378,13 +4383,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4400,13 +4405,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4470,13 +4475,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4492,7 +4497,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4514,22 +4519,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4590,22 +4595,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4629,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4641,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4663,22 +4668,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4715,13 +4720,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4734,13 +4739,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4769,28 +4774,28 @@
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="337" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="338">
+      <c r="B88" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
         <v>2.2875080906148866</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="337" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="338">
+      <c r="B89" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
         <v>1.5035598705501618</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="337" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="339">
+      <c r="B90" s="336" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="338">
         <f>BS!C50</f>
         <v>4.1998196571663646</v>
       </c>
@@ -4871,13 +4876,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4893,8 +4898,8 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="337" t="s">
-        <v>416</v>
+      <c r="B104" s="336" t="s">
+        <v>415</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4916,13 +4921,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5065,17 +5070,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5084,22 +5089,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5139,14 +5144,14 @@
     </row>
     <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C130" s="338">
+        <v>408</v>
+      </c>
+      <c r="C130" s="337">
         <f>C19</f>
         <v>0.25</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5193,14 +5198,14 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C136" s="92">
-        <f>Scenarios!C90</f>
+        <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5209,7 +5214,7 @@
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C91</f>
+        <f>Scenarios!C97</f>
         <v>2.1472332410455732</v>
       </c>
     </row>
@@ -5219,16 +5224,16 @@
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C92</f>
+        <f>Scenarios!C98</f>
         <v>13.252925372661792</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C93</f>
+        <f>Scenarios!C99</f>
         <v>15.400158613707365</v>
       </c>
       <c r="D139" s="101" t="str">
@@ -5241,7 +5246,7 @@
         <v>263</v>
       </c>
       <c r="C140" s="92">
-        <f>Scenarios!F93</f>
+        <f>Scenarios!F99</f>
         <v>7.755140237917002E-2</v>
       </c>
     </row>
@@ -5256,13 +5261,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B144" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5299,13 +5304,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5313,22 +5318,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5352,6 +5357,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5368,17 +5384,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5954,7 +5959,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8586,7 +8591,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11742,7 +11747,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12074,7 +12079,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16285,7 +16290,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I98"/>
+  <dimension ref="B2:I104"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17177,16 +17182,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>413</v>
-      </c>
-      <c r="C90" s="135">
-        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.08</v>
+        <v>421</v>
+      </c>
+      <c r="C90" s="168">
+        <f>Thesis!E19</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17195,9 +17200,11 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.1472332410455732</v>
+        <v>1.7551171263888887</v>
       </c>
       <c r="D91" s="117"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="100"/>
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
@@ -17205,69 +17212,123 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.252925372661792</v>
+        <v>9.6613825966704479</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>15.400158613707365</v>
-      </c>
-      <c r="D93" t="s">
-        <v>405</v>
+        <v>11.416499723059337</v>
+      </c>
+      <c r="D93" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>7.755140237917002E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" s="100"/>
-    </row>
-    <row r="95" spans="2:8" ht="14.65">
-      <c r="E95" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F95" s="317"/>
+        <v>0.31616716272641943</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
+      <c r="B95" s="109" t="s">
+        <v>405</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9">
-      <c r="E96" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>334</v>
+    <row r="96" spans="2:8">
+      <c r="B96" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="135">
+        <f>Thesis!C67</f>
+        <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9">
-      <c r="E97" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>335</v>
-      </c>
+    <row r="97" spans="2:8">
+      <c r="B97" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" s="117">
+        <f>PV(C96, C76, -C77, 0)</f>
+        <v>2.1472332410455732</v>
+      </c>
+      <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9">
-      <c r="E98" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>336</v>
-      </c>
+    <row r="98" spans="2:8">
+      <c r="B98" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" s="117">
+        <f>C60/(1+C96)^C76</f>
+        <v>13.252925372661792</v>
+      </c>
+      <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>
+    </row>
+    <row r="99" spans="2:8" ht="13.15">
+      <c r="B99" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="112">
+        <f>C97+C98</f>
+        <v>15.400158613707365</v>
+      </c>
+      <c r="D99" t="s">
+        <v>404</v>
+      </c>
+      <c r="E99" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="329">
+        <f>(1-C99/C60)</f>
+        <v>7.755140237917002E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="100"/>
+    </row>
+    <row r="101" spans="2:8" ht="14.65">
+      <c r="E101" s="320" t="s">
+        <v>332</v>
+      </c>
+      <c r="F101" s="317"/>
+    </row>
+    <row r="102" spans="2:8" ht="13.9">
+      <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="13.9">
+      <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="13.9">
+      <c r="E104" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F104" s="319" t="s">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C05505-7869-493F-9B2F-16F586E4296E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35268AD-E957-44ED-AE75-8B3E2990D077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3749,29 +3749,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4182,13 +4182,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4222,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7579000000000002</v>
+        <v>7.7550999999999997</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4244,7 +4244,7 @@
         <v>277</v>
       </c>
       <c r="C19" s="249">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>419</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>10.174176386967826</v>
+        <v>9.1088969706010197</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10954171828338932</v>
+        <v>0.10940387682956731</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4295,22 +4295,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4322,13 +4322,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4348,13 +4348,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4383,13 +4383,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4405,13 +4405,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0179322674134639</v>
+        <v>7.017235283281404</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.98206773258653</v>
+        <v>-144.98276471671861</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4475,13 +4475,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03423015290667</v>
+        <v>-102.03405590687365</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4497,7 +4497,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4519,22 +4519,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.21793226741335</v>
+        <v>342.21723528328124</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.65092530555904</v>
+        <v>273.65040256745999</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10764138310388582</v>
+        <v>0.1076023273696578</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.8429064516129031E-2</v>
+        <v>5.8407976157082743E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4595,22 +4595,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4668,22 +4668,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.187076538267647</v>
+        <v>19.180114853641498</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4720,13 +4720,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4739,13 +4739,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.030200061959096</v>
+        <v>13.025497170690391</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.31267702560837</v>
+        <v>327.34733661152836</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.835966278286302</v>
+        <v>1.8354979797100719</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,13 +4876,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9928427545948519</v>
+        <v>7.9901156626611796</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-12.13407231254085</v>
+        <v>-12.129692853863228</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4921,13 +4921,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.2 HKD</v>
+        <v>86.17 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>12.1 HKD</v>
+        <v>12.09 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>16.694869127046534</v>
+        <v>16.688984661810444</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5070,13 +5070,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5089,22 +5089,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C127" s="250">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83319845999999997</v>
+        <v>0.83289773999999994</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C130" s="337">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>418</v>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>1.6264033939199998</v>
+        <v>1.5126363143377335</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>8.5477729930478255</v>
+        <v>7.5962606562632864</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>10.174176386967826</v>
+        <v>9.1088969706010197</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.3905806442959685</v>
+        <v>0.45419705541194533</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C97</f>
-        <v>2.1472332410455732</v>
+        <v>2.1464582564395682</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C98</f>
-        <v>13.252925372661792</v>
+        <v>13.248254094436222</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C99</f>
-        <v>15.400158613707365</v>
+        <v>15.394712350875789</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F99</f>
-        <v>7.755140237917002E-2</v>
+        <v>7.7552489690780879E-2</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5261,13 +5261,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5304,13 +5304,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5318,22 +5318,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5357,17 +5357,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5384,6 +5373,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5932,11 +5932,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83319845999999997</v>
+        <v>0.83289773999999994</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79596054000000005</v>
+        <v>0.79567325999999994</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -7267,11 +7267,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83319845999999997</v>
+        <v>0.83289773999999994</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79596054000000005</v>
+        <v>0.79567325999999994</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8618,11 +8618,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2803191267602312</v>
+        <v>8.277330573987582</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.13407231254085</v>
+        <v>-12.129692853863228</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.31267702560837</v>
+        <v>327.34733661152836</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8880,11 +8880,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.380572003076</v>
+        <v>-342.34591241715606</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-348.98732297439159</v>
+        <v>-348.95266338847159</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -8896,11 +8896,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9752873127214823</v>
+        <v>1.9754872936117125</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9378927413063263</v>
+        <v>1.9380852217399724</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -8913,7 +8913,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>348.98732297439159</v>
+        <v>348.95266338847159</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18021.601699999999</v>
+        <v>-18015.097299999998</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-13.030200061959096</v>
+        <v>-13.025497170690388</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9045,11 +9045,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2539.259017096967</v>
+        <v>2538.6113301560636</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.835966278286302</v>
+        <v>1.8354979797100721</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9079,11 +9079,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15482.342682903032</v>
+        <v>-15476.485969843934</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.194233783672795</v>
+        <v>-11.189999190980316</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9663,24 +9663,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.98206773258653</v>
+        <v>-144.98276471671861</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.98206773258653</v>
+        <v>-144.98276471671861</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.62085063058731</v>
+        <v>-165.62158348890264</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75898500343837</v>
+        <v>-133.75943599317085</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.14231204686115</v>
+        <v>-167.14249654266081</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9718,24 +9718,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.13692061162669</v>
+        <v>408.13622362749459</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.41793226741333</v>
+        <v>487.41723528328123</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.87914936941291</v>
+        <v>497.87841651109761</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44101499656142</v>
+        <v>286.44056400682894</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.542312046861014</v>
+        <v>-53.542496542660672</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03423015290667</v>
+        <v>-102.03405590687365</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9885,26 +9885,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.65092530555904</v>
+        <v>273.65040256745999</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.21793226741335</v>
+        <v>342.21723528328124</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.97914936941294</v>
+        <v>329.97841651109758</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54101499656142</v>
+        <v>236.54056400682893</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5423120468610101</v>
+        <v>-6.5424965426606683</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -9993,26 +9993,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.65092530555904</v>
+        <v>273.65040256745999</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.21793226741335</v>
+        <v>342.21723528328124</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.97914936941294</v>
+        <v>329.97841651109758</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54101499656142</v>
+        <v>236.54056400682893</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5423120468610101</v>
+        <v>-6.5424965426606683</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10854,19 +10854,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270752503848539</v>
+        <v>0.24270787209903527</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27034673006587473</v>
+        <v>0.27034712800609983</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4834219709393602E-2</v>
+        <v>8.4834353277633792E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496371533379609</v>
+        <v>1.0496335365165861</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -10992,24 +10992,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0179322674134639</v>
+        <v>7.017235283281404</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.0179322674134639</v>
+        <v>7.017235283281404</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.3791493694126862</v>
+        <v>7.3784165110973587</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5410149965616533</v>
+        <v>4.5405640068291442</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8576879531388582</v>
+        <v>1.8575034573391951</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11104,24 +11104,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.98206773258653</v>
+        <v>-144.98276471671861</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.98206773258653</v>
+        <v>-144.98276471671861</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.62085063058731</v>
+        <v>-165.62158348890264</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75898500343837</v>
+        <v>-133.75943599317085</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.14231204686115</v>
+        <v>-167.14249654266081</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12191,26 +12191,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0400732244492706E-2</v>
+        <v>4.0400926466231571E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0400732244492706E-2</v>
+        <v>4.0400926466231571E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4976333540785167E-2</v>
+        <v>4.4976532557273151E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6450543479454917E-2</v>
+        <v>4.645070009486417E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2710962018438819E-2</v>
+        <v>8.2711053316835315E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12248,26 +12248,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373151663925395</v>
+        <v>0.11373132241751507</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582397934219845</v>
+        <v>0.13582378512045959</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520506989175887</v>
+        <v>0.13520487087527092</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9472501387887699E-2</v>
+        <v>9.9472344772478447E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6495601765073741E-2</v>
+        <v>-2.6495693063470247E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8432879159813487E-2</v>
+        <v>2.8432830604378768E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12420,26 +12420,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6255622054717448E-2</v>
+        <v>7.6255476388413304E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5362518048100475E-2</v>
+        <v>9.5362323826361603E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9609805933470815E-2</v>
+        <v>8.9609606916982831E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2143705721822974E-2</v>
+        <v>8.2143549106413721E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2374861672906821E-3</v>
+        <v>3.2375774656871873E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12527,26 +12527,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6255622054717448E-2</v>
+        <v>7.6255476388413304E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5362518048100475E-2</v>
+        <v>9.5362323826361603E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9609805933470815E-2</v>
+        <v>8.9609606916982831E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2143705721822974E-2</v>
+        <v>8.2143549106413721E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2374861672906821E-3</v>
+        <v>3.2375774656871873E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12596,16 +12596,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83319845999999997</v>
+        <v>0.83289773999999994</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83319845999999997</v>
+        <v>0.83289773999999994</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79596054000000005</v>
+        <v>0.79567325999999994</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12652,16 +12652,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1152.3668640369121</v>
+        <v>1151.9509490058722</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1152.3668640369121</v>
+        <v>1151.9509490058722</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1100.8644343592848</v>
+        <v>1100.4671077095206</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12707,16 +12707,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.2110833820502434</v>
+        <v>4.2095715489469994</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.367347983203985</v>
+        <v>3.3661394875459969</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3361636226501781</v>
+        <v>3.334966933125187</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12762,16 +12762,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.8429064516129031E-2</v>
+        <v>5.8407976157082743E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.8429064516129031E-2</v>
+        <v>5.8407976157082743E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.5817709677419357E-2</v>
+        <v>5.5797563814866759E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -12899,26 +12899,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265509823772861</v>
+        <v>-0.16265533082700578</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.101155896013962E-2</v>
+        <v>-2.1011517834260696E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815593194776841</v>
+        <v>0.73815611010746318</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3498066117478089</v>
+        <v>-6.3497797544536185</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.8281697302732316</v>
+        <v>-0.82816913818144844</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13510,19 +13510,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.04102992436358</v>
+        <v>165.04136605874592</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88901663055111</v>
+        <v>161.88937617440629</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.4003586667779</v>
+        <v>117.40058250304281</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5916.8684897219155</v>
+        <v>-5916.7016363844523</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13618,24 +13618,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373151663925395</v>
+        <v>0.11373132241751507</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582397934219845</v>
+        <v>0.13582378512045959</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520506989175887</v>
+        <v>0.13520487087527092</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9472501387887699E-2</v>
+        <v>9.9472344772478447E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6495601765073741E-2</v>
+        <v>-2.6495693063470247E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13904,30 +13904,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5349661230614118</v>
+        <v>1.53440918829132</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9195730186114348</v>
+        <v>1.9188762935617167</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8509230876274363</v>
+        <v>1.8502509387232873</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3268087594765656</v>
+        <v>1.3263273556713127</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.6697216891245832E-2</v>
+        <v>-3.668500654570736E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2183209011870488</v>
+        <v>-1.2178811818656701</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13961,30 +13961,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10764138310388582</v>
+        <v>0.1076023273696578</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1346124136473657</v>
+        <v>0.13456355494822697</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12979825298930128</v>
+        <v>0.12975111772253067</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.3044092529913441E-2</v>
+        <v>9.3010333497287004E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.5734373696525829E-3</v>
+        <v>-2.5725811041870518E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.5436248330087575E-2</v>
+        <v>-8.5405412473048392E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.65092530555904</v>
+        <v>273.65040256745999</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14836,7 +14836,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6365663194879</v>
+        <v>3420.6300320932496</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.31267702560837</v>
+        <v>327.34733661152836</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.9492433450962</v>
+        <v>1424.977368704778</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7579000000000002</v>
+        <v>7.7550999999999997</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>7.9928427545948519</v>
+        <v>7.9901156626611796</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.695208866956804</v>
+        <v>16.689324278452212</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.0841307321914</v>
+        <v>304.08354985945994</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15030,7 +15030,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.5593803075846</v>
+        <v>281.55884246246285</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90186698584517</v>
+        <v>337.90122151322555</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.69638801941454</v>
+        <v>289.69583463068034</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.48053375095964</v>
+        <v>375.47981649418358</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.06855356697372</v>
+        <v>298.06798418541979</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.23839078939289</v>
+        <v>417.2375937652169</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68267296295653</v>
+        <v>306.68208712639375</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.64021327397836</v>
+        <v>463.63932761132821</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15118,7 +15118,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.54573862341528</v>
+        <v>315.54513585629735</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.2024648499937</v>
+        <v>515.20148069122718</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.6649450437763</v>
+        <v>324.66432485681361</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.49904600198397</v>
+        <v>572.49795239317314</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.04769463889221</v>
+        <v>334.04705652865488</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.1676817066683</v>
+        <v>636.16646647567927</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70160375186964</v>
+        <v>343.70094720037878</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15194,7 +15194,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.91701946807154</v>
+        <v>706.9156690890859</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.6345088365523</v>
+        <v>353.63383331085953</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.53451673774885</v>
+        <v>785.53301618071782</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.85447281867465</v>
+        <v>363.85377777042942</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.0516341523926</v>
+        <v>3801.0443732432491</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6223648130358</v>
+        <v>1760.619001607203</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15701,7 +15701,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.0783233831462</v>
+        <v>4972.0688255355935</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15722,7 +15722,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.0783233831462</v>
+        <v>4972.0688255355935</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15752,19 +15752,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.6365663194874</v>
+        <v>3420.6300320932492</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.0042080640196</v>
+        <v>3530.9974630094384</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.8009340581302</v>
+        <v>3761.7937481271238</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.674958878918</v>
+        <v>4335.6666767125644</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.0584592712003</v>
+        <v>5077.048760886717</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15773,19 +15773,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.6365663194865</v>
+        <v>3420.6300320932487</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.4734809657621</v>
+        <v>3641.4665248886977</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.1977603875421</v>
+        <v>4152.1898287061076</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.7579563160789</v>
+        <v>5750.7469710059477</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.3988127527537</v>
+        <v>8648.3822922620948</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15794,19 +15794,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6365663194865</v>
+        <v>3420.6300320932482</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.2098364407966</v>
+        <v>3778.2026191648984</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.2036569593356</v>
+        <v>4689.1946994694144</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.4718615673955</v>
+        <v>8276.4560515453286</v>
       </c>
       <c r="F58" s="124">
-        <v>17363.949550869431</v>
+        <v>17363.916381612024</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15815,19 +15815,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6365663194856</v>
+        <v>3420.6300320932482</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.522254596418</v>
+        <v>3917.5147712007956</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.7814191996249</v>
+        <v>5301.7712915410502</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.511118532821</v>
+        <v>12134.487938741748</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.3050250874</v>
+        <v>36349.235589303142</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15836,19 +15836,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6365663194852</v>
+        <v>3420.6300320932482</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.0905339285673</v>
+        <v>4047.0828030268344</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.7442886631488</v>
+        <v>5943.7329347034029</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.406775163352</v>
+        <v>17688.372986115777</v>
       </c>
       <c r="F60" s="124">
-        <v>76382.624695481587</v>
+        <v>76382.47878657229</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15857,19 +15857,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6365663194852</v>
+        <v>3420.6300320932478</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.3877803069736</v>
+        <v>4161.3798310704215</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.6255772118038</v>
+        <v>6585.6129971067257</v>
       </c>
       <c r="E61" s="124">
-        <v>25476.667031359368</v>
+        <v>25476.618364889546</v>
       </c>
       <c r="F61" s="124">
-        <v>159940.00531395525</v>
+        <v>159939.6997906531</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15919,23 +15919,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9928427545948519</v>
+        <v>7.9901156626611796</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9928427545948519</v>
+        <v>7.9901156626611796</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9928427545948519</v>
+        <v>7.9901156626611796</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9928427545948519</v>
+        <v>7.9901156626611796</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9928427545948519</v>
+        <v>7.9901156626611796</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15946,23 +15946,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>7.9928427545948484</v>
+        <v>7.9901156626611778</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6119182829193797</v>
+        <v>8.6089665705971203</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9065061061429756</v>
+        <v>9.9030846759807893</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.1254873174114</v>
+        <v>13.12089793798056</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.284064731422148</v>
+        <v>17.277966487188895</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15973,23 +15973,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>7.9928427545948448</v>
+        <v>7.9901156626611751</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2315638819761414</v>
+        <v>9.2283873424254068</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.096324767626463</v>
+        <v>12.092108801262826</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.062988204575827</v>
+        <v>21.055518846124418</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.316470799098582</v>
+        <v>37.303104157667462</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16000,23 +16000,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>7.9928427545948448</v>
+        <v>7.9901156626611733</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>9.9985471224336777</v>
+        <v>9.9950922968489575</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.108504822203381</v>
+        <v>15.103195940640534</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.230253587570509</v>
+        <v>35.217643892423489</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.203844784382937</v>
+        <v>86.172740241129858</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16027,23 +16027,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>7.9928427545948395</v>
+        <v>7.9901156626611733</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.779980045241706</v>
+        <v>10.7762416908164</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.544583511612846</v>
+        <v>18.538027910877407</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>56.870814657373131</v>
+        <v>56.850353074993556</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>192.6967333235437</v>
+        <v>192.6269897565989</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16054,23 +16054,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>7.992842754594836</v>
+        <v>7.9901156626611733</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.506756025173566</v>
+        <v>11.502753973193494</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.145489504492332</v>
+        <v>22.137627379970379</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.023794222220971</v>
+        <v>87.992029343142534</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>417.25212051665545</v>
+        <v>417.10090107798914</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16080,23 +16080,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>7.992842754594836</v>
+        <v>7.9901156626611716</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.147873539956889</v>
+        <v>12.143638870051035</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.745937892704589</v>
+        <v>25.736769410429723</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>131.70979907492818</v>
+        <v>131.66218351699538</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>885.94320364707971</v>
+        <v>885.62192810313172</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.203844784382937</v>
+        <v>86.172740241129858</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.062988204575827</v>
+        <v>21.055518846124418</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.096324767626463</v>
+        <v>12.092108801262826</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2315638819761414</v>
+        <v>9.2283873424254068</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.9928427545948448</v>
+        <v>7.9901156626611733</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16343,7 +16343,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83319845999999997</v>
+        <v>0.83289773999999994</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83319845999999997</v>
+        <v>0.83289773999999994</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.528067587046532</v>
+        <v>17.521882401810444</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.21793226741335</v>
+        <v>342.21723528328124</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.65092530555904</v>
+        <v>273.65040256745999</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7398757115330907</v>
+        <v>-4.7398380179279727</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9928427545948519</v>
+        <v>7.9901156626611796</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16625,7 +16625,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.096324767626463</v>
+        <v>12.092108801262826</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16683,7 +16683,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2315638819761414</v>
+        <v>9.2283873424254068</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.062988204575827</v>
+        <v>21.055518846124418</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.316705277886271</v>
+        <v>13.31204651846766</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>7.9928427545948448</v>
+        <v>7.9901156626611733</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.203844784382937</v>
+        <v>86.172740241129858</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.694869127046534</v>
+        <v>16.688984661810444</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16988,7 +16988,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.695208866956804</v>
+        <v>16.689324278452212</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67051940919606068</v>
+        <v>-0.6705020957078649</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83319845999999997</v>
+        <v>0.83289773999999994</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6264033939199998</v>
+        <v>1.5126363143377335</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17123,7 +17123,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.5477729930478255</v>
+        <v>7.5962606562632864</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>10.174176386967826</v>
+        <v>9.1088969706010197</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17144,7 +17144,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.3905806442959685</v>
+        <v>0.45419705541194533</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10954171828338932</v>
+        <v>0.10940387682956731</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17200,7 +17200,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7551171263888887</v>
+        <v>1.7544836652777773</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>9.6613825966704479</v>
+        <v>9.6579772348440081</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>11.416499723059337</v>
+        <v>11.412460900121786</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31616716272641943</v>
+        <v>0.31616805147906779</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.1472332410455732</v>
+        <v>2.1464582564395682</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>13.252925372661792</v>
+        <v>13.248254094436222</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>15.400158613707365</v>
+        <v>15.394712350875789</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.755140237917002E-2</v>
+        <v>7.7552489690780879E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35268AD-E957-44ED-AE75-8B3E2990D077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60063429-0D0E-4028-9AC6-4A538488FF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2302,10 +2302,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Result (Sell)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2338,9 +2334,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
     <t>Target Return</t>
   </si>
   <si>
@@ -2351,6 +2344,15 @@
   </si>
   <si>
     <t>@ Position Yield</t>
+  </si>
+  <si>
+    <t>Result (Target)</t>
+  </si>
+  <si>
+    <t>Base Equity Return</t>
+  </si>
+  <si>
+    <t>Entry Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -3749,29 +3751,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4061,7 +4063,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4084,7 +4086,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4116,10 +4118,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4182,13 +4184,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4212,7 +4214,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4222,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7550999999999997</v>
+        <v>7.7549000000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4235,7 +4237,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4247,7 +4249,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4260,7 +4262,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>9.1088969706010197</v>
+        <v>9.1086666437717536</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4275,7 +4277,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10940387682956731</v>
+        <v>0.10939402978090751</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4295,22 +4297,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4322,13 +4324,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4348,13 +4350,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4383,13 +4385,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4405,13 +4407,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4419,7 +4421,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.017235283281404</v>
+        <v>7.0171854987005426</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4449,7 +4451,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.98276471671861</v>
+        <v>-144.98281450129946</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4475,13 +4477,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4489,7 +4491,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03405590687365</v>
+        <v>-102.03404346072844</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4497,7 +4499,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4519,22 +4521,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4544,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.21723528328124</v>
+        <v>342.21718549870042</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4555,7 +4557,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.65040256745999</v>
+        <v>273.65036522902437</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4568,7 +4570,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.1076023273696578</v>
+        <v>0.10759953768003538</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4577,7 +4579,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.8407976157082743E-2</v>
+        <v>5.8406469845722293E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4595,22 +4597,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4634,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4646,7 +4648,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4668,22 +4670,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4699,7 +4701,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.180114853641498</v>
+        <v>19.179617591466304</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4720,13 +4722,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4739,13 +4741,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4766,7 +4768,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.025497170690391</v>
+        <v>13.025161249885484</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4775,7 +4777,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4784,7 +4786,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4793,7 +4795,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4824,7 +4826,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.34733661152836</v>
+        <v>327.34981229623696</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4837,7 +4839,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8354979797100719</v>
+        <v>1.8354645244417702</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,13 +4878,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4890,7 +4892,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9901156626611796</v>
+        <v>7.9899208660225911</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4899,11 +4901,11 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-12.129692853863228</v>
+        <v>-12.129380035386257</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4921,13 +4923,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4983,7 +4985,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>21.06 HKD</v>
+        <v>21.05 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5062,7 +5064,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>16.688984661810444</v>
+        <v>16.688564338966547</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5070,17 +5072,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5089,22 +5091,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5135,228 +5137,293 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83289773999999994</v>
+        <v>0.83287625999999992</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>1.5126363143377335</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>1.5125973042330454</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>7.5962606562632864</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>7.5960693395387082</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>9.1088969706010197</v>
+        <v>9.1086666437717536</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="2:4">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.45419705541194533</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>0.45419711014303965</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C136" s="92">
-        <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>420</v>
+      </c>
+      <c r="C136" s="337">
+        <f>Scenarios!C90</f>
+        <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C97</f>
-        <v>2.1464582564395682</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <f>Scenarios!C91</f>
+        <v>1.7544384180555554</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C98</f>
-        <v>13.248254094436222</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+        <f>Scenarios!C92</f>
+        <v>9.6577339924574925</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
       <c r="B139" s="80" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C99</f>
-        <v>15.394712350875789</v>
-      </c>
-      <c r="D139" s="101" t="str">
+        <f>Scenarios!C93</f>
+        <v>11.412172410513048</v>
+      </c>
+      <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="2:4">
       <c r="B140" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C140" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.31616811496082498</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="234" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" s="92">
+        <f>Scenarios!C96</f>
+        <v>0.08</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C143" s="240">
+        <f>Scenarios!C97</f>
+        <v>2.1464029003962817</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C144" s="240">
+        <f>Scenarios!C98</f>
+        <v>13.247920428611099</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="239">
+        <f>Scenarios!C99</f>
+        <v>15.394323329007381</v>
+      </c>
+      <c r="D145" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="B146" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7552489690780879E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9">
-      <c r="A142" s="247" t="s">
+        <v>7.7552567355192448E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="13.9">
+      <c r="A148" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B142" s="36"/>
-      <c r="C142" s="36"/>
-      <c r="D142" s="36"/>
-      <c r="E142" s="36"/>
-      <c r="F142" s="36"/>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="36"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="234" t="s">
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="344" t="s">
+    <row r="153" spans="1:6">
+      <c r="B153" s="344" t="s">
         <v>388</v>
       </c>
-      <c r="C147" s="344"/>
-      <c r="D147" s="344"/>
-      <c r="E147" s="344"/>
-      <c r="F147" s="344"/>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="238" t="s">
+      <c r="C153" s="344"/>
+      <c r="D153" s="344"/>
+      <c r="E153" s="344"/>
+      <c r="F153" s="344"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="B154" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="238" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="238" t="s">
+    <row r="156" spans="1:6">
+      <c r="B156" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="1" t="s">
+    <row r="158" spans="1:6">
+      <c r="B158" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+    <row r="159" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="1" t="s">
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+    <row r="162" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
+    </row>
+    <row r="163" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="1" t="s">
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="238" t="s">
+    <row r="166" spans="2:6">
+      <c r="B166" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="238" t="s">
+    <row r="167" spans="2:6">
+      <c r="B167" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="238" t="s">
+    <row r="168" spans="2:6">
+      <c r="B168" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5373,20 +5440,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5932,11 +5988,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83289773999999994</v>
+        <v>0.83287625999999992</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79567325999999994</v>
+        <v>0.79565273999999997</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -5959,7 +6015,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7267,11 +7323,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83289773999999994</v>
+        <v>0.83287625999999992</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79567325999999994</v>
+        <v>0.79565273999999997</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8591,7 +8647,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8618,11 +8674,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.277330573987582</v>
+        <v>8.277117105932394</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.129692853863228</v>
+        <v>-12.129380035386257</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8813,7 +8869,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.34733661152836</v>
+        <v>327.34981229623696</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8880,11 +8936,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.34591241715606</v>
+        <v>-342.3434367324474</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-348.95266338847159</v>
+        <v>-348.95018770376299</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -8896,11 +8952,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9754872936117125</v>
+        <v>1.9755015795104918</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9380852217399724</v>
+        <v>1.9380989718055019</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -8913,7 +8969,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>348.95266338847159</v>
+        <v>348.95018770376299</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9028,11 +9084,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18015.097299999998</v>
+        <v>-18014.632700000002</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-13.025497170690388</v>
+        <v>-13.025161249885485</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9045,11 +9101,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2538.6113301560636</v>
+        <v>2538.5650593760879</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8354979797100721</v>
+        <v>1.83546452444177</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9079,11 +9135,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15476.485969843934</v>
+        <v>-15476.067640623914</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.189999190980316</v>
+        <v>-11.189696725443715</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9663,24 +9719,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.98276471671861</v>
+        <v>-144.98281450129946</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.98276471671861</v>
+        <v>-144.98281450129946</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.62158348890264</v>
+        <v>-165.62163583592516</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75943599317085</v>
+        <v>-133.7594682067232</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.14249654266081</v>
+        <v>-167.1425097209322</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9718,24 +9774,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.13622362749459</v>
+        <v>408.13617384291376</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.41723528328123</v>
+        <v>487.41718549870041</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.87841651109761</v>
+        <v>497.87836416407504</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44056400682894</v>
+        <v>286.44053179327659</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.542496542660672</v>
+        <v>-53.54250972093206</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9773,7 +9829,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03405590687365</v>
+        <v>-102.03404346072844</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9885,26 +9941,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.65040256745999</v>
+        <v>273.65036522902437</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.21723528328124</v>
+        <v>342.21718549870042</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.97841651109758</v>
+        <v>329.978364164075</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54056400682893</v>
+        <v>236.54053179327659</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5424965426606683</v>
+        <v>-6.5425097209320562</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -9993,26 +10049,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.65040256745999</v>
+        <v>273.65036522902437</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.21723528328124</v>
+        <v>342.21718549870042</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.97841651109758</v>
+        <v>329.978364164075</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54056400682893</v>
+        <v>236.54053179327659</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5424965426606683</v>
+        <v>-6.5425097209320562</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10854,19 +10910,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270787209903527</v>
+        <v>0.24270789688911248</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27034712800609983</v>
+        <v>0.27034715643044649</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4834353277633792E-2</v>
+        <v>8.4834362818238473E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496335365165861</v>
+        <v>1.0496332781731563</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -10992,24 +11048,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.017235283281404</v>
+        <v>7.0171854987005426</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.017235283281404</v>
+        <v>7.0171854987005418</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.3784165110973587</v>
+        <v>7.378364164074835</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5405640068291442</v>
+        <v>4.5405317932768217</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8575034573391951</v>
+        <v>1.8574902790677907</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11104,24 +11160,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.98276471671861</v>
+        <v>-144.98281450129946</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.98276471671861</v>
+        <v>-144.98281450129946</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.62158348890264</v>
+        <v>-165.62163583592516</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75943599317085</v>
+        <v>-133.7594682067232</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.14249654266081</v>
+        <v>-167.1425097209322</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -11747,7 +11803,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12079,7 +12135,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12191,26 +12247,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0400926466231571E-2</v>
+        <v>4.0400940339212911E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0400926466231571E-2</v>
+        <v>4.0400940339212911E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4976532557273151E-2</v>
+        <v>4.4976546772736575E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.645070009486417E-2</v>
+        <v>4.6450711281679123E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2711053316835315E-2</v>
+        <v>8.2711059838149345E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12248,26 +12304,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373132241751507</v>
+        <v>0.11373130854453374</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582378512045959</v>
+        <v>0.13582377124747824</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520487087527092</v>
+        <v>0.13520485665980747</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9472344772478447E-2</v>
+        <v>9.94723335856635E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6495693063470247E-2</v>
+        <v>-2.6495699584784274E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12305,7 +12361,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8432830604378768E-2</v>
+        <v>2.8432827136133435E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12420,26 +12476,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6255476388413304E-2</v>
+        <v>7.6255465983677301E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5362323826361603E-2</v>
+        <v>9.536230995338027E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9609606916982831E-2</v>
+        <v>8.9609592701519386E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2143549106413721E-2</v>
+        <v>8.2143537919598761E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2375774656871873E-3</v>
+        <v>3.2375839870012156E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12527,26 +12583,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6255476388413304E-2</v>
+        <v>7.6255465983677301E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5362323826361603E-2</v>
+        <v>9.536230995338027E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9609606916982831E-2</v>
+        <v>8.9609592701519386E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2143549106413721E-2</v>
+        <v>8.2143537919598761E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2375774656871873E-3</v>
+        <v>3.2375839870012156E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12596,16 +12652,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83289773999999994</v>
+        <v>0.83287625999999992</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83289773999999994</v>
+        <v>0.83287625999999992</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79567325999999994</v>
+        <v>0.79565273999999997</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12652,16 +12708,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1151.9509490058722</v>
+        <v>1151.9212407893697</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1151.9509490058722</v>
+        <v>1151.9212407893697</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1100.4671077095206</v>
+        <v>1100.4387272345373</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12707,16 +12763,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.2095715489469994</v>
+        <v>4.209463560647178</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.3661394875459969</v>
+        <v>3.3660531662392037</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.334966933125187</v>
+        <v>3.3348814550985733</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12762,16 +12818,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.8407976157082743E-2</v>
+        <v>5.8406469845722293E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.8407976157082743E-2</v>
+        <v>5.8406469845722293E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.5797563814866759E-2</v>
+        <v>5.5796124824684427E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -12899,26 +12955,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265533082700578</v>
+        <v>-0.1626553474405511</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1011517834260696E-2</v>
+        <v>-2.1011514896693062E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815611010746318</v>
+        <v>0.738156122833177</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3497797544536185</v>
+        <v>-6.3497778360825459</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82816913818144844</v>
+        <v>-0.8281690958891782</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13510,19 +13566,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.04136605874592</v>
+        <v>165.04139006839702</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88937617440629</v>
+        <v>161.88940185617139</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.40058250304281</v>
+        <v>117.40059849138012</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5916.7016363844523</v>
+        <v>-5916.6897186490251</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13618,24 +13674,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373132241751507</v>
+        <v>0.11373130854453374</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582378512045959</v>
+        <v>0.13582377124747824</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520487087527092</v>
+        <v>0.13520485665980747</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9472344772478447E-2</v>
+        <v>9.94723335856635E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6495693063470247E-2</v>
+        <v>-2.6495699584784274E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13904,30 +13960,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.53440918829132</v>
+        <v>1.5343694073173044</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9188762935617167</v>
+        <v>1.9188265275947247</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8502509387232873</v>
+        <v>1.8502029282008225</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3263273556713127</v>
+        <v>1.3262929697550976</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.668500654570736E-2</v>
+        <v>-3.6684134349583855E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2178811818656701</v>
+        <v>-1.2178497733427145</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13961,30 +14017,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1076023273696578</v>
+        <v>0.10759953768003538</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13456355494822697</v>
+        <v>0.13456006504871842</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12975111772253067</v>
+        <v>0.12974775092572388</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.3010333497287004E-2</v>
+        <v>9.3007922142713723E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.5725811041870518E-3</v>
+        <v>-2.5725199403635241E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.5405412473048392E-2</v>
+        <v>-8.5403209911831313E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14804,7 +14860,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.65040256745999</v>
+        <v>273.65036522902437</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14836,7 +14892,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6300320932496</v>
+        <v>3420.6295653628044</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14870,7 +14926,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.34733661152836</v>
+        <v>327.34981229623696</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14902,7 +14958,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.977368704778</v>
+        <v>1424.9793776590413</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14916,7 +14972,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7550999999999997</v>
+        <v>7.7549000000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14930,7 +14986,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>7.9901156626611796</v>
+        <v>7.9899208660225911</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14983,7 +15039,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.689324278452212</v>
+        <v>16.688903946803435</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15018,7 +15074,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.08354985945994</v>
+        <v>304.08350836855055</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15030,7 +15086,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.55884246246285</v>
+        <v>281.55880404495417</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15040,7 +15096,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90122151322555</v>
+        <v>337.90117540803845</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15052,7 +15108,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.69583463068034</v>
+        <v>289.69579510291362</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15062,7 +15118,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.47981649418358</v>
+        <v>375.47976526155674</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15074,7 +15130,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.06798418541979</v>
+        <v>298.0679435153088</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15084,7 +15140,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.2375937652169</v>
+        <v>417.23753683491861</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15096,7 +15152,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68208712639375</v>
+        <v>306.68204528092497</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15106,7 +15162,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.63932761132821</v>
+        <v>463.63926434971034</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15118,7 +15174,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.54513585629735</v>
+        <v>315.54509280150324</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15128,7 +15184,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.20148069122718</v>
+        <v>515.20141039417251</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15140,7 +15196,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.66432485681361</v>
+        <v>324.66428055774492</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15150,7 +15206,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.49795239317314</v>
+        <v>572.49787427825811</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15162,7 +15218,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.04705652865488</v>
+        <v>334.04701094935223</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15172,7 +15228,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.16646647567927</v>
+        <v>636.16637967346583</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15184,7 +15240,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70094720037878</v>
+        <v>343.70090030384375</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15194,7 +15250,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.9156690890859</v>
+        <v>706.91557263344407</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15206,7 +15262,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.63383331085953</v>
+        <v>353.63378505902432</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15216,7 +15272,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.53301618071782</v>
+        <v>785.5329089980728</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15228,7 +15284,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.85377777042942</v>
+        <v>363.85372812412618</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15678,7 +15734,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.0443732432491</v>
+        <v>3801.0438546068817</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15690,7 +15746,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.619001607203</v>
+        <v>1760.6187613782149</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15701,7 +15757,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.0688255355935</v>
+        <v>4972.0681471179105</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15722,7 +15778,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.0688255355935</v>
+        <v>4972.0681471179105</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15752,19 +15808,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.6300320932492</v>
+        <v>3420.629565362804</v>
       </c>
       <c r="C56" s="124">
-        <v>3530.9974630094384</v>
+        <v>3530.9969812198256</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.7937481271238</v>
+        <v>3761.7932348463373</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.6666767125644</v>
+        <v>4335.6660851292536</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.048760886717</v>
+        <v>5077.0480681449699</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15773,19 +15829,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.6300320932487</v>
+        <v>3420.6295653628031</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.4665248886977</v>
+        <v>3641.4660280260505</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.1898287061076</v>
+        <v>4152.1892621574334</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.7469710059477</v>
+        <v>5750.746186340938</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.3822922620948</v>
+        <v>8648.381112227049</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15794,19 +15850,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6300320932482</v>
+        <v>3420.6295653628031</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.2026191648984</v>
+        <v>3778.2021036451924</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.1946994694144</v>
+        <v>4689.1940596487048</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.4560515453286</v>
+        <v>8276.454922258039</v>
       </c>
       <c r="F58" s="124">
-        <v>17363.916381612024</v>
+        <v>17363.914012379355</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15815,19 +15871,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6300320932482</v>
+        <v>3420.6295653628031</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.5147712007956</v>
+        <v>3917.5142366725368</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.7712915410502</v>
+        <v>5301.7705681368643</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.487938741748</v>
+        <v>12134.48628304239</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.235589303142</v>
+        <v>36349.230629604273</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15836,19 +15892,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6300320932482</v>
+        <v>3420.6295653628031</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.0828030268344</v>
+        <v>4047.0822508195679</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.7329347034029</v>
+        <v>5943.732123706277</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.372986115777</v>
+        <v>17688.370572612384</v>
       </c>
       <c r="F60" s="124">
-        <v>76382.47878657229</v>
+        <v>76382.468364507353</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15857,19 +15913,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6300320932478</v>
+        <v>3420.6295653628031</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.3798310704215</v>
+        <v>4161.3792632678096</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.6129971067257</v>
+        <v>6585.6120985277894</v>
       </c>
       <c r="E61" s="124">
-        <v>25476.618364889546</v>
+        <v>25476.614888713142</v>
       </c>
       <c r="F61" s="124">
-        <v>159939.6997906531</v>
+        <v>159939.67796756013</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15919,23 +15975,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9901156626611796</v>
+        <v>7.9899208660225911</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9901156626611796</v>
+        <v>7.9899208660225911</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9901156626611796</v>
+        <v>7.9899208660225911</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9901156626611796</v>
+        <v>7.9899208660225911</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9901156626611796</v>
+        <v>7.9899208660225911</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15946,23 +16002,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>7.9901156626611778</v>
+        <v>7.9899208660225876</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6089665705971203</v>
+        <v>8.6087557296777195</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9030846759807893</v>
+        <v>9.902840283855415</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.12089793798056</v>
+        <v>13.120570121077273</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.277966487188895</v>
+        <v>17.277530894447729</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15973,23 +16029,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>7.9901156626611751</v>
+        <v>7.989920866022584</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2283873424254068</v>
+        <v>9.2281604424509567</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.092108801262826</v>
+        <v>12.091807656667177</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.055518846124418</v>
+        <v>21.054985316852761</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.303104157667462</v>
+        <v>37.302149394754856</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16000,23 +16056,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>7.9901156626611733</v>
+        <v>7.989920866022584</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>9.9950922968489575</v>
+        <v>9.9948455193411245</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.103195940640534</v>
+        <v>15.102816730832442</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.217643892423489</v>
+        <v>35.216743196992525</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.172740241129858</v>
+        <v>86.170518487809474</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16027,23 +16083,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>7.9901156626611733</v>
+        <v>7.989920866022584</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.7762416908164</v>
+        <v>10.77597466128975</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.538027910877407</v>
+        <v>18.537559649881139</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>56.850353074993556</v>
+        <v>56.848891531616417</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>192.6269897565989</v>
+        <v>192.6220080786338</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16054,23 +16110,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>7.9901156626611733</v>
+        <v>7.989920866022584</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.502753973193494</v>
+        <v>11.502468108165566</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.137627379970379</v>
+        <v>22.137065796036506</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>87.992029343142534</v>
+        <v>87.98976042307352</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>417.10090107798914</v>
+        <v>417.09009970674953</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16080,23 +16136,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>7.9901156626611716</v>
+        <v>7.989920866022584</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.143638870051035</v>
+        <v>12.1433363894908</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.736769410429723</v>
+        <v>25.736114515417757</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>131.66218351699538</v>
+        <v>131.65878240788473</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>885.62192810313172</v>
+        <v>885.5989798919594</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16131,7 +16187,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.172740241129858</v>
+        <v>86.170518487809474</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16153,7 +16209,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.055518846124418</v>
+        <v>21.054985316852761</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16176,7 +16232,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.092108801262826</v>
+        <v>12.091807656667177</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16199,7 +16255,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2283873424254068</v>
+        <v>9.2281604424509567</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16222,7 +16278,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.9901156626611733</v>
+        <v>7.989920866022584</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16343,7 +16399,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83289773999999994</v>
+        <v>0.83287625999999992</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16352,7 +16408,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83289773999999994</v>
+        <v>0.83287625999999992</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16372,7 +16428,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.521882401810444</v>
+        <v>17.521440598966546</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16406,7 +16462,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.21723528328124</v>
+        <v>342.21718549870042</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16428,7 +16484,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.65040256745999</v>
+        <v>273.65036522902437</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16512,7 +16568,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7398380179279727</v>
+        <v>-4.7398353255798833</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16578,7 +16634,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9901156626611796</v>
+        <v>7.9899208660225911</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16625,7 +16681,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.092108801262826</v>
+        <v>12.091807656667177</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16683,7 +16739,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2283873424254068</v>
+        <v>9.2281604424509567</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16741,7 +16797,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.055518846124418</v>
+        <v>21.054985316852761</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16768,7 +16824,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.31204651846766</v>
+        <v>13.311713745861049</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16842,7 +16898,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>7.9901156626611733</v>
+        <v>7.989920866022584</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16900,7 +16956,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.172740241129858</v>
+        <v>86.170518487809474</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16926,7 +16982,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.688984661810444</v>
+        <v>16.688564338966547</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16988,7 +17044,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.689324278452212</v>
+        <v>16.688903946803435</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17051,7 +17107,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.6705020957078649</v>
+        <v>-0.67050085904133838</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17084,7 +17140,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83289773999999994</v>
+        <v>0.83287625999999992</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17111,7 +17167,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.5126363143377335</v>
+        <v>1.5125973042330454</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17123,7 +17179,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>7.5962606562632864</v>
+        <v>7.5960693395387082</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17133,7 +17189,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.1088969706010197</v>
+        <v>9.1086666437717536</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17144,7 +17200,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.45419705541194533</v>
+        <v>0.45419711014303965</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17174,7 +17230,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10940387682956731</v>
+        <v>0.10939402978090751</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17182,12 +17238,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17200,7 +17256,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7544836652777773</v>
+        <v>1.7544384180555554</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17212,7 +17268,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>9.6579772348440081</v>
+        <v>9.6577339924574925</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17222,7 +17278,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>11.412460900121786</v>
+        <v>11.412172410513048</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17233,7 +17289,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31616805147906779</v>
+        <v>0.31616811496082498</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17245,7 +17301,7 @@
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>
@@ -17260,7 +17316,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.1464582564395682</v>
+        <v>2.1464029003962817</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17272,7 +17328,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>13.248254094436222</v>
+        <v>13.247920428611099</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17284,7 +17340,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>15.394712350875789</v>
+        <v>15.394323329007381</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17294,7 +17350,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.7552489690780879E-2</v>
+        <v>7.7552567355192448E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60063429-0D0E-4028-9AC6-4A538488FF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0061DB6C-FBC2-4AB6-BFCB-81520E1E4732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3751,29 +3751,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4129,7 +4129,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>14.26</v>
+        <v>14.64</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>19722.493823579996</v>
+        <v>20248.058175120001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4184,13 +4184,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10939402978090751</v>
+        <v>9.919795200818049E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4297,22 +4297,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4324,13 +4324,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4350,13 +4350,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4385,13 +4385,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4407,13 +4407,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4477,13 +4477,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4499,7 +4499,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4521,22 +4521,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10759953768003538</v>
+        <v>0.10480665350528036</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.8406469845722293E-2</v>
+        <v>5.6890454918032782E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4597,22 +4597,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4670,22 +4670,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4722,13 +4722,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4741,13 +4741,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4878,13 +4878,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4923,13 +4923,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5072,13 +5072,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5091,22 +5091,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5317,13 +5317,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5360,13 +5360,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5374,22 +5374,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5413,17 +5413,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5440,6 +5429,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12818,16 +12818,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.8406469845722293E-2</v>
+        <v>5.6890454918032782E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.8406469845722293E-2</v>
+        <v>5.6890454918032782E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.5796124824684427E-2</v>
+        <v>5.4347864754098356E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14017,30 +14017,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10759953768003538</v>
+        <v>0.10480665350528036</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13456006504871842</v>
+        <v>0.13106738576466698</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12974775092572388</v>
+        <v>0.1263799814344824</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.3007922142713723E-2</v>
+        <v>9.0593782087096827E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.5725199403635241E-3</v>
+        <v>-2.5057468818021757E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.5403209911831313E-2</v>
+        <v>-8.3186459927781037E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14074,23 +14074,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8892134196260898E-2</v>
+        <v>1.8401764592806038E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2831798251680843E-2</v>
+        <v>2.223916960853612E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7153003216841281E-2</v>
+        <v>1.6707774991267531E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1915328867743722E-3</v>
+        <v>1.1606051205876055E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.5306142900654951E-2</v>
+        <v>-6.3611038098588771E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.26</v>
+        <v>-14.64</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.26</v>
+        <v>14.64</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.26</v>
+        <v>14.64</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10939402978090751</v>
+        <v>9.919795200818049E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0061DB6C-FBC2-4AB6-BFCB-81520E1E4732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89460AEB-375A-4BEB-B46C-63B1E8C2F9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2340,12 +2340,6 @@
     <t>in contrast to a position yield of</t>
   </si>
   <si>
-    <t>Position Price Output</t>
-  </si>
-  <si>
-    <t>@ Position Yield</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2353,6 +2347,15 @@
   </si>
   <si>
     <t>Entry Yield</t>
+  </si>
+  <si>
+    <t>Result (Entry)</t>
+  </si>
+  <si>
+    <t>Entry Price Output</t>
+  </si>
+  <si>
+    <t>@ Entry Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -3751,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4086,7 +4089,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4118,10 +4121,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4184,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4214,7 +4217,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4237,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4297,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4324,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4350,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4385,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4407,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4477,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4499,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4521,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4597,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4636,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4648,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4670,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4722,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4741,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4878,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4923,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5072,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5091,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5146,7 +5149,7 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
@@ -5200,14 +5203,14 @@
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5261,7 +5264,7 @@
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5317,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5360,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5374,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5413,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5429,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6015,7 +6018,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11803,7 +11806,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12135,7 +12138,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17238,12 +17241,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89460AEB-375A-4BEB-B46C-63B1E8C2F9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D055E5-DC2F-4882-BE85-21F979211EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>14.64</v>
+        <v>14.82</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>20248.058175120001</v>
+        <v>20497.00971006</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4227,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7549000000000001</v>
+        <v>7.7589302062988281</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>9.1086666437717536</v>
+        <v>9.113307921310053</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.919795200818049E-2</v>
+        <v>9.4690284991131524E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0171854987005426</v>
+        <v>7.0181887093574025</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.98281450129946</v>
+        <v>-144.98181129064261</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03404346072844</v>
+        <v>-102.03429426339265</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.21718549870042</v>
+        <v>342.21818870935726</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.65036522902437</v>
+        <v>273.65111763701697</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10480665350528036</v>
+        <v>0.10358778927538839</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.6890454918032782E-2</v>
+        <v>5.6228684490991498E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.179617591466304</v>
+        <v>19.189637963265699</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.025161249885484</v>
+        <v>13.031930400604711</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.34981229623696</v>
+        <v>327.29992469570499</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8354645244417702</v>
+        <v>1.8361385444501035</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9899208660225911</v>
+        <v>7.993846107111092</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-12.129380035386257</v>
+        <v>-12.135683650367685</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.17 HKD</v>
+        <v>86.22 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>21.05 HKD</v>
+        <v>21.07 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>12.09 HKD</v>
+        <v>12.1 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>16.688564338966547</v>
+        <v>16.69703417753378</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83287625999999992</v>
+        <v>0.83330910415649406</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>1.5125973042330454</v>
+        <v>1.5133833980812073</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>7.5960693395387082</v>
+        <v>7.5999245232288466</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>9.1086666437717536</v>
+        <v>9.113307921310053</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.45419711014303965</v>
+        <v>0.45419600724227982</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.7544384180555554</v>
+        <v>1.7553501962555775</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>9.6577339924574925</v>
+        <v>9.6626355194061233</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>11.412172410513048</v>
+        <v>11.4179857156617</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31616811496082498</v>
+        <v>0.31616683572314619</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>2.1464029003962817</v>
+        <v>2.1475183817679309</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>13.247920428611099</v>
+        <v>13.254644059542004</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>15.394323329007381</v>
+        <v>15.402162441309935</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7552567355192448E-2</v>
+        <v>7.7551002319089846E-2</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83287625999999992</v>
+        <v>0.83330910415649406</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79565273999999997</v>
+        <v>0.79606623916625974</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -7326,11 +7326,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83287625999999992</v>
+        <v>0.83330910415649406</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79565273999999997</v>
+        <v>0.79606623916625974</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8677,11 +8677,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.277117105932394</v>
+        <v>8.2814187074355043</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.129380035386257</v>
+        <v>-12.135683650367685</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.34981229623696</v>
+        <v>327.29992469570499</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8939,11 +8939,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.3434367324474</v>
+        <v>-342.39332433297938</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-348.95018770376299</v>
+        <v>-349.00007530429497</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -8955,11 +8955,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9755015795104918</v>
+        <v>1.9752137437770092</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9380989718055019</v>
+        <v>1.9378219314432252</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -8972,7 +8972,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>348.95018770376299</v>
+        <v>349.00007530429497</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9087,11 +9087,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18014.632700000002</v>
+        <v>-18023.994869232178</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-13.025161249885485</v>
+        <v>-13.031930400604711</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9104,11 +9104,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2538.5650593760879</v>
+        <v>2539.497272240837</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.83546452444177</v>
+        <v>1.8361385444501035</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9138,11 +9138,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15476.067640623914</v>
+        <v>-15484.497596991341</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.189696725443715</v>
+        <v>-11.195791856154608</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9722,24 +9722,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.98281450129946</v>
+        <v>-144.98181129064261</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.98281450129946</v>
+        <v>-144.98181129064261</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.62163583592516</v>
+        <v>-165.62058098942566</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.7594682067232</v>
+        <v>-133.7588190704158</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.1425097209322</v>
+        <v>-167.1422441651701</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9777,24 +9777,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.13617384291376</v>
+        <v>408.13717705357061</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.41718549870041</v>
+        <v>487.41818870935725</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.87836416407504</v>
+        <v>497.87941901057457</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44053179327659</v>
+        <v>286.44118092958399</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.54250972093206</v>
+        <v>-53.542244165169961</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03404346072844</v>
+        <v>-102.03429426339265</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9944,26 +9944,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.65036522902437</v>
+        <v>273.65111763701697</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.21718549870042</v>
+        <v>342.21818870935726</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.978364164075</v>
+        <v>329.97941901057453</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54053179327659</v>
+        <v>236.54118092958399</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5425097209320562</v>
+        <v>-6.5422441651699579</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10052,26 +10052,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.65036522902437</v>
+        <v>273.65111763701697</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.21718549870042</v>
+        <v>342.21818870935726</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.978364164075</v>
+        <v>329.97941901057453</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54053179327659</v>
+        <v>236.54118092958399</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5425097209320562</v>
+        <v>-6.5422441651699579</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10913,19 +10913,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270789688911248</v>
+        <v>0.24270739734446214</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27034715643044649</v>
+        <v>0.27034658365169578</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4834362818238473E-2</v>
+        <v>8.4834170565627171E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496332781731563</v>
+        <v>1.0496384840842916</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11051,24 +11051,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0171854987005426</v>
+        <v>7.0181887093574025</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.0171854987005418</v>
+        <v>7.0181887093574025</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.378364164074835</v>
+        <v>7.3794190105743285</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5405317932768217</v>
+        <v>4.5411809295842023</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8574902790677907</v>
+        <v>1.8577558348299008</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11163,24 +11163,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.98281450129946</v>
+        <v>-144.98181129064261</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.98281450129946</v>
+        <v>-144.98181129064261</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.62163583592516</v>
+        <v>-165.62058098942566</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.7594682067232</v>
+        <v>-133.7588190704158</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.1425097209322</v>
+        <v>-167.1422441651701</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12250,26 +12250,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0400940339212911E-2</v>
+        <v>4.0400660784328878E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0400940339212911E-2</v>
+        <v>4.0400660784328878E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4976546772736575E-2</v>
+        <v>4.4976260316485349E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6450711281679123E-2</v>
+        <v>4.6450485855818797E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2711059838149345E-2</v>
+        <v>8.271092842694483E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12307,26 +12307,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373130854453374</v>
+        <v>0.11373158809941777</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582377124747824</v>
+        <v>0.13582405080236229</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520485665980747</v>
+        <v>0.13520514311605869</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.94723335856635E-2</v>
+        <v>9.9472559011523826E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6495699584784274E-2</v>
+        <v>-2.6495568173579752E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8432827136133435E-2</v>
+        <v>2.8432897024854444E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12479,26 +12479,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6255465983677301E-2</v>
+        <v>7.6255675649840315E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.536230995338027E-2</v>
+        <v>9.5362589508264303E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9609592701519386E-2</v>
+        <v>8.9609879157770619E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2143537919598761E-2</v>
+        <v>8.2143763345459087E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2375839870012156E-3</v>
+        <v>3.2374525757966933E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12586,26 +12586,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6255465983677301E-2</v>
+        <v>7.6255675649840315E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.536230995338027E-2</v>
+        <v>9.5362589508264303E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9609592701519386E-2</v>
+        <v>8.9609879157770619E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2143537919598761E-2</v>
+        <v>8.2143763345459087E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2375839870012156E-3</v>
+        <v>3.2374525757966933E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12655,16 +12655,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83287625999999992</v>
+        <v>0.83330910415649406</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83287625999999992</v>
+        <v>0.83330910415649406</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79565273999999997</v>
+        <v>0.79606623916625974</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12711,16 +12711,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1151.9212407893697</v>
+        <v>1152.5198919957531</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1151.9212407893697</v>
+        <v>1152.5198919957531</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1100.4387272345373</v>
+        <v>1101.0106230797417</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12766,16 +12766,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.209463560647178</v>
+        <v>4.2116396305916304</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.3660531662392037</v>
+        <v>3.367792624764832</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3348814550985733</v>
+        <v>3.3366039202719451</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12821,16 +12821,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.6890454918032782E-2</v>
+        <v>5.6228684490991498E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.6890454918032782E-2</v>
+        <v>5.6228684490991498E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.4347864754098356E-2</v>
+        <v>5.3715670658991882E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -12958,26 +12958,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.1626553474405511</v>
+        <v>-0.16265501266113225</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1011514896693062E-2</v>
+        <v>-2.1011574091587715E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.738156122833177</v>
+        <v>0.73815586639746655</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3497778360825459</v>
+        <v>-6.3498164934206907</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.8281690958891782</v>
+        <v>-0.82816994812204758</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13569,19 +13569,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.04139006839702</v>
+        <v>165.04090625050893</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88940185617139</v>
+        <v>161.88888434368721</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.40059849138012</v>
+        <v>117.40027631073195</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5916.6897186490251</v>
+        <v>-5916.9298825756023</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13677,24 +13677,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373130854453374</v>
+        <v>0.11373158809941777</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582377124747824</v>
+        <v>0.13582405080236229</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520485665980747</v>
+        <v>0.13520514311605869</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.94723335856635E-2</v>
+        <v>9.9472559011523826E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6495699584784274E-2</v>
+        <v>-2.6495568173579752E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13963,30 +13963,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5343694073173044</v>
+        <v>1.5351710370612559</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9188265275947247</v>
+        <v>1.9198293659411765</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8502029282008225</v>
+        <v>1.8511703926723144</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3262929697550976</v>
+        <v>1.3269858832333987</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.6684134349583855E-2</v>
+        <v>-3.6701709265715525E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2178497733427145</v>
+        <v>-1.2184826874779777</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14020,30 +14020,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10480665350528036</v>
+        <v>0.10358778927538839</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13106738576466698</v>
+        <v>0.12954314210129395</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1263799814344824</v>
+        <v>0.124910282906364</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.0593782087096827E-2</v>
+        <v>8.954020804543851E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.5057468818021757E-3</v>
+        <v>-2.476498600925474E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.3186459927781037E-2</v>
+        <v>-8.221880482307542E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14077,23 +14077,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8401764592806038E-2</v>
+        <v>1.8178261379128226E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.223916960853612E-2</v>
+        <v>2.1969058236772521E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6707774991267531E-2</v>
+        <v>1.6504846550078046E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1606051205876055E-3</v>
+        <v>1.1465087021189301E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.3611038098588771E-2</v>
+        <v>-6.283843439698647E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.65036522902437</v>
+        <v>273.65111763701697</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6295653628044</v>
+        <v>3420.6389704627122</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.34981229623696</v>
+        <v>327.29992469570499</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.9793776590413</v>
+        <v>1424.9388951584172</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7549000000000001</v>
+        <v>7.7589302062988281</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14989,7 +14989,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>7.9899208660225911</v>
+        <v>7.993846107111092</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.688903946803435</v>
+        <v>16.697373962798437</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.08350836855055</v>
+        <v>304.08434445317232</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15089,7 +15089,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.55880404495417</v>
+        <v>281.55957819738177</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90117540803845</v>
+        <v>337.90210447511595</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.69579510291362</v>
+        <v>289.69659162818579</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.47976526155674</v>
+        <v>375.48079765183405</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.0679435153088</v>
+        <v>298.06876305999623</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15143,7 +15143,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.23753683491861</v>
+        <v>417.23868403915225</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68204528092497</v>
+        <v>306.68288851028393</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.63926434971034</v>
+        <v>463.64053913656426</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.54509280150324</v>
+        <v>315.54596040001582</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.20141039417251</v>
+        <v>515.20282695233652</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.66428055774492</v>
+        <v>324.66517322967456</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.49787427825811</v>
+        <v>572.49944837437147</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.04701094935223</v>
+        <v>334.04792941931561</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.16637967346583</v>
+        <v>636.16812882760371</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70090030384375</v>
+        <v>343.70184531739864</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.91557263344407</v>
+        <v>706.91751631412023</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.63378505902432</v>
+        <v>353.63475738327503</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.5329089980728</v>
+        <v>785.53506883892908</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15287,7 +15287,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.85372812412618</v>
+        <v>363.85472854834609</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.0438546068817</v>
+        <v>3801.0543056646538</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15749,7 +15749,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6187613782149</v>
+        <v>1760.6236022401185</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.0681471179105</v>
+        <v>4972.0818179339913</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15781,7 +15781,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.0681471179105</v>
+        <v>4972.0818179339913</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15811,19 +15811,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.629565362804</v>
+        <v>3420.6389704627118</v>
       </c>
       <c r="C56" s="124">
-        <v>3530.9969812198256</v>
+        <v>3531.0066897774896</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.7932348463373</v>
+        <v>3761.8035779836255</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.6660851292536</v>
+        <v>4335.6780061431837</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.0480681449699</v>
+        <v>5077.0620276057671</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15832,19 +15832,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.6295653628031</v>
+        <v>3420.6389704627109</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.4660280260505</v>
+        <v>3641.4760403209075</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.1892621574334</v>
+        <v>4152.2006786976053</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.746186340938</v>
+        <v>5750.7619981502539</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.381112227049</v>
+        <v>8648.4048911504451</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15853,19 +15853,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6295653628031</v>
+        <v>3420.6389704627104</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.2021036451924</v>
+        <v>3778.2124918990435</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.1940596487048</v>
+        <v>4689.2069526959585</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.454922258039</v>
+        <v>8276.4776785617942</v>
       </c>
       <c r="F58" s="124">
-        <v>17363.914012379355</v>
+        <v>17363.961754861535</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15874,19 +15874,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6295653628031</v>
+        <v>3420.6389704627099</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.5142366725368</v>
+        <v>3917.5250079683124</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.7705681368643</v>
+        <v>5301.7851454773609</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.48628304239</v>
+        <v>12134.51964709238</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.230629604273</v>
+        <v>36349.330572652507</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15895,19 +15895,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6295653628031</v>
+        <v>3420.6389704627099</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.0822508195679</v>
+        <v>4047.0933783655873</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.732123706277</v>
+        <v>5943.7484661348799</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.370572612384</v>
+        <v>17688.419207195362</v>
       </c>
       <c r="F60" s="124">
-        <v>76382.468364507353</v>
+        <v>76382.678379866367</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15916,19 +15916,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6295653628031</v>
+        <v>3420.6389704627099</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.3792632678096</v>
+        <v>4161.3907050761027</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.6120985277894</v>
+        <v>6585.6302058201936</v>
       </c>
       <c r="E61" s="124">
-        <v>25476.614888713142</v>
+        <v>25476.684937253543</v>
       </c>
       <c r="F61" s="124">
-        <v>159939.67796756013</v>
+        <v>159940.1177253947</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15978,23 +15978,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9899208660225911</v>
+        <v>7.993846107111092</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9899208660225911</v>
+        <v>7.993846107111092</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9899208660225911</v>
+        <v>7.993846107111092</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9899208660225911</v>
+        <v>7.993846107111092</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9899208660225911</v>
+        <v>7.993846107111092</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16005,23 +16005,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>7.9899208660225876</v>
+        <v>7.9938461071110885</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6087557296777195</v>
+        <v>8.6130042804144296</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.902840283855415</v>
+        <v>9.9077649277577411</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.120570121077273</v>
+        <v>13.127175864676463</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.277530894447729</v>
+        <v>17.2863084379958</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16032,23 +16032,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>7.989920866022584</v>
+        <v>7.9938461071110831</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2281604424509567</v>
+        <v>9.2327326005529695</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.091807656667177</v>
+        <v>12.097875924358023</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.054985316852761</v>
+        <v>21.065736387640737</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.302149394754856</v>
+        <v>37.32138877997194</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16059,23 +16059,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>7.989920866022584</v>
+        <v>7.9938461071110796</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>9.9948455193411245</v>
+        <v>9.9998182312856105</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.102816730832442</v>
+        <v>15.110458097166719</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.216743196992525</v>
+        <v>35.234893063852176</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.170518487809474</v>
+        <v>86.2152891030006</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16086,23 +16086,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>7.989920866022584</v>
+        <v>7.9938461071110778</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.77597466128975</v>
+        <v>10.781355473363886</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.537559649881139</v>
+        <v>18.546995494177246</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>56.848891531616417</v>
+        <v>56.878343092480058</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>192.6220080786338</v>
+        <v>192.7223941668245</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16113,23 +16113,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>7.989920866022584</v>
+        <v>7.9938461071110778</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.502468108165566</v>
+        <v>11.508228476005756</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.137065796036506</v>
+        <v>22.148382198675684</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>87.98976042307352</v>
+        <v>88.035481499372523</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>417.09009970674953</v>
+        <v>417.30775892223221</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16139,23 +16139,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>7.989920866022584</v>
+        <v>7.9938461071110778</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.1433363894908</v>
+        <v>12.149431578315964</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.736114515417757</v>
+        <v>25.749311237417864</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>131.65878240788473</v>
+        <v>131.72731832052318</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>885.5989798919594</v>
+        <v>886.06141109772739</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.170518487809474</v>
+        <v>86.2152891030006</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.054985316852761</v>
+        <v>21.065736387640737</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16235,7 +16235,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.091807656667177</v>
+        <v>12.097875924358023</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2281604424509567</v>
+        <v>9.2327326005529695</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.989920866022584</v>
+        <v>7.9938461071110796</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.64</v>
+        <v>-14.82</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83287625999999992</v>
+        <v>0.83330910415649406</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83287625999999992</v>
+        <v>0.83330910415649406</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.521440598966546</v>
+        <v>17.530343281690275</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.21718549870042</v>
+        <v>342.21818870935726</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.65036522902437</v>
+        <v>273.65111763701697</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7398353255798833</v>
+        <v>-4.7398895805159587</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.64</v>
+        <v>14.82</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9899208660225911</v>
+        <v>7.993846107111092</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.091807656667177</v>
+        <v>12.097875924358023</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2281604424509567</v>
+        <v>9.2327326005529695</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16800,7 +16800,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.054985316852761</v>
+        <v>21.065736387640737</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.311713745861049</v>
+        <v>13.318419352253555</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>7.989920866022584</v>
+        <v>7.9938461071110796</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.170518487809474</v>
+        <v>86.2152891030006</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16985,7 +16985,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.688564338966547</v>
+        <v>16.69703417753378</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.688903946803435</v>
+        <v>16.697373962798437</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67050085904133838</v>
+        <v>-0.67052577943565495</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83287625999999992</v>
+        <v>0.83330910415649406</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.5125973042330454</v>
+        <v>1.5133833980812073</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>7.5960693395387082</v>
+        <v>7.5999245232288466</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.1086666437717536</v>
+        <v>9.113307921310053</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.45419711014303965</v>
+        <v>0.45419600724227982</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.64</v>
+        <v>14.82</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.919795200818049E-2</v>
+        <v>9.4690284991131524E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17259,7 +17259,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7544384180555554</v>
+        <v>1.7553501962555775</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>9.6577339924574925</v>
+        <v>9.6626355194061233</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>11.412172410513048</v>
+        <v>11.4179857156617</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31616811496082498</v>
+        <v>0.31616683572314619</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.1464029003962817</v>
+        <v>2.1475183817679309</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>13.247920428611099</v>
+        <v>13.254644059542004</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>15.394323329007381</v>
+        <v>15.402162441309935</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.7552567355192448E-2</v>
+        <v>7.7551002319089846E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D055E5-DC2F-4882-BE85-21F979211EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EC586B-1D56-4FE6-B177-1A54CC8BCAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>14.82</v>
+        <v>14.3</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>20497.00971006</v>
+        <v>19777.816386900002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4227,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7589302062988281</v>
+        <v>7.7691999999999997</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>9.113307921310053</v>
+        <v>9.1251344157607761</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.4690284991131524E-2</v>
+        <v>0.1090060893695004</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0181887093574025</v>
+        <v>7.0207450962321305</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.98181129064261</v>
+        <v>-144.97925490376787</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03429426339265</v>
+        <v>-102.03493336011134</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.21818870935726</v>
+        <v>342.22074509623201</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.65111763701697</v>
+        <v>273.65303492717305</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10358778927538839</v>
+        <v>0.10749746672561937</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.6228684490991498E-2</v>
+        <v>5.8350495104895095E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.189637963265699</v>
+        <v>19.215172177204465</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.031930400604711</v>
+        <v>13.049179587436369</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.29992469570499</v>
+        <v>327.17280083957422</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8361385444501035</v>
+        <v>1.8378547715368729</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.993846107111092</v>
+        <v>8.0038473613049721</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-12.135683650367685</v>
+        <v>-12.151746556489819</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.22 HKD</v>
+        <v>86.33 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>21.07 HKD</v>
+        <v>21.09 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>12.1 HKD</v>
+        <v>12.11 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>9.23 HKD</v>
+        <v>9.24 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.99 HKD</v>
+        <v>8 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>16.69703417753378</v>
+        <v>16.718616112226428</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83330910415649406</v>
+        <v>0.83441207999999989</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>1.5133833980812073</v>
+        <v>1.5153865267182525</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>7.5999245232288466</v>
+        <v>7.6097478890425236</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>9.113307921310053</v>
+        <v>9.1251344157607761</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.45419600724227982</v>
+        <v>0.45419319670319436</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.7553501962555775</v>
+        <v>1.7576735944444439</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>9.6626355194061233</v>
+        <v>9.6751250649458491</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>11.4179857156617</v>
+        <v>11.432798659390293</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31616683572314619</v>
+        <v>0.31616357582195953</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>2.1475183817679309</v>
+        <v>2.1503608574912367</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>13.254644059542004</v>
+        <v>13.271776495124621</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>15.402162441309935</v>
+        <v>15.422137352615858</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7551002319089846E-2</v>
+        <v>7.7547014113353963E-2</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83330910415649406</v>
+        <v>0.83441207999999989</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79606623916625974</v>
+        <v>0.79711991999999998</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -7326,11 +7326,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83330910415649406</v>
+        <v>0.83441207999999989</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79606623916625974</v>
+        <v>0.79711991999999998</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8677,11 +8677,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2814187074355043</v>
+        <v>8.2923800718784193</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.135683650367685</v>
+        <v>-12.151746556489819</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.29992469570499</v>
+        <v>327.17280083957422</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8939,11 +8939,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.39332433297938</v>
+        <v>-342.52044818911014</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.00007530429497</v>
+        <v>-349.12719916042573</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -8955,11 +8955,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9752137437770092</v>
+        <v>1.974480658236806</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9378219314432252</v>
+        <v>1.9371163336066424</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -8972,7 +8972,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.00007530429497</v>
+        <v>349.12719916042573</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9087,11 +9087,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18023.994869232178</v>
+        <v>-18047.851599999998</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-13.031930400604711</v>
+        <v>-13.049179587436369</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9104,11 +9104,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2539.497272240837</v>
+        <v>2541.8709242828199</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8361385444501035</v>
+        <v>1.8378547715368729</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9138,11 +9138,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15484.497596991341</v>
+        <v>-15505.980675717179</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.195791856154608</v>
+        <v>-11.211324815899495</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9722,24 +9722,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.98181129064261</v>
+        <v>-144.97925490376787</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.98181129064261</v>
+        <v>-144.97925490376787</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.62058098942566</v>
+        <v>-165.61789302381473</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.7588190704158</v>
+        <v>-133.75716493773217</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.1422441651701</v>
+        <v>-167.14156747452679</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9777,24 +9777,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.13717705357061</v>
+        <v>408.13973344044535</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.41818870935725</v>
+        <v>487.420745096232</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.87941901057457</v>
+        <v>497.88210697618547</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44118092958399</v>
+        <v>286.44283506226765</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.542244165169961</v>
+        <v>-53.541567474526659</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03429426339265</v>
+        <v>-102.03493336011134</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9944,26 +9944,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.65111763701697</v>
+        <v>273.65303492717305</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.21818870935726</v>
+        <v>342.22074509623201</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.97941901057453</v>
+        <v>329.98210697618543</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54118092958399</v>
+        <v>236.54283506226764</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5422441651699579</v>
+        <v>-6.541567474526655</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10052,26 +10052,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.65111763701697</v>
+        <v>273.65303492717305</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.21818870935726</v>
+        <v>342.22074509623201</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.97941901057453</v>
+        <v>329.98210697618543</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54118092958399</v>
+        <v>236.54283506226764</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5422441651699579</v>
+        <v>-6.541567474526655</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10913,19 +10913,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270739734446214</v>
+        <v>0.24270612441135206</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27034658365169578</v>
+        <v>0.27034512410472733</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4834170565627171E-2</v>
+        <v>8.4833680670412331E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496384840842916</v>
+        <v>1.0496517500489342</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11051,24 +11051,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0181887093574025</v>
+        <v>7.0207450962321305</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.0181887093574025</v>
+        <v>7.0207450962321314</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.3794190105743285</v>
+        <v>7.3821069761852565</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5411809295842023</v>
+        <v>4.5428350622678497</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8577558348299008</v>
+        <v>1.8584325254732112</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11163,24 +11163,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.98181129064261</v>
+        <v>-144.97925490376787</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.98181129064261</v>
+        <v>-144.97925490376787</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.62058098942566</v>
+        <v>-165.61789302381473</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.7588190704158</v>
+        <v>-133.75716493773217</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.1422441651701</v>
+        <v>-167.14156747452679</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12250,26 +12250,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0400660784328878E-2</v>
+        <v>4.0399948421046612E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0400660784328878E-2</v>
+        <v>4.0399948421046612E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4976260316485349E-2</v>
+        <v>4.4975530367101543E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6450485855818797E-2</v>
+        <v>4.6449911424410392E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.271092842694483E-2</v>
+        <v>8.2710593564195758E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12307,26 +12307,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373158809941777</v>
+        <v>0.11373230046270004</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582405080236229</v>
+        <v>0.13582476316564454</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520514311605869</v>
+        <v>0.13520587306544249</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9472559011523826E-2</v>
+        <v>9.9473133442932238E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6495568173579752E-2</v>
+        <v>-2.6495233310830691E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8432897024854444E-2</v>
+        <v>2.843307511567501E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12479,26 +12479,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6255675649840315E-2</v>
+        <v>7.6256209922302032E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5362589508264303E-2</v>
+        <v>9.5363301871546569E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9609879157770619E-2</v>
+        <v>8.9610609107154418E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2143763345459087E-2</v>
+        <v>8.2144337776867499E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2374525757966933E-3</v>
+        <v>3.2371177130476321E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12586,26 +12586,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6255675649840315E-2</v>
+        <v>7.6256209922302032E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5362589508264303E-2</v>
+        <v>9.5363301871546569E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9609879157770619E-2</v>
+        <v>8.9610609107154418E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2143763345459087E-2</v>
+        <v>8.2144337776867499E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2374525757966933E-3</v>
+        <v>3.2371177130476321E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12655,16 +12655,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83330910415649406</v>
+        <v>0.83441207999999989</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83330910415649406</v>
+        <v>0.83441207999999989</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79606623916625974</v>
+        <v>0.79711991999999998</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12711,16 +12711,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1152.5198919957531</v>
+        <v>1154.0453782693223</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1152.5198919957531</v>
+        <v>1154.0453782693223</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1101.0106230797417</v>
+        <v>1102.4679311958334</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12766,16 +12766,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.2116396305916304</v>
+        <v>4.217184649811931</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.367792624764832</v>
+        <v>3.3722250763752104</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3366039202719451</v>
+        <v>3.3409930656494584</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12821,16 +12821,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.6228684490991498E-2</v>
+        <v>5.8350495104895095E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.6228684490991498E-2</v>
+        <v>5.8350495104895095E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.3715670658991882E-2</v>
+        <v>5.5742651748251743E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -12958,26 +12958,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265501266113225</v>
+        <v>-0.1626541595806188</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1011574091587715E-2</v>
+        <v>-2.1011724931207176E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815586639746655</v>
+        <v>0.73815521295184294</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3498164934206907</v>
+        <v>-6.3499150019944386</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82816994812204758</v>
+        <v>-0.82817211978649974</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13569,19 +13569,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.04090625050893</v>
+        <v>165.03967339594769</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88888434368721</v>
+        <v>161.8875656305064</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.40027631073195</v>
+        <v>117.39945533623883</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5916.9298825756023</v>
+        <v>-5917.5419577554749</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13677,24 +13677,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373158809941777</v>
+        <v>0.11373230046270004</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582405080236229</v>
+        <v>0.13582476316564454</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520514311605869</v>
+        <v>0.13520587306544249</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9472559011523826E-2</v>
+        <v>9.9473133442932238E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6495568173579752E-2</v>
+        <v>-2.6495233310830691E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13963,30 +13963,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5351710370612559</v>
+        <v>1.5372137741763576</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9198293659411765</v>
+        <v>1.9223848305238982</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8511703926723144</v>
+        <v>1.8536357187141124</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3269858832333987</v>
+        <v>1.3287515862457473</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.6701709265715525E-2</v>
+        <v>-3.6746486766436035E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2184826874779777</v>
+        <v>-1.2200954827340413</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14020,30 +14020,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10358778927538839</v>
+        <v>0.10749746672561937</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.12954314210129395</v>
+        <v>0.13443250563104184</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.124910282906364</v>
+        <v>0.12962487543455331</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.954020804543851E-2</v>
+        <v>9.2919691345856453E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.476498600925474E-3</v>
+        <v>-2.5696843892612608E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.221880482307542E-2</v>
+        <v>-8.532136242895394E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14077,23 +14077,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8178261379128226E-2</v>
+        <v>1.883928906564198E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1969058236772521E-2</v>
+        <v>2.2767933081746065E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6504846550078046E-2</v>
+        <v>1.7105022788262699E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1465087021189301E-3</v>
+        <v>1.1881999276505276E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.283843439698647E-2</v>
+        <v>-6.5123468375058696E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.65111763701697</v>
+        <v>273.65303492717305</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6389704627122</v>
+        <v>3420.6629365896629</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.29992469570499</v>
+        <v>327.17280083957422</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.9388951584172</v>
+        <v>1424.835737429237</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7589302062988281</v>
+        <v>7.7691999999999997</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14989,7 +14989,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>7.993846107111092</v>
+        <v>8.0038473613049721</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.697373962798437</v>
+        <v>16.718956349617887</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.08434445317232</v>
+        <v>304.08647496857191</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15089,7 +15089,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.55957819738177</v>
+        <v>281.56155089682579</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90210447511595</v>
+        <v>337.90447192891708</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.69659162818579</v>
+        <v>289.69862133823477</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.48079765183405</v>
+        <v>375.48342839437714</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.06876305999623</v>
+        <v>298.07085142824479</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15143,7 +15143,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.23868403915225</v>
+        <v>417.24160735124593</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68288851028393</v>
+        <v>306.68503723194186</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.64053913656426</v>
+        <v>463.64378755538792</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.54596040001582</v>
+        <v>315.54817121928409</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.20282695233652</v>
+        <v>515.20643663358703</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.66517322967456</v>
+        <v>324.66744794116136</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.49944837437147</v>
+        <v>572.50345949468488</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.04792941931561</v>
+        <v>334.05026986949269</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.16812882760371</v>
+        <v>636.17258603173116</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70184531739864</v>
+        <v>343.70425340610058</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.91751631412023</v>
+        <v>706.92246921183505</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.63475738327503</v>
+        <v>353.63723506524116</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.53506883892908</v>
+        <v>785.54057255719545</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15287,7 +15287,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.85472854834609</v>
+        <v>363.85727783480735</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.0543056646538</v>
+        <v>3801.0809371071487</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15749,7 +15749,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6236022401185</v>
+        <v>1760.6359377508604</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.0818179339913</v>
+        <v>4972.1166539821952</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15781,7 +15781,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.0818179339913</v>
+        <v>4972.1166539821952</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15811,19 +15811,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.6389704627118</v>
+        <v>3420.6629365896624</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.0066897774896</v>
+        <v>3531.0314291771515</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.8035779836255</v>
+        <v>3761.8299344225516</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.6780061431837</v>
+        <v>4335.7083833359857</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.0620276057671</v>
+        <v>5077.0975991800078</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15832,19 +15832,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.6389704627109</v>
+        <v>3420.6629365896615</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.4760403209075</v>
+        <v>3641.5015537053432</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.2006786976053</v>
+        <v>4152.2297703876229</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.7619981502539</v>
+        <v>5750.8022898891077</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.4048911504451</v>
+        <v>8648.465484732913</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15853,19 +15853,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6389704627104</v>
+        <v>3420.6629365896611</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.2124918990435</v>
+        <v>3778.2389633042426</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.2069526959585</v>
+        <v>4689.2398068293796</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.4776785617942</v>
+        <v>8276.535666299309</v>
       </c>
       <c r="F58" s="124">
-        <v>17363.961754861535</v>
+        <v>17364.083412515381</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15874,19 +15874,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6389704627099</v>
+        <v>3420.6629365896606</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.5250079683124</v>
+        <v>3917.5524554430335</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.7851454773609</v>
+        <v>5301.8222915360238</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.51964709238</v>
+        <v>12134.604665546785</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.330572652507</v>
+        <v>36349.585248073847</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15895,19 +15895,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6389704627099</v>
+        <v>3420.6629365896601</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.0933783655873</v>
+        <v>4047.1217336391269</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.7484661348799</v>
+        <v>5943.7901100007002</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.419207195362</v>
+        <v>17688.543138105331</v>
       </c>
       <c r="F60" s="124">
-        <v>76382.678379866367</v>
+        <v>76383.213542151148</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15916,19 +15916,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6389704627099</v>
+        <v>3420.6629365896606</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.3907050761027</v>
+        <v>4161.4198611544816</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.6302058201936</v>
+        <v>6585.6763469215857</v>
       </c>
       <c r="E61" s="124">
-        <v>25476.684937253543</v>
+        <v>25476.863435326795</v>
       </c>
       <c r="F61" s="124">
-        <v>159940.1177253947</v>
+        <v>159941.23831871044</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15978,23 +15978,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.993846107111092</v>
+        <v>8.0038473613049721</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.993846107111092</v>
+        <v>8.0038473613049721</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.993846107111092</v>
+        <v>8.0038473613049721</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.993846107111092</v>
+        <v>8.0038473613049721</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.993846107111092</v>
+        <v>8.0038473613049721</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16005,23 +16005,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>7.9938461071110885</v>
+        <v>8.0038473613049685</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6130042804144296</v>
+        <v>8.6238294020147332</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9077649277577411</v>
+        <v>9.9203128903742233</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.127175864676463</v>
+        <v>13.144007656293654</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.2863084379958</v>
+        <v>17.308674475810339</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16032,23 +16032,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>7.9938461071110831</v>
+        <v>8.0038473613049632</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2327326005529695</v>
+        <v>9.2443823482113903</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.097875924358023</v>
+        <v>12.113338103638934</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.065736387640737</v>
+        <v>21.093131427149697</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.32138877997194</v>
+        <v>37.370413998575195</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16059,23 +16059,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>7.9938461071110796</v>
+        <v>8.0038473613049597</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>9.9998182312856105</v>
+        <v>10.012488682338331</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.110458097166719</v>
+        <v>15.129928893903344</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.234893063852176</v>
+        <v>35.281141938883977</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.2152891030006</v>
+        <v>86.329373772623185</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16086,23 +16086,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>7.9938461071110778</v>
+        <v>8.0038473613049579</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.781355473363886</v>
+        <v>10.7950658574877</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.546995494177246</v>
+        <v>18.571039033832314</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>56.878343092480058</v>
+        <v>56.953391285376114</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>192.7223941668245</v>
+        <v>192.97819986380065</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16113,23 +16113,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>7.9938461071110778</v>
+        <v>8.0038473613049543</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.508228476005756</v>
+        <v>11.522906055591587</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.148382198675684</v>
+        <v>22.177217833875499</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.035481499372523</v>
+        <v>88.151988162684972</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>417.30775892223221</v>
+        <v>417.86240354270228</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16139,23 +16139,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>7.9938461071110778</v>
+        <v>8.0038473613049579</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.149431578315964</v>
+        <v>12.164962358844091</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.749311237417864</v>
+        <v>25.782938359180861</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>131.72731832052318</v>
+        <v>131.90196243858625</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>886.06141109772739</v>
+        <v>887.23979109361926</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.2152891030006</v>
+        <v>86.329373772623185</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.065736387640737</v>
+        <v>21.093131427149697</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16235,7 +16235,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.097875924358023</v>
+        <v>12.113338103638934</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2327326005529695</v>
+        <v>9.2443823482113903</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.9938461071110796</v>
+        <v>8.0038473613049597</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.82</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83330910415649406</v>
+        <v>0.83441207999999989</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83330910415649406</v>
+        <v>0.83441207999999989</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.530343281690275</v>
+        <v>17.553028192226428</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.21818870935726</v>
+        <v>342.22074509623201</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.65111763701697</v>
+        <v>273.65303492717305</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7398895805159587</v>
+        <v>-4.7400278460365488</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.82</v>
+        <v>14.3</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.993846107111092</v>
+        <v>8.0038473613049721</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.097875924358023</v>
+        <v>12.113338103638934</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2327326005529695</v>
+        <v>9.2443823482113903</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16800,7 +16800,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.065736387640737</v>
+        <v>21.093131427149697</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.318419352253555</v>
+        <v>13.335505617255578</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>7.9938461071110796</v>
+        <v>8.0038473613049597</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.2152891030006</v>
+        <v>86.329373772623185</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16985,7 +16985,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.69703417753378</v>
+        <v>16.718616112226428</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.697373962798437</v>
+        <v>16.718956349617887</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67052577943565495</v>
+        <v>-0.6705892844624014</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83330910415649406</v>
+        <v>0.83441207999999989</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.5133833980812073</v>
+        <v>1.5153865267182525</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>7.5999245232288466</v>
+        <v>7.6097478890425236</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.113307921310053</v>
+        <v>9.1251344157607761</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.45419600724227982</v>
+        <v>0.45419319670319436</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.82</v>
+        <v>14.3</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.4690284991131524E-2</v>
+        <v>0.1090060893695004</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17259,7 +17259,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7553501962555775</v>
+        <v>1.7576735944444439</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>9.6626355194061233</v>
+        <v>9.6751250649458491</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>11.4179857156617</v>
+        <v>11.432798659390293</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31616683572314619</v>
+        <v>0.31616357582195953</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.1475183817679309</v>
+        <v>2.1503608574912367</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>13.254644059542004</v>
+        <v>13.271776495124621</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>15.402162441309935</v>
+        <v>15.422137352615858</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.7551002319089846E-2</v>
+        <v>7.7547014113353963E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EC586B-1D56-4FE6-B177-1A54CC8BCAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3720E4F-728F-4EFF-A8B9-3BFC1F6C1B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>14.3</v>
+        <v>14.62</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>19777.816386900002</v>
+        <v>20220.396893459998</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4227,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7691999999999997</v>
+        <v>7.7786</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>9.1251344157607761</v>
+        <v>9.1359587259076722</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1090060893695004</v>
+        <v>0.10088016442395631</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0207450962321305</v>
+        <v>7.0230849715326169</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.97925490376787</v>
+        <v>-144.97691502846737</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03493336011134</v>
+        <v>-102.03551832893646</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.22074509623201</v>
+        <v>342.2230849715325</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.65303492717305</v>
+        <v>273.65478983364841</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10749746672561937</v>
+        <v>0.10527247112980752</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.8350495104895095E-2</v>
+        <v>5.7142383036935702E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.215172177204465</v>
+        <v>19.238544098972323</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.049179587436369</v>
+        <v>13.064967865267022</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.17280083957422</v>
+        <v>327.05644365827135</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8378547715368729</v>
+        <v>1.8394239890330735</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.0038473613049721</v>
+        <v>8.0130002227383752</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-12.151746556489819</v>
+        <v>-12.166449024907546</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.33 HKD</v>
+        <v>86.43 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>21.09 HKD</v>
+        <v>21.12 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>12.11 HKD</v>
+        <v>12.13 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>9.24 HKD</v>
+        <v>9.26 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>8 HKD</v>
+        <v>8.01 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>16.718616112226428</v>
+        <v>16.73836897721916</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83441207999999989</v>
+        <v>0.83542163999999997</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>1.5153865267182525</v>
+        <v>1.5172200016385984</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>7.6097478890425236</v>
+        <v>7.6187387242690745</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>9.1251344157607761</v>
+        <v>9.1359587259076722</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.45419319670319436</v>
+        <v>0.45419062404815735</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.7576735944444439</v>
+        <v>1.7598002138888889</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>9.6751250649458491</v>
+        <v>9.6865561210759026</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>11.432798659390293</v>
+        <v>11.446356334964792</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31616357582195953</v>
+        <v>0.31616059183883283</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>2.1503608574912367</v>
+        <v>2.1529625915256831</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>13.271776495124621</v>
+        <v>13.28745695620837</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>15.422137352615858</v>
+        <v>15.440419547734052</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7547014113353963E-2</v>
+        <v>7.7543363469380511E-2</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83441207999999989</v>
+        <v>0.83542163999999997</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79711991999999998</v>
+        <v>0.79808435999999994</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -7326,11 +7326,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83441207999999989</v>
+        <v>0.83542163999999997</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79711991999999998</v>
+        <v>0.79808435999999994</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8677,11 +8677,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2923800718784193</v>
+        <v>8.3024130704723103</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.151746556489819</v>
+        <v>-12.166449024907546</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.17280083957422</v>
+        <v>327.05644365827135</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8939,11 +8939,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.52044818911014</v>
+        <v>-342.63680537041301</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.12719916042573</v>
+        <v>-349.24355634172861</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -8955,11 +8955,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.974480658236806</v>
+        <v>1.9738101377313362</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9371163336066424</v>
+        <v>1.936470946190493</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -8972,7 +8972,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.12719916042573</v>
+        <v>349.24355634172861</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9087,11 +9087,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18047.851599999998</v>
+        <v>-18069.6878</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-13.049179587436369</v>
+        <v>-13.064967865267022</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9104,11 +9104,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2541.8709242828199</v>
+        <v>2544.0412526402297</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8378547715368729</v>
+        <v>1.8394239890330735</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9138,11 +9138,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15505.980675717179</v>
+        <v>-15525.646547359771</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.211324815899495</v>
+        <v>-11.225543876233948</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9722,24 +9722,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.97925490376787</v>
+        <v>-144.97691502846737</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.97925490376787</v>
+        <v>-144.97691502846737</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.61789302381473</v>
+        <v>-165.61543271375615</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75716493773217</v>
+        <v>-133.75565090077302</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.14156747452679</v>
+        <v>-167.14094809577077</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9777,24 +9777,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.13973344044535</v>
+        <v>408.14207331574585</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.420745096232</v>
+        <v>487.42308497153249</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.88210697618547</v>
+        <v>497.88456728624408</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44283506226765</v>
+        <v>286.44434909922677</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.541567474526659</v>
+        <v>-53.540948095770631</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03493336011134</v>
+        <v>-102.03551832893646</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9944,26 +9944,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.65303492717305</v>
+        <v>273.65478983364841</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.22074509623201</v>
+        <v>342.2230849715325</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.98210697618543</v>
+        <v>329.98456728624404</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54283506226764</v>
+        <v>236.54434909922676</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.541567474526655</v>
+        <v>-6.5409480957706272</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10052,26 +10052,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.65303492717305</v>
+        <v>273.65478983364841</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.22074509623201</v>
+        <v>342.2230849715325</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.98210697618543</v>
+        <v>329.98456728624404</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54283506226764</v>
+        <v>236.54434909922676</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.541567474526655</v>
+        <v>-6.5409480957706272</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10913,19 +10913,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270612441135206</v>
+        <v>0.24270495930021288</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27034512410472733</v>
+        <v>0.2703437881869829</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4833680670412331E-2</v>
+        <v>8.4833232271523271E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496517500489342</v>
+        <v>1.0496638927549999</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11051,24 +11051,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0207450962321305</v>
+        <v>7.0230849715326169</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.0207450962321314</v>
+        <v>7.0230849715326169</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.3821069761852565</v>
+        <v>7.3845672862438558</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5428350622678497</v>
+        <v>4.5443490992269879</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8584325254732112</v>
+        <v>1.8590519042292224</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11163,24 +11163,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.97925490376787</v>
+        <v>-144.97691502846737</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.97925490376787</v>
+        <v>-144.97691502846737</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.61789302381473</v>
+        <v>-165.61543271375615</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75716493773217</v>
+        <v>-133.75565090077302</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.14156747452679</v>
+        <v>-167.14094809577077</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12250,26 +12250,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0399948421046612E-2</v>
+        <v>4.0399296390923309E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0399948421046612E-2</v>
+        <v>4.0399296390923309E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4975530367101543E-2</v>
+        <v>4.4974862240320483E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6449911424410392E-2</v>
+        <v>4.6449385644107874E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2710593564195758E-2</v>
+        <v>8.271028706243605E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12307,26 +12307,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373230046270004</v>
+        <v>0.11373295249282335</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582476316564454</v>
+        <v>0.13582541519576785</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520587306544249</v>
+        <v>0.13520654119222356</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9473133442932238E-2</v>
+        <v>9.9473659223234742E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6495233310830691E-2</v>
+        <v>-2.6494926809070979E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.843307511567501E-2</v>
+        <v>2.8433238123205837E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12479,26 +12479,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6256209922302032E-2</v>
+        <v>7.6256698944894508E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5363301871546569E-2</v>
+        <v>9.5363953901669879E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9610609107154418E-2</v>
+        <v>8.9611277233935485E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2144337776867499E-2</v>
+        <v>8.2144863557170017E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2371177130476321E-3</v>
+        <v>3.2368112112879195E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12586,26 +12586,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6256209922302032E-2</v>
+        <v>7.6256698944894508E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5363301871546569E-2</v>
+        <v>9.5363953901669879E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9610609107154418E-2</v>
+        <v>8.9611277233935485E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2144337776867499E-2</v>
+        <v>8.2144863557170017E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2371177130476321E-3</v>
+        <v>3.2368112112879195E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12655,16 +12655,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83441207999999989</v>
+        <v>0.83542163999999997</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83441207999999989</v>
+        <v>0.83542163999999997</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79711991999999998</v>
+        <v>0.79808435999999994</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12711,16 +12711,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1154.0453782693223</v>
+        <v>1155.4416644449561</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1154.0453782693223</v>
+        <v>1155.4416644449561</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1102.4679311958334</v>
+        <v>1103.8018135200416</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12766,16 +12766,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.217184649811931</v>
+        <v>4.2222599690191274</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.3722250763752104</v>
+        <v>3.3762820662465547</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3409930656494584</v>
+        <v>3.3450104124492359</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12821,16 +12821,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.8350495104895095E-2</v>
+        <v>5.7142383036935702E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.8350495104895095E-2</v>
+        <v>5.7142383036935702E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.5742651748251743E-2</v>
+        <v>5.4588533515731875E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -12958,26 +12958,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.1626541595806188</v>
+        <v>-0.16265337875906505</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1011724931207176E-2</v>
+        <v>-2.1011862994132713E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815521295184294</v>
+        <v>0.73815461485599987</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3499150019944386</v>
+        <v>-6.3500051696292976</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82817211978649974</v>
+        <v>-0.82817410752320075</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13569,19 +13569,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.03967339594769</v>
+        <v>165.0385449733709</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.8875656305064</v>
+        <v>161.88635862373829</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.39945533623883</v>
+        <v>117.3987039037272</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5917.5419577554749</v>
+        <v>-5918.1023046230657</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13677,24 +13677,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373230046270004</v>
+        <v>0.11373295249282335</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582476316564454</v>
+        <v>0.13582541519576785</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520587306544249</v>
+        <v>0.13520654119222356</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9473133442932238E-2</v>
+        <v>9.9473659223234742E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6495233310830691E-2</v>
+        <v>-2.6494926809070979E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13963,30 +13963,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5372137741763576</v>
+        <v>1.5390835279177857</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9223848305238982</v>
+        <v>1.9247238949227798</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8536357187141124</v>
+        <v>1.8558922805117612</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3287515862457473</v>
+        <v>1.3303677656874309</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.6746486766436035E-2</v>
+        <v>-3.67874630562302E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2200954827340413</v>
+        <v>-1.2215716833129557</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14020,30 +14020,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10749746672561937</v>
+        <v>0.10527247112980752</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13443250563104184</v>
+        <v>0.13165006121222844</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12962487543455331</v>
+        <v>0.12694201645087286</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.2919691345856453E-2</v>
+        <v>9.099642720160267E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.5696843892612608E-3</v>
+        <v>-2.5162423431074011E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.532136242895394E-2</v>
+        <v>-8.3554834699928582E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14077,23 +14077,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.883928906564198E-2</v>
+        <v>1.8426938005381695E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2767933081746065E-2</v>
+        <v>2.2269592549177073E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7105022788262699E-2</v>
+        <v>1.6730631044607158E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1881999276505276E-3</v>
+        <v>1.1621928156910087E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.5123468375058696E-2</v>
+        <v>-6.3698057302553998E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.65303492717305</v>
+        <v>273.65478983364841</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6629365896629</v>
+        <v>3420.6848729206049</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.17280083957422</v>
+        <v>327.05644365827135</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.835737429237</v>
+        <v>1424.7413165788762</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7691999999999997</v>
+        <v>7.7786</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14989,7 +14989,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.0038473613049721</v>
+        <v>8.0130002227383752</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.718956349617887</v>
+        <v>16.738709628450355</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.08647496857191</v>
+        <v>304.08842504131326</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15089,7 +15089,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.56155089682579</v>
+        <v>281.56335651973444</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90447192891708</v>
+        <v>337.90663887271148</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.69862133823477</v>
+        <v>289.70047914327114</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.48342839437714</v>
+        <v>375.48583632783954</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.07085142824479</v>
+        <v>298.07276292346148</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15143,7 +15143,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.24160735124593</v>
+        <v>417.24428307526534</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68503723194186</v>
+        <v>306.68700396897395</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.64378755538792</v>
+        <v>463.64676085142781</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.54817121928409</v>
+        <v>315.55019479460867</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.20643663358703</v>
+        <v>515.20974059516027</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.66744794116136</v>
+        <v>324.66952999739323</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.50345949468488</v>
+        <v>572.50713089569285</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.05026986949269</v>
+        <v>334.05241209671806</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.17258603173116</v>
+        <v>636.17666573576582</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70425340610058</v>
+        <v>343.70645754324852</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.92246921183505</v>
+        <v>706.92700262700123</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.63723506524116</v>
+        <v>353.63950290149563</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.54057255719545</v>
+        <v>785.54561014151386</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15287,7 +15287,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.85727783480735</v>
+        <v>363.8596112110593</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.0809371071487</v>
+        <v>3801.1053130164155</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15749,7 +15749,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6359377508604</v>
+        <v>1760.6472285132991</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.1166539821952</v>
+        <v>4972.1485396132639</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15781,7 +15781,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.1166539821952</v>
+        <v>4972.1485396132639</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15811,19 +15811,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.6629365896624</v>
+        <v>3420.684872920604</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.0314291771515</v>
+        <v>3531.0540732889604</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.8299344225516</v>
+        <v>3761.8540586195036</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.7083833359857</v>
+        <v>4335.7361877516005</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.0975991800078</v>
+        <v>5077.1301580422005</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15832,19 +15832,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.6629365896615</v>
+        <v>3420.684872920604</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.5015537053432</v>
+        <v>3641.5249062497737</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.2297703876229</v>
+        <v>4152.2563981753001</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.8022898891077</v>
+        <v>5750.8391691445477</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.465484732913</v>
+        <v>8648.520946380122</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15853,19 +15853,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6629365896611</v>
+        <v>3420.6848729206031</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.2389633042426</v>
+        <v>3778.2631927304719</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.2398068293796</v>
+        <v>4689.2698784026907</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.535666299309</v>
+        <v>8276.5887428019614</v>
       </c>
       <c r="F58" s="124">
-        <v>17364.083412515381</v>
+        <v>17364.194766450946</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15874,19 +15874,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6629365896606</v>
+        <v>3420.6848729206031</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.5524554430335</v>
+        <v>3917.5775782711926</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.8222915360238</v>
+        <v>5301.8562915326738</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.604665546785</v>
+        <v>12134.682483416807</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.585248073847</v>
+        <v>36349.818353920993</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15895,19 +15895,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6629365896601</v>
+        <v>3420.6848729206031</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.1217336391269</v>
+        <v>4047.1476873806555</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.7901100007002</v>
+        <v>5943.8282268655648</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.543138105331</v>
+        <v>17688.656572765027</v>
       </c>
       <c r="F60" s="124">
-        <v>76383.213542151148</v>
+        <v>76383.703379203725</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15916,19 +15916,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6629365896606</v>
+        <v>3420.6848729206026</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.4198611544816</v>
+        <v>4161.4465478771899</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.6763469215857</v>
+        <v>6585.7185801314936</v>
       </c>
       <c r="E61" s="124">
-        <v>25476.863435326795</v>
+        <v>25477.026815618279</v>
       </c>
       <c r="F61" s="124">
-        <v>159941.23831871044</v>
+        <v>159942.26400408198</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15978,23 +15978,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.0038473613049721</v>
+        <v>8.0130002227383752</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.0038473613049721</v>
+        <v>8.0130002227383752</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.0038473613049721</v>
+        <v>8.0130002227383752</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.0038473613049721</v>
+        <v>8.0130002227383752</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.0038473613049721</v>
+        <v>8.0130002227383752</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16005,23 +16005,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.0038473613049685</v>
+        <v>8.0130002227383699</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6238294020147332</v>
+        <v>8.6337363639901099</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9203128903742233</v>
+        <v>9.9317967994819938</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.144007656293654</v>
+        <v>13.159412630546077</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.308674475810339</v>
+        <v>17.329145044385694</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16032,23 +16032,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>8.0038473613049632</v>
+        <v>8.0130002227383699</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2443823482113903</v>
+        <v>9.2550441051361751</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.113338103638934</v>
+        <v>12.127489447274309</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.093131427149697</v>
+        <v>21.118205130736524</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.370413998575195</v>
+        <v>37.415286191155218</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16059,23 +16059,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>8.0038473613049597</v>
+        <v>8.0130002227383663</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>10.012488682338331</v>
+        <v>10.024084707298035</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.129928893903344</v>
+        <v>15.147749396644116</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.281141938883977</v>
+        <v>35.323472894639238</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.329373772623185</v>
+        <v>86.433796041940568</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16086,23 +16086,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>8.0038473613049579</v>
+        <v>8.0130002227383663</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.7950658574877</v>
+        <v>10.807613751748717</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.571039033832314</v>
+        <v>18.593045049783342</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>56.953391285376114</v>
+        <v>57.02208277079972</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>192.97819986380065</v>
+        <v>193.21234191897534</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16113,23 +16113,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>8.0038473613049543</v>
+        <v>8.0130002227383663</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.522906055591587</v>
+        <v>11.536339241122057</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.177217833875499</v>
+        <v>22.203610140410763</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.151988162684972</v>
+        <v>88.25862732605593</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>417.86240354270228</v>
+        <v>418.3700781984042</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16139,23 +16139,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>8.0038473613049579</v>
+        <v>8.0130002227383628</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.164962358844091</v>
+        <v>12.179176494425485</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.782938359180861</v>
+        <v>25.813716398888705</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>131.90196243858625</v>
+        <v>132.06181585196194</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>887.23979109361926</v>
+        <v>888.3183818712414</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.329373772623185</v>
+        <v>86.433796041940568</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.093131427149697</v>
+        <v>21.118205130736524</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16235,7 +16235,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.113338103638934</v>
+        <v>12.127489447274309</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2443823482113903</v>
+        <v>9.2550441051361751</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>8.0038473613049597</v>
+        <v>8.0130002227383663</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.3</v>
+        <v>-14.62</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83441207999999989</v>
+        <v>0.83542163999999997</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83441207999999989</v>
+        <v>0.83542163999999997</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.553028192226428</v>
+        <v>17.57379061721916</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.22074509623201</v>
+        <v>342.2230849715325</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.65303492717305</v>
+        <v>273.65478983364841</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7400278460365488</v>
+        <v>-4.7401544173595855</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.3</v>
+        <v>14.62</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.0038473613049721</v>
+        <v>8.0130002227383752</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.113338103638934</v>
+        <v>12.127489447274309</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2443823482113903</v>
+        <v>9.2550441051361751</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16800,7 +16800,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.093131427149697</v>
+        <v>21.118205130736524</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.335505617255578</v>
+        <v>13.351143515539125</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>8.0038473613049597</v>
+        <v>8.0130002227383663</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.329373772623185</v>
+        <v>86.433796041940568</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16985,7 +16985,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.718616112226428</v>
+        <v>16.73836897721916</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.718956349617887</v>
+        <v>16.738709628450355</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.6705892844624014</v>
+        <v>-0.67064741442322484</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83441207999999989</v>
+        <v>0.83542163999999997</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.5153865267182525</v>
+        <v>1.5172200016385984</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>7.6097478890425236</v>
+        <v>7.6187387242690745</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.1251344157607761</v>
+        <v>9.1359587259076722</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.45419319670319436</v>
+        <v>0.45419062404815735</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.3</v>
+        <v>14.62</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1090060893695004</v>
+        <v>0.10088016442395631</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17259,7 +17259,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7576735944444439</v>
+        <v>1.7598002138888889</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>9.6751250649458491</v>
+        <v>9.6865561210759026</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>11.432798659390293</v>
+        <v>11.446356334964792</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31616357582195953</v>
+        <v>0.31616059183883283</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.1503608574912367</v>
+        <v>2.1529625915256831</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>13.271776495124621</v>
+        <v>13.28745695620837</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>15.422137352615858</v>
+        <v>15.440419547734052</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.7547014113353963E-2</v>
+        <v>7.7543363469380511E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3720E4F-728F-4EFF-A8B9-3BFC1F6C1B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849A7063-219A-4B5F-B4CE-18CF4FB40815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2358,6 +2358,24 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
@@ -2365,6 +2383,9 @@
   </si>
   <si>
     <t>1910.HK</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>USD</t>
@@ -3053,7 +3074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3754,29 +3775,36 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4066,13 +4094,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4089,7 +4116,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4107,9 +4134,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>1910.HK Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>424</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4121,340 +4147,332 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>425</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>1383064083</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>14.62</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>1383064083</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (HKD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>20220.396893459998</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>USD/HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>7.7786</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">High Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>7.7786</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>USD/HKD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="C22" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>428</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E19" s="339">
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>9.1359587259076722</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="280">
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.10088016442395631</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
         <v>362</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>553.11898834421322</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>7.0230849715326169</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-152</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>-144.97691502846737</v>
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4462,405 +4480,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-32.451765153160977</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>7.0230849715326169</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-152</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>-144.97691502846737</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-32.451765153160977</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-102.03551832893646</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
-        <v>369</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>342.2230849715325</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>342.2230849715325</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>273.65478983364841</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
         <v>398</v>
       </c>
-      <c r="C58" s="92">
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.10527247112980752</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>5.7142383036935702E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
         <v>363</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C72" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>19.238544098972323</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
         <v>365</v>
       </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>2323</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>13.064967865267022</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
         <v>412</v>
       </c>
-      <c r="C88" s="337">
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>2.2875080906148866</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
         <v>413</v>
       </c>
-      <c r="C89" s="337">
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>1.5035598705501618</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
         <v>415</v>
       </c>
-      <c r="C90" s="338">
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>4.1998196571663646</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>676.3</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>327.05644365827135</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8394239890330735</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>0</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4869,591 +4895,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>327.05644365827135</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.8394239890330735</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>8.0130002227383752</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>0</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
+        <f>Reporting_currency</f>
+        <v>USD</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>414</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>-12.166449024907546</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>8.0130002227383752</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>-12.166449024907546</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
         <v>366</v>
       </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.25</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>86.43 HKD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.15</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>21.12 HKD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.06</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>12.13 HKD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>9.26 HKD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>8.01 HKD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>16.73836897721916</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
         <v>410</v>
       </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>0.83542163999999997</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
         <v>418</v>
       </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>1910.HK</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>1.5172200016385984</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>7.6187387242690745</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>9.1359587259076722</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.45419062404815735</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
         <v>421</v>
       </c>
-      <c r="C136" s="337">
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>1.7598002138888889</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>9.6865561210759026</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>11.446356334964792</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.31616059183883283</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
-      <c r="C142" s="92">
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>2.1529625915256831</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>13.28745695620837</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="C145" s="239">
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>15.440419547734052</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>7.7543363469380511E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
-        <v>389</v>
-      </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
-        <v>390</v>
-      </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
-        <v>391</v>
-      </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5477,7 +5600,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>USD</v>
       </c>
       <c r="C1" s="104">
@@ -6018,7 +6141,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9178,7 +9301,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -11806,7 +11929,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12138,7 +12261,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -14873,7 +14996,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -14883,7 +15006,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -14901,10 +15024,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -14919,8 +15042,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -14935,8 +15058,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -14951,8 +15074,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -14978,7 +15101,7 @@
         <v>7.7786</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>USD/HKD</v>
       </c>
       <c r="H11" s="121"/>
@@ -16446,11 +16569,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 新秀麗(1910.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16471,8 +16594,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16493,8 +16616,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16504,8 +16627,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16518,8 +16641,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16537,8 +16660,8 @@
         <v>0.21097145624674352</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16555,8 +16678,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.77230247224880189</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16573,8 +16696,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-4.7401544173595855</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16600,21 +16723,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="350" t="s">
+      <c r="E18" s="353" t="s">
         <v>338</v>
       </c>
-      <c r="F18" s="351"/>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16628,8 +16751,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16643,8 +16766,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16664,8 +16787,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16675,8 +16798,8 @@
         <v>0.06</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16690,8 +16813,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16701,8 +16824,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16722,8 +16845,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16733,8 +16856,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16748,8 +16871,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16759,8 +16882,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16780,8 +16903,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16791,8 +16914,8 @@
         <v>0.15</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16806,8 +16929,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16818,8 +16941,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -16881,8 +17004,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -16892,8 +17015,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -16907,8 +17030,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -16918,8 +17041,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -16939,8 +17062,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -16950,8 +17073,8 @@
         <v>0.25</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -16965,8 +17088,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -16976,8 +17099,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -16995,7 +17118,7 @@
         <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
@@ -17160,7 +17283,7 @@
         <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17249,7 +17372,7 @@
         <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17307,7 +17430,7 @@
         <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849A7063-219A-4B5F-B4CE-18CF4FB40815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789149CD-0E3C-4447-91E2-E215FCC92A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5566,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8508,7 +8508,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>68.8</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789149CD-0E3C-4447-91E2-E215FCC92A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404A4A38-2EE8-4ACF-B0C2-A153E650740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>14.62</v>
+        <v>13.8</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4226,8 +4226,7 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>20220.396893459998</v>
+        <v>7.8063000000000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4264,13 +4263,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4319,7 +4318,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4335,7 +4334,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>9.1359587259076722</v>
+        <v>7.4274079182285586</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4349,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10088016442395631</v>
+        <v>0.12343060589714883</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4370,22 +4369,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4396,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4422,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4457,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4479,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4549,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4571,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4593,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4643,7 +4642,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10527247112980752</v>
+        <v>0.11152779187810041</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4651,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.7142383036935702E-2</v>
+        <v>6.0537799999999996E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4670,22 +4669,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4742,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4794,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4813,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4950,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4995,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5144,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5163,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5201,7 +5200,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5236,7 +5235,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5246,7 +5245,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>1.5172200016385984</v>
+        <v>1.3274192239067051</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5255,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>7.6187387242690745</v>
+        <v>6.0999886943218531</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5264,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>9.1359587259076722</v>
+        <v>7.4274079182285586</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.45419062404815735</v>
+        <v>0.55626453638719364</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5443,13 +5442,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5485,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5499,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5538,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5565,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12944,16 +12943,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.7142383036935702E-2</v>
+        <v>6.0537799999999996E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.7142383036935702E-2</v>
+        <v>6.0537799999999996E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.4588533515731875E-2</v>
+        <v>5.7832199999999993E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14143,30 +14142,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10527247112980752</v>
+        <v>0.11152779187810041</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13165006121222844</v>
+        <v>0.13947274600889709</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12694201645087286</v>
+        <v>0.13448494786317111</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.099642720160267E-2</v>
+        <v>9.6403461281697883E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.5162423431074011E-3</v>
+        <v>-2.665758192480449E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.3554834699928582E-2</v>
+        <v>-8.8519687196590993E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14200,23 +14199,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8426938005381695E-2</v>
+        <v>1.9521872002802924E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2269592549177073E-2</v>
+        <v>2.3592858193403531E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6730631044607158E-2</v>
+        <v>1.7724769990735988E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1621928156910087E-3</v>
+        <v>1.2312506496668511E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.3698057302553998E-2</v>
+        <v>-6.7483014330676772E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16505,7 +16504,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.62</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16745,7 +16744,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.62</v>
+        <v>13.8</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17284,7 +17283,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17293,7 +17292,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.5172200016385984</v>
+        <v>1.3274192239067051</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17305,7 +17304,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>7.6187387242690745</v>
+        <v>6.0999886943218531</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17315,7 +17314,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.1359587259076722</v>
+        <v>7.4274079182285586</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17326,7 +17325,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.45419062404815735</v>
+        <v>0.55626453638719364</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17343,7 +17342,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.62</v>
+        <v>13.8</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17356,7 +17355,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10088016442395631</v>
+        <v>0.12343060589714883</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404A4A38-2EE8-4ACF-B0C2-A153E650740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8773FDBB-674B-4678-B7F4-13E622DB9954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4226,7 +4226,8 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <v>7.8063000000000002</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>19086.284345400003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4263,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4369,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4396,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4422,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4457,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4479,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4549,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4571,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4593,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4669,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4742,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4794,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4813,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4950,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4995,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5144,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5163,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5442,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5485,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5499,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5538,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5565,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8773FDBB-674B-4678-B7F4-13E622DB9954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0490DC-8420-4258-9CB1-D55519FA4E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>13.8</v>
+        <v>13.96</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>19086.284345400003</v>
+        <v>19307.574598679999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4254,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>7.7786</v>
+        <v>7.8074000000000003</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>7.4274079182285586</v>
+        <v>7.454375218200834</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12343060589714883</v>
+        <v>0.12031246204964541</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0230849715326169</v>
+        <v>7.0302539511766549</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.97691502846737</v>
+        <v>-144.96974604882334</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03551832893646</v>
+        <v>-102.03731057384746</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.2230849715325</v>
+        <v>342.23025395117651</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.65478983364841</v>
+        <v>273.66016656838144</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11152779187810041</v>
+        <v>0.11065990570416093</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.0537799999999996E-2</v>
+        <v>6.0065527220630369E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.238544098972323</v>
+        <v>19.310153545376078</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.064967865267022</v>
+        <v>13.113340461173699</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>327.05644365827135</v>
+        <v>326.69994506023733</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8394239890330735</v>
+        <v>1.8442219579085819</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.0130002227383752</v>
+        <v>8.0410350421109609</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-12.166449024907546</v>
+        <v>-12.211494885591646</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.43 HKD</v>
+        <v>86.75 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>21.12 HKD</v>
+        <v>21.2 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>12.13 HKD</v>
+        <v>12.17 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>9.26 HKD</v>
+        <v>9.29 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>8.01 HKD</v>
+        <v>8.04 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>16.73836897721916</v>
+        <v>16.798881245143086</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83542163999999997</v>
+        <v>0.83851476000000003</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>1.3274192239067051</v>
+        <v>1.3323339481049561</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>6.0999886943218531</v>
+        <v>6.1220412700958784</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>7.4274079182285586</v>
+        <v>7.454375218200834</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55626453638719364</v>
+        <v>0.55625763945702911</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>1.7598002138888889</v>
+        <v>1.7663158138888888</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>9.6865561210759026</v>
+        <v>9.72157479464299</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>11.446356334964792</v>
+        <v>11.487890608531879</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31616059183883283</v>
+        <v>0.31615144836783271</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>2.1529625915256831</v>
+        <v>2.1609338617588794</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>13.28745695620837</v>
+        <v>13.335493545463633</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>15.440419547734052</v>
+        <v>15.496427407222512</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7543363469380511E-2</v>
+        <v>7.7532177227405574E-2</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -6114,11 +6114,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83542163999999997</v>
+        <v>0.83851476000000003</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.79808435999999994</v>
+        <v>0.80103924000000004</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -7301,11 +7301,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
       <c r="E62" s="183">
@@ -7449,11 +7449,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83542163999999997</v>
+        <v>0.83851476000000003</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.79808435999999994</v>
+        <v>0.80103924000000004</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8800,11 +8800,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.3024130704723103</v>
+        <v>8.3331524704195505</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.166449024907546</v>
+        <v>-12.211494885591646</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>327.05644365827135</v>
+        <v>326.69994506023733</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9062,11 +9062,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.63680537041301</v>
+        <v>-342.99330396844704</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.24355634172861</v>
+        <v>-349.60005493976263</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9078,11 +9078,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9738101377313362</v>
+        <v>1.9717586092065948</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.936470946190493</v>
+        <v>1.9344962634989544</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9095,7 +9095,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.24355634172861</v>
+        <v>349.60005493976263</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9210,11 +9210,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18069.6878</v>
+        <v>-18136.590200000002</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-13.064967865267022</v>
+        <v>-13.113340461173703</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9227,11 +9227,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2544.0412526402297</v>
+        <v>2550.6771510632971</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8394239890330735</v>
+        <v>1.8442219579085819</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9261,11 +9261,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15525.646547359771</v>
+        <v>-15585.913048936705</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.225543876233948</v>
+        <v>-11.269118503265121</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9845,24 +9845,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.97691502846737</v>
+        <v>-144.96974604882334</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.97691502846737</v>
+        <v>-144.96974604882334</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.61543271375615</v>
+        <v>-165.60789474251277</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75565090077302</v>
+        <v>-133.75101214923865</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.14094809577077</v>
+        <v>-167.13905042468852</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9900,24 +9900,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.14207331574585</v>
+        <v>408.14924229538985</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.42308497153249</v>
+        <v>487.4302539511765</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.88456728624408</v>
+        <v>497.89210525748746</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44434909922677</v>
+        <v>286.44898785076117</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.540948095770631</v>
+        <v>-53.539050424688384</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03551832893646</v>
+        <v>-102.03731057384746</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10067,26 +10067,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.65478983364841</v>
+        <v>273.66016656838144</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.2230849715325</v>
+        <v>342.23025395117651</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.98456728624404</v>
+        <v>329.99210525748748</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54434909922676</v>
+        <v>236.54898785076116</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5409480957706272</v>
+        <v>-6.53905042468838</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10175,26 +10175,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.65478983364841</v>
+        <v>273.66016656838144</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.2230849715325</v>
+        <v>342.23025395117651</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.98456728624404</v>
+        <v>329.99210525748748</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54434909922676</v>
+        <v>236.54898785076116</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5409480957706272</v>
+        <v>-6.53905042468838</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11036,19 +11036,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270495930021288</v>
+        <v>0.24270138966763752</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2703437881869829</v>
+        <v>0.27033969524459706</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4833232271523271E-2</v>
+        <v>8.4831858483159342E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0496638927549999</v>
+        <v>1.049701097688587</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11174,24 +11174,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0230849715326169</v>
+        <v>7.0302539511766549</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.0230849715326169</v>
+        <v>7.0302539511766557</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.3845672862438558</v>
+        <v>7.392105257487219</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5443490992269879</v>
+        <v>4.5489878507613657</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8590519042292224</v>
+        <v>1.8609495753114678</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11286,24 +11286,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.97691502846737</v>
+        <v>-144.96974604882334</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.97691502846737</v>
+        <v>-144.96974604882334</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.61543271375615</v>
+        <v>-165.60789474251277</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75565090077302</v>
+        <v>-133.75101214923865</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.14094809577077</v>
+        <v>-167.13905042468852</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12373,26 +12373,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0399296390923309E-2</v>
+        <v>4.0397298681609357E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0399296390923309E-2</v>
+        <v>4.0397298681609357E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4974862240320483E-2</v>
+        <v>4.4972815213587002E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6449385644107874E-2</v>
+        <v>4.6447774742755472E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.271028706243605E-2</v>
+        <v>8.2709347993214832E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12430,26 +12430,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373295249282335</v>
+        <v>0.11373495020213728</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582541519576785</v>
+        <v>0.1358274129050818</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520654119222356</v>
+        <v>0.13520858821895704</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9473659223234742E-2</v>
+        <v>9.9475270124587165E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6494926809070979E-2</v>
+        <v>-2.6493987739849754E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8433238123205837E-2</v>
+        <v>2.843373755053432E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12602,26 +12602,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6256698944894508E-2</v>
+        <v>7.6258197226879973E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5363953901669879E-2</v>
+        <v>9.536595161098381E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9611277233935485E-2</v>
+        <v>8.9613324260668981E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2144863557170017E-2</v>
+        <v>8.2146474458522425E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2368112112879195E-3</v>
+        <v>3.2358721420666964E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12709,26 +12709,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6256698944894508E-2</v>
+        <v>7.6258197226879973E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5363953901669879E-2</v>
+        <v>9.536595161098381E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9611277233935485E-2</v>
+        <v>8.9613324260668981E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2144863557170017E-2</v>
+        <v>8.2146474458522425E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2368112112879195E-3</v>
+        <v>3.2358721420666964E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12778,16 +12778,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83542163999999997</v>
+        <v>0.83851476000000003</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83542163999999997</v>
+        <v>0.83851476000000003</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.79808435999999994</v>
+        <v>0.80103924000000004</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12834,16 +12834,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1155.4416644449561</v>
+        <v>1159.7196476213651</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1155.4416644449561</v>
+        <v>1159.7196476213651</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1103.8018135200416</v>
+        <v>1107.8886019176171</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12889,16 +12889,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.2222599690191274</v>
+        <v>4.2378094779518367</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.3762820662465547</v>
+        <v>3.3887116472958403</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3450104124492359</v>
+        <v>3.3573185063113846</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12944,16 +12944,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.0537799999999996E-2</v>
+        <v>6.0065527220630369E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.0537799999999996E-2</v>
+        <v>6.0065527220630369E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.7832199999999993E-2</v>
+        <v>5.7381034383954158E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -13081,26 +13081,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265337875906505</v>
+        <v>-0.16265098650139975</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1011862994132713E-2</v>
+        <v>-2.1012285986942048E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815461485599987</v>
+        <v>0.73815278243149995</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3500051696292976</v>
+        <v>-6.3502814409026458</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82817410752320075</v>
+        <v>-0.82818019761011419</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13692,19 +13692,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.0385449733709</v>
+        <v>165.0350877747284</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88635862373829</v>
+        <v>161.88266067249469</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.3987039037272</v>
+        <v>117.39640170229814</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5918.1023046230657</v>
+        <v>-5919.8197728907608</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13800,24 +13800,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373295249282335</v>
+        <v>0.11373495020213728</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582541519576785</v>
+        <v>0.1358274129050818</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520654119222356</v>
+        <v>0.13520858821895704</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9473659223234742E-2</v>
+        <v>9.9475270124587165E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6494926809070979E-2</v>
+        <v>-2.6493987739849754E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14086,30 +14086,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5390835279177857</v>
+        <v>1.5448122836300864</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9247238949227798</v>
+        <v>1.931890588108357</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8558922805117612</v>
+        <v>1.8628062099616449</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3303677656874309</v>
+        <v>1.3353195925239227</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.67874630562302E-2</v>
+        <v>-3.6912955020112444E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2215716833129557</v>
+        <v>-1.226094510618565</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14143,30 +14143,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11152779187810041</v>
+        <v>0.11065990570416093</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13947274600889709</v>
+        <v>0.1383875779447247</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13448494786317111</v>
+        <v>0.13343884025513214</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.6403461281697883E-2</v>
+        <v>9.5653265940109075E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.665758192480449E-3</v>
+        <v>-2.6441944856814069E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.8519687196590993E-2</v>
+        <v>-8.7829119671816974E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14200,23 +14200,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9521872002802924E-2</v>
+        <v>1.9298125618816643E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3592858193403531E-2</v>
+        <v>2.3322452941903205E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7724769990735988E-2</v>
+        <v>1.7521620764481133E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2312506496668511E-3</v>
+        <v>1.2171388943698098E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.7483014330676772E-2</v>
+        <v>-6.6709570040353827E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.65478983364841</v>
+        <v>273.66016656838144</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.6848729206049</v>
+        <v>3420.7520821047679</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>327.05644365827135</v>
+        <v>326.69994506023733</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.7413165788762</v>
+        <v>1424.4520271650051</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7786</v>
+        <v>7.8074000000000003</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.0130002227383752</v>
+        <v>8.0410350421109609</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.738709628450355</v>
+        <v>16.799223164341644</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.08842504131326</v>
+        <v>304.0943997322654</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.56335651973444</v>
+        <v>281.56888864098647</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.90663887271148</v>
+        <v>337.91327801965588</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.70047914327114</v>
+        <v>289.70617114168027</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.48583632783954</v>
+        <v>375.49321382610725</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.07276292346148</v>
+        <v>298.07861941944446</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.24428307526534</v>
+        <v>417.25248103821838</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.68700396897395</v>
+        <v>306.69302971647659</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.64676085142781</v>
+        <v>463.655870524401</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.55019479460867</v>
+        <v>315.55639468496469</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.20974059516027</v>
+        <v>515.2198633710442</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.66952999739323</v>
+        <v>324.67590906329502</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.50713089569285</v>
+        <v>572.51837944346153</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.05241209671806</v>
+        <v>334.0589755163017</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.17666573576582</v>
+        <v>636.18916525451016</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.70645754324852</v>
+        <v>343.71321064429731</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.92700262700123</v>
+        <v>706.94089223942512</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.63950290149563</v>
+        <v>353.64645116576452</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.54561014151386</v>
+        <v>785.56104444240441</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.8596112110593</v>
+        <v>363.86676027872494</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.1053130164155</v>
+        <v>3801.1799966533176</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6472285132991</v>
+        <v>1760.6818214875786</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.1485396132639</v>
+        <v>4972.2462317595146</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15904,7 +15904,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.1485396132639</v>
+        <v>4972.2462317595146</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15934,19 +15934,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.684872920604</v>
+        <v>3420.7520821047674</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.0540732889604</v>
+        <v>3531.1234509932265</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.8540586195036</v>
+        <v>3761.9279710527189</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.7361877516005</v>
+        <v>4335.8213757483754</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.1301580422005</v>
+        <v>5077.2299128540262</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15955,19 +15955,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.684872920604</v>
+        <v>3420.7520821047665</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.5249062497737</v>
+        <v>3641.5964544710068</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.2563981753001</v>
+        <v>4152.3379811843542</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.8391691445477</v>
+        <v>5750.9521609058966</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.520946380122</v>
+        <v>8648.6908714268939</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15976,19 +15976,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.6848729206031</v>
+        <v>3420.752082104766</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.2631927304719</v>
+        <v>3778.33742756828</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.2698784026907</v>
+        <v>4689.3620125847492</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.5887428019614</v>
+        <v>8276.7513601717928</v>
       </c>
       <c r="F58" s="124">
-        <v>17364.194766450946</v>
+        <v>17364.535935955668</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15997,19 +15997,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.6848729206031</v>
+        <v>3420.752082104766</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.5775782711926</v>
+        <v>3917.654550340445</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.8562915326738</v>
+        <v>5301.9604617351733</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.682483416807</v>
+        <v>12134.920904124967</v>
       </c>
       <c r="F59" s="124">
-        <v>36349.818353920993</v>
+        <v>36350.53255055903</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16018,19 +16018,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.6848729206031</v>
+        <v>3420.7520821047656</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.1476873806555</v>
+        <v>4047.2272052270396</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.8282268655648</v>
+        <v>5943.9450104515336</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.656572765027</v>
+        <v>17689.004117254321</v>
       </c>
       <c r="F60" s="124">
-        <v>76383.703379203725</v>
+        <v>76385.204156556269</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16039,19 +16039,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.6848729206026</v>
+        <v>3420.7520821047651</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.4465478771899</v>
+        <v>4161.5283114531421</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.7185801314936</v>
+        <v>6585.8479754980181</v>
       </c>
       <c r="E61" s="124">
-        <v>25477.026815618279</v>
+        <v>25477.527385022011</v>
       </c>
       <c r="F61" s="124">
-        <v>159942.26400408198</v>
+        <v>159945.40652947567</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16101,23 +16101,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.0130002227383752</v>
+        <v>8.0410350421109609</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.0130002227383752</v>
+        <v>8.0410350421109609</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.0130002227383752</v>
+        <v>8.0410350421109609</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.0130002227383752</v>
+        <v>8.0410350421109609</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.0130002227383752</v>
+        <v>8.0410350421109609</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16128,23 +16128,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.0130002227383699</v>
+        <v>8.0410350421109573</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6337363639901099</v>
+        <v>8.6640816789599278</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9317967994819938</v>
+        <v>9.9669737372973888</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.159412630546077</v>
+        <v>13.206603355978528</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.329145044385694</v>
+        <v>17.391856290927791</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16155,23 +16155,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>8.0130002227383699</v>
+        <v>8.041035042110952</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2550441051361751</v>
+        <v>9.2877020433045505</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.127489447274309</v>
+        <v>12.170839162310909</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.118205130736524</v>
+        <v>21.195019965043802</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.415286191155218</v>
+        <v>37.552761798269934</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16182,23 +16182,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>8.0130002227383663</v>
+        <v>8.0410350421109484</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>10.024084707298035</v>
+        <v>10.059605157904956</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.147749396644116</v>
+        <v>15.202341082063564</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.323472894639238</v>
+        <v>35.453162382837</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.433796041940568</v>
+        <v>86.753727677738837</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16209,23 +16209,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>8.0130002227383663</v>
+        <v>8.0410350421109484</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.807613751748717</v>
+        <v>10.846050643476429</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.593045049783342</v>
+        <v>18.660460767684103</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>57.02208277079972</v>
+        <v>57.232538528678262</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>193.21234191897534</v>
+        <v>193.92972320162397</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16236,23 +16236,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>8.0130002227383663</v>
+        <v>8.0410350421109467</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.536339241122057</v>
+        <v>11.577488584925453</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.203610140410763</v>
+        <v>22.284465054438552</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.25862732605593</v>
+        <v>88.585351323966592</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>418.3700781984042</v>
+        <v>419.92553853555654</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16262,23 +16262,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>8.0130002227383628</v>
+        <v>8.0410350421109431</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.179176494425485</v>
+        <v>12.222718598283896</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.813716398888705</v>
+        <v>25.908008801184756</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>132.06181585196194</v>
+        <v>132.55158348066519</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>888.3183818712414</v>
+        <v>891.62307737355354</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.433796041940568</v>
+        <v>86.753727677738837</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.118205130736524</v>
+        <v>21.195019965043802</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.127489447274309</v>
+        <v>12.170839162310909</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2550441051361751</v>
+        <v>9.2877020433045505</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>8.0130002227383663</v>
+        <v>8.0410350421109484</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-13.8</v>
+        <v>-13.96</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83542163999999997</v>
+        <v>0.83851476000000003</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83542163999999997</v>
+        <v>0.83851476000000003</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.57379061721916</v>
+        <v>17.637396005143085</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.2230849715325</v>
+        <v>342.23025395117651</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.65478983364841</v>
+        <v>273.66016656838144</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7401544173595855</v>
+        <v>-4.7405423062634977</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>13.8</v>
+        <v>13.96</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.0130002227383752</v>
+        <v>8.0410350421109609</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.127489447274309</v>
+        <v>12.170839162310909</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2550441051361751</v>
+        <v>9.2877020433045505</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.118205130736524</v>
+        <v>21.195019965043802</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.351143515539125</v>
+        <v>13.399047899056217</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>8.0130002227383663</v>
+        <v>8.0410350421109484</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.433796041940568</v>
+        <v>86.753727677738837</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.73836897721916</v>
+        <v>16.798881245143086</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.738709628450355</v>
+        <v>16.799223164341644</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67064741442322484</v>
+        <v>-0.67082553527326483</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83542163999999997</v>
+        <v>0.83851476000000003</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.3274192239067051</v>
+        <v>1.3323339481049561</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>6.0999886943218531</v>
+        <v>6.1220412700958784</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>7.4274079182285586</v>
+        <v>7.454375218200834</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.55626453638719364</v>
+        <v>0.55625763945702911</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>13.8</v>
+        <v>13.96</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12343060589714883</v>
+        <v>0.12031246204964541</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7598002138888889</v>
+        <v>1.7663158138888888</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>9.6865561210759026</v>
+        <v>9.72157479464299</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17404,7 +17404,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>11.446356334964792</v>
+        <v>11.487890608531879</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31616059183883283</v>
+        <v>0.31615144836783271</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.1529625915256831</v>
+        <v>2.1609338617588794</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>13.28745695620837</v>
+        <v>13.335493545463633</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>15.440419547734052</v>
+        <v>15.496427407222512</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.7543363469380511E-2</v>
+        <v>7.7532177227405574E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0490DC-8420-4258-9CB1-D55519FA4E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A52216-BE5E-4352-9109-FE9E126664E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4254,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>7.8074000000000003</v>
+        <v>7.8068999999999997</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>7.454375218200834</v>
+        <v>7.4539070694150338</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12031246204964541</v>
+        <v>0.12028775104137335</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0302539511766549</v>
+        <v>7.0301294897245015</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.96974604882334</v>
+        <v>-144.96987051027548</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03731057384746</v>
+        <v>-102.03727945848443</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.23025395117651</v>
+        <v>342.23012948972439</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.66016656838144</v>
+        <v>273.66007322229234</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11065990570416093</v>
+        <v>0.1106527810999718</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.0065527220630369E-2</v>
+        <v>6.0061680515759309E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.310153545376078</v>
+        <v>19.308910301945076</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.113340461173699</v>
+        <v>13.11250065916143</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>326.69994506023733</v>
+        <v>326.70613427200874</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8442219579085819</v>
+        <v>1.8441387864803258</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.0410350421109609</v>
+        <v>8.0405484292639748</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-12.211494885591646</v>
+        <v>-12.210712839399212</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>21.2 HKD</v>
+        <v>21.19 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>16.798881245143086</v>
+        <v>16.79783077687485</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83851476000000003</v>
+        <v>0.83846105999999998</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>1.3323339481049561</v>
+        <v>1.3322486230320696</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>6.1220412700958784</v>
+        <v>6.1216584463829644</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>7.454375218200834</v>
+        <v>7.4539070694150338</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55625763945702911</v>
+        <v>0.5562577592056327</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>1.7663158138888888</v>
+        <v>1.7662026958333332</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>9.72157479464299</v>
+        <v>9.7209668847655379</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>11.487890608531879</v>
+        <v>11.487169580598872</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31615144836783271</v>
+        <v>0.31615160712221435</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>2.1609338617588794</v>
+        <v>2.1607954716506641</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>13.335493545463633</v>
+        <v>13.334659649884138</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>15.496427407222512</v>
+        <v>15.495455121534802</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7532177227405574E-2</v>
+        <v>7.7532371449591908E-2</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5539,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5566,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6114,11 +6114,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83851476000000003</v>
+        <v>0.83846105999999998</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.80103924000000004</v>
+        <v>0.80098793999999995</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -7449,11 +7449,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83851476000000003</v>
+        <v>0.83846105999999998</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.80103924000000004</v>
+        <v>0.80098793999999995</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8800,11 +8800,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.3331524704195505</v>
+        <v>8.332618800281578</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.211494885591646</v>
+        <v>-12.210712839399212</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>326.69994506023733</v>
+        <v>326.70613427200874</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9062,11 +9062,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.99330396844704</v>
+        <v>-342.98711475667568</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.60005493976263</v>
+        <v>-349.59386572799121</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9078,11 +9078,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9717586092065948</v>
+        <v>1.9717941896440787</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9344962634989544</v>
+        <v>1.9345305118317186</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9095,7 +9095,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.60005493976263</v>
+        <v>349.59386572799121</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9210,11 +9210,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18136.590200000002</v>
+        <v>-18135.4287</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-13.113340461173703</v>
+        <v>-13.11250065916143</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9227,11 +9227,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2550.6771510632971</v>
+        <v>2550.5621196481447</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8442219579085819</v>
+        <v>1.8441387864803258</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9261,11 +9261,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15585.913048936705</v>
+        <v>-15584.866580351856</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.269118503265121</v>
+        <v>-11.268361872681105</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9845,24 +9845,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.96974604882334</v>
+        <v>-144.96987051027548</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.96974604882334</v>
+        <v>-144.96987051027548</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.60789474251277</v>
+        <v>-165.60802561006909</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75101214923865</v>
+        <v>-133.75109268311945</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.13905042468852</v>
+        <v>-167.13908337036705</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9900,24 +9900,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.14924229538985</v>
+        <v>408.14911783393774</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.4302539511765</v>
+        <v>487.43012948972438</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.89210525748746</v>
+        <v>497.89197438993114</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44898785076117</v>
+        <v>286.44890731688037</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.539050424688384</v>
+        <v>-53.53908337036691</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03731057384746</v>
+        <v>-102.03727945848443</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10067,26 +10067,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.66016656838144</v>
+        <v>273.66007322229234</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.23025395117651</v>
+        <v>342.23012948972439</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.99210525748748</v>
+        <v>329.99197438993116</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54898785076116</v>
+        <v>236.54890731688036</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.53905042468838</v>
+        <v>-6.5390833703669067</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10175,26 +10175,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.66016656838144</v>
+        <v>273.66007322229234</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.23025395117651</v>
+        <v>342.23012948972439</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.99210525748748</v>
+        <v>329.99197438993116</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54898785076116</v>
+        <v>236.54890731688036</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.53905042468838</v>
+        <v>-6.5390833703669067</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11036,19 +11036,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270138966763752</v>
+        <v>0.24270145163952961</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27033969524459706</v>
+        <v>0.27033976630156747</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4831858483159342E-2</v>
+        <v>8.483188233327224E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.049701097688587</v>
+        <v>1.0497004517471038</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11174,24 +11174,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0302539511766549</v>
+        <v>7.0301294897245015</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.0302539511766557</v>
+        <v>7.0301294897245015</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.392105257487219</v>
+        <v>7.39197438993091</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5489878507613657</v>
+        <v>4.5489073168805607</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8609495753114678</v>
+        <v>1.8609166296329565</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11286,24 +11286,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.96974604882334</v>
+        <v>-144.96987051027548</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.96974604882334</v>
+        <v>-144.96987051027548</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.60789474251277</v>
+        <v>-165.60802561006909</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75101214923865</v>
+        <v>-133.75109268311945</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.13905042468852</v>
+        <v>-167.13908337036705</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12373,26 +12373,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0397298681609357E-2</v>
+        <v>4.0397333364062725E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0397298681609357E-2</v>
+        <v>4.0397333364062725E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4972815213587002E-2</v>
+        <v>4.4972850752245573E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6447774742755472E-2</v>
+        <v>4.6447802709792839E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2709347993214832E-2</v>
+        <v>8.2709364296499929E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12430,26 +12430,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373495020213728</v>
+        <v>0.11373491551968393</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.1358274129050818</v>
+        <v>0.13582737822262844</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520858821895704</v>
+        <v>0.13520855268029849</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9475270124587165E-2</v>
+        <v>9.9475242157549784E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6493987739849754E-2</v>
+        <v>-2.6494004043134855E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.843373755053432E-2</v>
+        <v>2.8433728879920982E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12602,26 +12602,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6258197226879973E-2</v>
+        <v>7.6258171215039944E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.536595161098381E-2</v>
+        <v>9.5365916928530456E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9613324260668981E-2</v>
+        <v>8.9613288722010409E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2146474458522425E-2</v>
+        <v>8.2146446491485059E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2358721420666964E-3</v>
+        <v>3.2358884453517946E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12709,26 +12709,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6258197226879973E-2</v>
+        <v>7.6258171215039944E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.536595161098381E-2</v>
+        <v>9.5365916928530456E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9613324260668981E-2</v>
+        <v>8.9613288722010409E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2146474458522425E-2</v>
+        <v>8.2146446491485059E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2358721420666964E-3</v>
+        <v>3.2358884453517946E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12778,16 +12778,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83851476000000003</v>
+        <v>0.83846105999999998</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83851476000000003</v>
+        <v>0.83846105999999998</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.80103924000000004</v>
+        <v>0.80098793999999995</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12834,16 +12834,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1159.7196476213651</v>
+        <v>1159.6453770801079</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1159.7196476213651</v>
+        <v>1159.6453770801079</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1107.8886019176171</v>
+        <v>1107.8176507301591</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12889,16 +12889,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.2378094779518367</v>
+        <v>4.237539526411422</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.3887116472958403</v>
+        <v>3.3884958604000612</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3573185063113846</v>
+        <v>3.357104828922655</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12944,16 +12944,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.0065527220630369E-2</v>
+        <v>6.0061680515759309E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.0065527220630369E-2</v>
+        <v>6.0061680515759309E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.7381034383954158E-2</v>
+        <v>5.7377359598853858E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -13081,26 +13081,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265098650139975</v>
+        <v>-0.16265102803305065</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1012285986942048E-2</v>
+        <v>-2.101227864342603E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815278243149995</v>
+        <v>0.7381528142439191</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3502814409026458</v>
+        <v>-6.350276644359317</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82818019761011419</v>
+        <v>-0.82818009187943864</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13692,19 +13692,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.0350877747284</v>
+        <v>165.03514779430265</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88266067249469</v>
+        <v>161.88272487159605</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.39640170229814</v>
+        <v>117.39644167030276</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5919.8197728907608</v>
+        <v>-5919.7899472304771</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13800,24 +13800,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373495020213728</v>
+        <v>0.11373491551968393</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.1358274129050818</v>
+        <v>0.13582737822262844</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520858821895704</v>
+        <v>0.13520855268029849</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9475270124587165E-2</v>
+        <v>9.9475242157549784E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6493987739849754E-2</v>
+        <v>-2.6494004043134855E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14086,30 +14086,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5448122836300864</v>
+        <v>1.5447128241556065</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.931890588108357</v>
+        <v>1.9317661638049559</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8628062099616449</v>
+        <v>1.8626861737864633</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3353195925239227</v>
+        <v>1.3352336216601419</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.6912955020112444E-2</v>
+        <v>-3.6910777014312363E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.226094510618565</v>
+        <v>-1.2260159893111759</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14143,30 +14143,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11065990570416093</v>
+        <v>0.1106527810999718</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1383875779447247</v>
+        <v>0.13837866502900831</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13343884025513214</v>
+        <v>0.13343024167524808</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.5653265940109075E-2</v>
+        <v>9.5647107568778075E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.6441944856814069E-3</v>
+        <v>-2.6440384680739512E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.7829119671816974E-2</v>
+        <v>-8.7823494936330654E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.66016656838144</v>
+        <v>273.66007322229234</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.7520821047679</v>
+        <v>3420.7509152786542</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>326.69994506023733</v>
+        <v>326.70613427200874</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.4520271650051</v>
+        <v>1424.457049550663</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.8074000000000003</v>
+        <v>7.8068999999999997</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.0410350421109609</v>
+        <v>8.0405484292639748</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.799223164341644</v>
+        <v>16.798172674059668</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.0943997322654</v>
+        <v>304.09429600499192</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.56888864098647</v>
+        <v>281.56879259721472</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.91327801965588</v>
+        <v>337.91316275668811</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.70617114168027</v>
+        <v>289.70607232226342</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.49321382610725</v>
+        <v>375.49308574454005</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.07861941944446</v>
+        <v>298.0785177441669</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.25248103821838</v>
+        <v>417.25233871247264</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.69302971647659</v>
+        <v>306.69292510280462</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.655870524401</v>
+        <v>463.6557123703563</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.55639468496469</v>
+        <v>315.55628704797931</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.2198633710442</v>
+        <v>515.21968762840731</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.67590906329502</v>
+        <v>324.67579831562307</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.51837944346153</v>
+        <v>572.5181841561739</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.0589755163017</v>
+        <v>334.05886156804507</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.18916525451016</v>
+        <v>636.18894824897632</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.71321064429731</v>
+        <v>343.7130934029596</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.94089223942512</v>
+        <v>706.94065110032057</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.64645116576452</v>
+        <v>353.64633053617655</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.56104444240441</v>
+        <v>785.56077648579173</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.86676027872494</v>
+        <v>363.86663616296687</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.1799966533176</v>
+        <v>3801.178700062399</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6818214875786</v>
+        <v>1760.6812209151083</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.2462317595146</v>
+        <v>4972.2445357153092</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15904,7 +15904,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.2462317595146</v>
+        <v>4972.2445357153092</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15934,19 +15934,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.7520821047674</v>
+        <v>3420.7509152786538</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.1234509932265</v>
+        <v>3531.1222465191945</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.9279710527189</v>
+        <v>3761.9266878507538</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.8213757483754</v>
+        <v>4335.8198967900989</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.2299128540262</v>
+        <v>5077.2281809996539</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15955,19 +15955,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.7520821047665</v>
+        <v>3420.7509152786533</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.5964544710068</v>
+        <v>3641.5952123143888</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.3379811843542</v>
+        <v>4152.3365648126692</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.9521609058966</v>
+        <v>5750.9501992433734</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.6908714268939</v>
+        <v>8648.6879213392749</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15976,19 +15976,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.752082104766</v>
+        <v>3420.7509152786524</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.33742756828</v>
+        <v>3778.3361387690129</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.3620125847492</v>
+        <v>4689.3604130329786</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.7513601717928</v>
+        <v>8276.7485369535661</v>
       </c>
       <c r="F58" s="124">
-        <v>17364.535935955668</v>
+        <v>17364.530012873984</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15997,19 +15997,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.752082104766</v>
+        <v>3420.7509152786524</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.654550340445</v>
+        <v>3917.6532140197992</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.9604617351733</v>
+        <v>5301.9586532247149</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.920904124967</v>
+        <v>12134.91676487656</v>
       </c>
       <c r="F59" s="124">
-        <v>36350.53255055903</v>
+        <v>36350.520151311845</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16018,19 +16018,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.7520821047656</v>
+        <v>3420.7509152786524</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.2272052270396</v>
+        <v>4047.2258247088748</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.9450104515336</v>
+        <v>5943.9429829587243</v>
       </c>
       <c r="E60" s="124">
-        <v>17689.004117254321</v>
+        <v>17688.998083495826</v>
       </c>
       <c r="F60" s="124">
-        <v>76385.204156556269</v>
+        <v>76385.178101393903</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16039,19 +16039,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.7520821047651</v>
+        <v>3420.7509152786524</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.5283114531421</v>
+        <v>4161.5268919466162</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.8479754980181</v>
+        <v>6585.8457290506849</v>
       </c>
       <c r="E61" s="124">
-        <v>25477.527385022011</v>
+        <v>25477.518694580973</v>
       </c>
       <c r="F61" s="124">
-        <v>159945.40652947567</v>
+        <v>159945.35197174316</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16101,23 +16101,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.0410350421109609</v>
+        <v>8.0405484292639748</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.0410350421109609</v>
+        <v>8.0405484292639748</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.0410350421109609</v>
+        <v>8.0405484292639748</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.0410350421109609</v>
+        <v>8.0405484292639748</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.0410350421109609</v>
+        <v>8.0405484292639748</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16128,23 +16128,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.0410350421109573</v>
+        <v>8.0405484292639731</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6640816789599278</v>
+        <v>8.663554952571813</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9669737372973888</v>
+        <v>9.9663631269572885</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.206603355978528</v>
+        <v>13.205784168931215</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.391856290927791</v>
+        <v>17.390767645214272</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16155,23 +16155,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>8.041035042110952</v>
+        <v>8.0405484292639695</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2877020433045505</v>
+        <v>9.2871351664370749</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.170839162310909</v>
+        <v>12.170086660752489</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.195019965043802</v>
+        <v>21.193686460673739</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.552761798269934</v>
+        <v>37.550375135258086</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16182,23 +16182,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>8.0410350421109484</v>
+        <v>8.0405484292639642</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>10.059605157904956</v>
+        <v>10.058988583686581</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.202341082063564</v>
+        <v>15.201393403660029</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.453162382837</v>
+        <v>35.450910898096787</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.753727677738837</v>
+        <v>86.748173314507255</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16209,23 +16209,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>8.0410350421109484</v>
+        <v>8.0405484292639642</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.846050643476429</v>
+        <v>10.845383435627337</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.660460767684103</v>
+        <v>18.659290445552099</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>57.232538528678262</v>
+        <v>57.228884824827716</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>193.92972320162397</v>
+        <v>193.9172685383983</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16236,23 +16236,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>8.0410350421109467</v>
+        <v>8.0405484292639642</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.577488584925453</v>
+        <v>11.576774284990135</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.284465054438552</v>
+        <v>22.283061408448571</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.585351323966592</v>
+        <v>88.579679035517046</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>419.92553853555654</v>
+        <v>419.89853360932096</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16262,23 +16262,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>8.0410350421109431</v>
+        <v>8.0405484292639642</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.222718598283896</v>
+        <v>12.221962756577623</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.908008801184756</v>
+        <v>25.906371860987687</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>132.55158348066519</v>
+        <v>132.54308051926495</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>891.62307737355354</v>
+        <v>891.56570319804177</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.753727677738837</v>
+        <v>86.748173314507255</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.195019965043802</v>
+        <v>21.193686460673739</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.170839162310909</v>
+        <v>12.170086660752489</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2877020433045505</v>
+        <v>9.2871351664370749</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>8.0410350421109484</v>
+        <v>8.0405484292639642</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83851476000000003</v>
+        <v>0.83846105999999998</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83851476000000003</v>
+        <v>0.83846105999999998</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.637396005143085</v>
+        <v>17.63629183687485</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.23025395117651</v>
+        <v>342.23012948972439</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.66016656838144</v>
+        <v>273.66007322229234</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7405423062634977</v>
+        <v>-4.7405355708471459</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.0410350421109609</v>
+        <v>8.0405484292639748</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.170839162310909</v>
+        <v>12.170086660752489</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2877020433045505</v>
+        <v>9.2871351664370749</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.195019965043802</v>
+        <v>21.193686460673739</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.399047899056217</v>
+        <v>13.398216321873655</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>8.0410350421109484</v>
+        <v>8.0405484292639642</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.753727677738837</v>
+        <v>86.748173314507255</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.798881245143086</v>
+        <v>16.79783077687485</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.799223164341644</v>
+        <v>16.798172674059668</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67082553527326483</v>
+        <v>-0.67082244263312707</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83851476000000003</v>
+        <v>0.83846105999999998</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.3323339481049561</v>
+        <v>1.3322486230320696</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>6.1220412700958784</v>
+        <v>6.1216584463829644</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>7.454375218200834</v>
+        <v>7.4539070694150338</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.55625763945702911</v>
+        <v>0.5562577592056327</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17356,7 +17356,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12031246204964541</v>
+        <v>0.12028775104137335</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7663158138888888</v>
+        <v>1.7662026958333332</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>9.72157479464299</v>
+        <v>9.7209668847655379</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17404,7 +17404,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>11.487890608531879</v>
+        <v>11.487169580598872</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31615144836783271</v>
+        <v>0.31615160712221435</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.1609338617588794</v>
+        <v>2.1607954716506641</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>13.335493545463633</v>
+        <v>13.334659649884138</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>15.496427407222512</v>
+        <v>15.495455121534802</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.7532177227405574E-2</v>
+        <v>7.7532371449591908E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A52216-BE5E-4352-9109-FE9E126664E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39810BCA-C2EE-43D0-A186-76DE4DE63A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2374,6 +2374,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -4094,7 +4106,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4116,7 +4128,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4159,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4194,10 +4206,10 @@
         <v>426</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4206,7 +4218,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>13.96</v>
+        <v>13.98</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4227,7 +4239,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>19307.574598679999</v>
+        <v>19335.235880339998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4254,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>7.8068999999999997</v>
+        <v>7.8139000000000003</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4294,7 +4306,7 @@
         <v>355</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D22" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4310,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4335,7 +4347,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>7.4539070694150338</v>
+        <v>7.4604610446780413</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,10 +4362,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12028775104137335</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.12006981785810078</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4494,7 +4510,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>7.0301294897245015</v>
+        <v>7.0318719500546489</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4524,7 +4540,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.96987051027548</v>
+        <v>-144.96812804994536</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4564,7 +4580,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03727945848443</v>
+        <v>-102.03771507356697</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4617,7 +4633,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.23012948972439</v>
+        <v>342.23187195005454</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4630,7 +4646,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.66007322229234</v>
+        <v>273.66138006753994</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4643,7 +4659,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.1106527810999718</v>
+        <v>0.11059408175537334</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4668,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.0061680515759309E-2</v>
+        <v>6.0029532188841196E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4709,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4721,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4774,7 +4790,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.308910301945076</v>
+        <v>19.326315786751493</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4841,7 +4857,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.11250065916143</v>
+        <v>13.124257887333194</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4899,7 +4915,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>326.70613427200874</v>
+        <v>326.61948530720883</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4912,7 +4928,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8441387864803258</v>
+        <v>1.8453027792509011</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4965,7 +4981,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.0405484292639748</v>
+        <v>8.0473606786692038</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4978,7 +4994,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-12.210712839399212</v>
+        <v>-12.221661486093266</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5036,7 +5052,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.75 HKD</v>
+        <v>86.83 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5058,7 +5074,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>21.19 HKD</v>
+        <v>21.21 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5080,7 +5096,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>12.17 HKD</v>
+        <v>12.18 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5102,7 +5118,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>9.29 HKD</v>
+        <v>9.3 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5124,7 +5140,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>8.04 HKD</v>
+        <v>8.05 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5137,7 +5153,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>16.79783077687485</v>
+        <v>16.812537036996542</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5210,7 +5226,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83846105999999998</v>
+        <v>0.83921285999999995</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5246,7 +5262,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>1.3322486230320696</v>
+        <v>1.3334431740524777</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5272,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>6.1216584463829644</v>
+        <v>6.1270178706255631</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5281,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>7.4539070694150338</v>
+        <v>7.4604610446780413</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5307,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5562577592056327</v>
+        <v>0.556256082692276</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5308,40 +5324,40 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>1.7662026958333332</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+        <v>1.7677863486111107</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>9.7209668847655379</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>9.7294774519655913</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>11.487169580598872</v>
+        <v>11.497263800576702</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>425</v>
       </c>
@@ -5354,21 +5370,21 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31615160712221435</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>0.31614938451724484</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5377,40 +5393,40 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>2.1607954716506641</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+        <v>2.1627329331656768</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>13.334659649884138</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>13.346333953313566</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>15.495455121534802</v>
+        <v>15.509066886479243</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>425</v>
       </c>
@@ -5423,127 +5439,196 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7532371449591908E-2</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+        <v>7.7529652285611039E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>2.0246875693639139</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>12.050560654213566</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>14.07524822357748</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.1628293987800582</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6114,11 +6199,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83846105999999998</v>
+        <v>0.83921285999999995</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.80098793999999995</v>
+        <v>0.80170613999999996</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -6141,7 +6226,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7449,11 +7534,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83846105999999998</v>
+        <v>0.83921285999999995</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.80098793999999995</v>
+        <v>0.80170613999999996</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8800,11 +8885,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.332618800281578</v>
+        <v>8.3400901822131992</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.210712839399212</v>
+        <v>-12.221661486093266</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8995,7 +9080,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>326.70613427200874</v>
+        <v>326.61948530720883</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9062,11 +9147,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-342.98711475667568</v>
+        <v>-343.07376372147559</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.59386572799121</v>
+        <v>-349.68051469279112</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9078,11 +9163,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>1.9717941896440787</v>
+        <v>1.9712961803428783</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>1.9345305118317186</v>
+        <v>1.9340511454982203</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9095,7 +9180,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.59386572799121</v>
+        <v>349.68051469279112</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9210,11 +9295,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18135.4287</v>
+        <v>-18151.689699999999</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-13.11250065916143</v>
+        <v>-13.124257887333194</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9227,11 +9312,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2550.5621196481447</v>
+        <v>2552.1719962419993</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8441387864803258</v>
+        <v>1.8453027792509011</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9261,11 +9346,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15584.866580351856</v>
+        <v>-15599.517703758</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-11.268361872681105</v>
+        <v>-11.278955108082293</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9845,24 +9930,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.96987051027548</v>
+        <v>-144.96812804994536</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.96987051027548</v>
+        <v>-144.96812804994536</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.60802561006909</v>
+        <v>-165.60619346428078</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.75109268311945</v>
+        <v>-133.74996520878818</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.13908337036705</v>
+        <v>-167.13862213086787</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9900,24 +9985,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.14911783393774</v>
+        <v>408.15086029426789</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.43012948972438</v>
+        <v>487.43187195005453</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.89197438993114</v>
+        <v>497.89380653571948</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.44890731688037</v>
+        <v>286.45003479121164</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.53908337036691</v>
+        <v>-53.538622130867736</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9955,7 +10040,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03727945848443</v>
+        <v>-102.03771507356697</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10067,26 +10152,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.66007322229234</v>
+        <v>273.66138006753994</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.23012948972439</v>
+        <v>342.23187195005454</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.99197438993116</v>
+        <v>329.99380653571944</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.54890731688036</v>
+        <v>236.55003479121163</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5390833703669067</v>
+        <v>-6.5386221308677328</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10175,26 +10260,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.66007322229234</v>
+        <v>273.66138006753994</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.23012948972439</v>
+        <v>342.23187195005454</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.99197438993116</v>
+        <v>329.99380653571944</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.54890731688036</v>
+        <v>236.55003479121163</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5390833703669067</v>
+        <v>-6.5386221308677328</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11036,19 +11121,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270145163952961</v>
+        <v>0.24270058403591999</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27033976630156747</v>
+        <v>0.27033877150738095</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.483188233327224E-2</v>
+        <v>8.4831548432912018E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0497004517471038</v>
+        <v>1.0497094950002055</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11174,24 +11259,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0301294897245015</v>
+        <v>7.0318719500546489</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.0301294897245015</v>
+        <v>7.0318719500546489</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.39197438993091</v>
+        <v>7.3938065357192277</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>4.5489073168805607</v>
+        <v>4.5500347912118322</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>1.8609166296329565</v>
+        <v>1.8613778691321132</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11286,24 +11371,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.96987051027548</v>
+        <v>-144.96812804994536</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.96987051027548</v>
+        <v>-144.96812804994536</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.60802561006909</v>
+        <v>-165.60619346428078</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.75109268311945</v>
+        <v>-133.74996520878818</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.13908337036705</v>
+        <v>-167.13862213086787</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -11929,7 +12014,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12261,7 +12346,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12373,26 +12458,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0397333364062725E-2</v>
+        <v>4.0396847809715593E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0397333364062725E-2</v>
+        <v>4.0396847809715593E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4972850752245573E-2</v>
+        <v>4.4972353211025627E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6447802709792839E-2</v>
+        <v>4.6447411171269687E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2709364296499929E-2</v>
+        <v>8.2709136050508641E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12430,26 +12515,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373491551968393</v>
+        <v>0.11373540107403107</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582737822262844</v>
+        <v>0.13582786377697556</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520855268029849</v>
+        <v>0.13520905022151844</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9475242157549784E-2</v>
+        <v>9.9475633696072943E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6494004043134855E-2</v>
+        <v>-2.6493775797143574E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12487,7 +12572,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8433728879920982E-2</v>
+        <v>2.8433850268507768E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12602,26 +12687,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6258171215039944E-2</v>
+        <v>7.6258535380800296E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5365916928530456E-2</v>
+        <v>9.5366402482877602E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9613288722010409E-2</v>
+        <v>8.9613786263230355E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2146446491485059E-2</v>
+        <v>8.2146838030008204E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2358884453517946E-3</v>
+        <v>3.2356601993605173E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12709,26 +12794,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6258171215039944E-2</v>
+        <v>7.6258535380800296E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5365916928530456E-2</v>
+        <v>9.5366402482877602E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9613288722010409E-2</v>
+        <v>8.9613786263230355E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2146446491485059E-2</v>
+        <v>8.2146838030008204E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2358884453517946E-3</v>
+        <v>3.2356601993605173E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12778,16 +12863,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83846105999999998</v>
+        <v>0.83921285999999995</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83846105999999998</v>
+        <v>0.83921285999999995</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.80098793999999995</v>
+        <v>0.80170613999999996</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12834,16 +12919,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1159.6453770801079</v>
+        <v>1160.6851646577072</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1159.6453770801079</v>
+        <v>1160.6851646577072</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1107.8176507301591</v>
+        <v>1108.8109673545696</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12889,16 +12974,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.237539526411422</v>
+        <v>4.2413188312185257</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.3884958604000612</v>
+        <v>3.3915168626582455</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.357104828922655</v>
+        <v>3.3600962969423147</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12944,16 +13029,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.0061680515759309E-2</v>
+        <v>6.0029532188841196E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.0061680515759309E-2</v>
+        <v>6.0029532188841196E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.7377359598853858E-2</v>
+        <v>5.7346648068669522E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -13081,26 +13166,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265102803305065</v>
+        <v>-0.16265044659186811</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.101227864342603E-2</v>
+        <v>-2.1012381452297446E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.7381528142439191</v>
+        <v>0.73815236887167934</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.350276644359317</v>
+        <v>-6.3503437965030978</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82818009187943864</v>
+        <v>-0.82818157210889676</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13692,19 +13777,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.03514779430265</v>
+        <v>165.03430752423526</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88272487159605</v>
+        <v>161.88182608881075</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.39644167030276</v>
+        <v>117.39588212071452</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5919.7899472304771</v>
+        <v>-5920.2075338253017</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13800,24 +13885,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373491551968393</v>
+        <v>0.11373540107403107</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582737822262844</v>
+        <v>0.13582786377697556</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520855268029849</v>
+        <v>0.13520905022151844</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9475242157549784E-2</v>
+        <v>9.9475633696072943E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6494004043134855E-2</v>
+        <v>-2.6493775797143574E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14086,30 +14171,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5447128241556065</v>
+        <v>1.5461052629401195</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.9317661638049559</v>
+        <v>1.93350811224163</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8626861737864633</v>
+        <v>1.8643666888495565</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3352336216601419</v>
+        <v>1.3364372190518727</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.6910777014312363E-2</v>
+        <v>-3.6941266927822736E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2260159893111759</v>
+        <v>-1.2271152876146227</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14143,30 +14228,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1106527810999718</v>
+        <v>0.11059408175537334</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13837866502900831</v>
+        <v>0.13830530130483762</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13343024167524808</v>
+        <v>0.13335956286477513</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.5647107568778075E-2</v>
+        <v>9.559636760027701E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.6440384680739512E-3</v>
+        <v>-2.6424368331775918E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.7823494936330654E-2</v>
+        <v>-8.7776486953835678E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14200,23 +14285,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9298125618816643E-2</v>
+        <v>1.9270517427659541E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3322452941903205E-2</v>
+        <v>2.3289087487050698E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7521620764481133E-2</v>
+        <v>1.7496554068108485E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2171388943698098E-3</v>
+        <v>1.2153976370101963E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.6709570040353827E-2</v>
+        <v>-6.6614134317835444E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14986,7 +15071,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.66007322229234</v>
+        <v>273.66138006753994</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15018,7 +15103,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.7509152786542</v>
+        <v>3420.7672508442492</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15052,7 +15137,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>326.70613427200874</v>
+        <v>326.61948530720883</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15084,7 +15169,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.457049550663</v>
+        <v>1424.3867361514581</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15098,7 +15183,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.8068999999999997</v>
+        <v>7.8139000000000003</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15112,7 +15197,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.0405484292639748</v>
+        <v>8.0473606786692038</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15165,7 +15250,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.798172674059668</v>
+        <v>16.812879242375146</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15200,7 +15285,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.09429600499192</v>
+        <v>304.09574818682057</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15212,7 +15297,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.56879259721472</v>
+        <v>281.57013721001903</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15222,7 +15307,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.91316275668811</v>
+        <v>337.91477643823708</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15234,7 +15319,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.70607232226342</v>
+        <v>289.70745579409902</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15244,7 +15329,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.49308574454005</v>
+        <v>375.49487888648014</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15256,7 +15341,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.0785177441669</v>
+        <v>298.0799411980517</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15266,7 +15351,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.25233871247264</v>
+        <v>417.25433127291262</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15278,7 +15363,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.69292510280462</v>
+        <v>306.69438969421151</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15288,7 +15373,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.6557123703563</v>
+        <v>463.65792652698173</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15300,7 +15385,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.55628704797931</v>
+        <v>315.55779396577418</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15310,7 +15395,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.21968762840731</v>
+        <v>515.22214802532358</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15322,7 +15407,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.67579831562307</v>
+        <v>324.6773487830298</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15332,7 +15417,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.5181841561739</v>
+        <v>572.52091817820099</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15344,7 +15429,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.05886156804507</v>
+        <v>334.06045684363829</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15354,7 +15439,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.18894824897632</v>
+        <v>636.19198632644895</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15366,7 +15451,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.7130934029596</v>
+        <v>343.71473478168679</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15376,7 +15461,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.94065110032057</v>
+        <v>706.94402704778474</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15388,7 +15473,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.64633053617655</v>
+        <v>353.64801935040856</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15398,7 +15483,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.56077648579173</v>
+        <v>785.56452787836929</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15410,7 +15495,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.86663616296687</v>
+        <v>363.86837378358007</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15860,7 +15945,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.178700062399</v>
+        <v>3801.1968523352571</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15872,7 +15957,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6812209151083</v>
+        <v>1760.6896289296901</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15883,7 +15968,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.2445357153092</v>
+        <v>4972.2682803341886</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15904,7 +15989,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.2445357153092</v>
+        <v>4972.2682803341886</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15934,19 +16019,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.7509152786538</v>
+        <v>3420.7672508442483</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.1222465191945</v>
+        <v>3531.1391091556479</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.9266878507538</v>
+        <v>3761.9446526782708</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.8198967900989</v>
+        <v>4335.8406022059808</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.2281809996539</v>
+        <v>5077.2524269608612</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15955,19 +16040,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.7509152786533</v>
+        <v>3420.7672508442483</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.5952123143888</v>
+        <v>3641.6126025070498</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.3365648126692</v>
+        <v>4152.3563940162576</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.9501992433734</v>
+        <v>5750.9776625187005</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.6879213392749</v>
+        <v>8648.7292225659221</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15976,19 +16061,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.7509152786524</v>
+        <v>3420.7672508442474</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.3361387690129</v>
+        <v>3778.3541819587581</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.3604130329786</v>
+        <v>4689.3828067577833</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.7485369535661</v>
+        <v>8276.7880620087344</v>
       </c>
       <c r="F58" s="124">
-        <v>17364.530012873984</v>
+        <v>17364.612936017496</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15997,19 +16082,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.7509152786524</v>
+        <v>3420.7672508442474</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.6532140197992</v>
+        <v>3917.6719225088536</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.9586532247149</v>
+        <v>5301.9839723711548</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.91676487656</v>
+        <v>12134.974714354237</v>
       </c>
       <c r="F59" s="124">
-        <v>36350.520151311845</v>
+        <v>36350.693740772476</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16018,19 +16103,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.7509152786524</v>
+        <v>3420.7672508442474</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.2258247088748</v>
+        <v>4047.2451519632036</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.9429829587243</v>
+        <v>5943.9713678580911</v>
       </c>
       <c r="E60" s="124">
-        <v>17688.998083495826</v>
+        <v>17689.082556114754</v>
       </c>
       <c r="F60" s="124">
-        <v>76385.178101393903</v>
+        <v>76385.542873667073</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16039,19 +16124,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.7509152786524</v>
+        <v>3420.767250844247</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.5268919466162</v>
+        <v>4161.5467650379933</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.8457290506849</v>
+        <v>6585.877179313381</v>
       </c>
       <c r="E61" s="124">
-        <v>25477.518694580973</v>
+        <v>25477.6403607555</v>
       </c>
       <c r="F61" s="124">
-        <v>159945.35197174316</v>
+        <v>159946.11577999857</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16101,23 +16186,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.0405484292639748</v>
+        <v>8.0473606786692038</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.0405484292639748</v>
+        <v>8.0473606786692038</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.0405484292639748</v>
+        <v>8.0473606786692038</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.0405484292639748</v>
+        <v>8.0473606786692038</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.0405484292639748</v>
+        <v>8.0473606786692038</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16128,23 +16213,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.0405484292639731</v>
+        <v>8.0473606786691985</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.663554952571813</v>
+        <v>8.6709287940299404</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9663631269572885</v>
+        <v>9.9749113489231878</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.205784168931215</v>
+        <v>13.21725247767808</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.390767645214272</v>
+        <v>17.406008391927472</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16155,23 +16240,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>8.0405484292639695</v>
+        <v>8.0473606786691985</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.2871351664370749</v>
+        <v>9.295071117085639</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.170086660752489</v>
+        <v>12.180621368536858</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.193686460673739</v>
+        <v>21.212355243699054</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.550375135258086</v>
+        <v>37.583788204302508</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16182,23 +16267,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>8.0405484292639642</v>
+        <v>8.0473606786691931</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>10.058988583686581</v>
+        <v>10.067620300316582</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.201393403660029</v>
+        <v>15.214660599328603</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.450910898096787</v>
+        <v>35.482431462991038</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.748173314507255</v>
+        <v>86.825934382238671</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16209,23 +16294,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>8.0405484292639642</v>
+        <v>8.0473606786691931</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.845383435627337</v>
+        <v>10.854724026214141</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.659290445552099</v>
+        <v>18.675674667167947</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>57.228884824827716</v>
+        <v>57.280036543855921</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>193.9172685383983</v>
+        <v>194.09163423215298</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16236,23 +16321,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>8.0405484292639642</v>
+        <v>8.0473606786691931</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.576774284990135</v>
+        <v>11.586774167692182</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.283061408448571</v>
+        <v>22.302712178484313</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.579679035517046</v>
+        <v>88.659091063582395</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>419.89853360932096</v>
+        <v>420.27660388371834</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16262,23 +16347,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>8.0405484292639642</v>
+        <v>8.0473606786691896</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.221962756577623</v>
+        <v>12.23254422663825</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.906371860987687</v>
+        <v>25.929288764328959</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>132.54308051926495</v>
+        <v>132.66212214343895</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>891.56570319804177</v>
+        <v>892.36894483765798</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16313,7 +16398,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.748173314507255</v>
+        <v>86.825934382238671</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16335,7 +16420,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.193686460673739</v>
+        <v>21.212355243699054</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16358,7 +16443,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.170086660752489</v>
+        <v>12.180621368536858</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16381,7 +16466,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.2871351664370749</v>
+        <v>9.295071117085639</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16404,7 +16489,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>8.0405484292639642</v>
+        <v>8.0473606786691931</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16472,7 +16557,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16505,7 +16590,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-13.96</v>
+        <v>-13.98</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16525,7 +16610,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83846105999999998</v>
+        <v>0.83921285999999995</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16534,7 +16619,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.83846105999999998</v>
+        <v>0.83921285999999995</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16554,7 +16639,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>17.63629183687485</v>
+        <v>17.651749896996542</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16588,7 +16673,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.23012948972439</v>
+        <v>342.23187195005454</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16610,7 +16695,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.66007322229234</v>
+        <v>273.66138006753994</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16694,7 +16779,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7405355708471459</v>
+        <v>-4.7406298706450745</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16745,7 +16830,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>13.96</v>
+        <v>13.98</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16760,7 +16845,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.0405484292639748</v>
+        <v>8.0473606786692038</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16807,7 +16892,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.170086660752489</v>
+        <v>12.180621368536858</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16865,7 +16950,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.2871351664370749</v>
+        <v>9.295071117085639</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16923,7 +17008,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.193686460673739</v>
+        <v>21.212355243699054</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16950,7 +17035,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.398216321873655</v>
+        <v>13.409858093279055</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17024,7 +17109,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>8.0405484292639642</v>
+        <v>8.0473606786691931</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17082,7 +17167,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.748173314507255</v>
+        <v>86.825934382238671</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17108,7 +17193,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.79783077687485</v>
+        <v>16.812537036996542</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17170,7 +17255,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.798172674059668</v>
+        <v>16.812879242375146</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17233,7 +17318,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.67082244263312707</v>
+        <v>-0.67086574044491798</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17266,7 +17351,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83846105999999998</v>
+        <v>0.83921285999999995</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17293,7 +17378,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.3322486230320696</v>
+        <v>1.3334431740524777</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17305,7 +17390,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>6.1216584463829644</v>
+        <v>6.1270178706255631</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17315,7 +17400,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>7.4539070694150338</v>
+        <v>7.4604610446780413</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17326,7 +17411,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.5562577592056327</v>
+        <v>0.556256082692276</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17343,7 +17428,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>13.96</v>
+        <v>13.98</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17356,7 +17441,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12028775104137335</v>
+        <v>0.12006981785810078</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17382,7 +17467,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7662026958333332</v>
+        <v>1.7677863486111107</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17394,7 +17479,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>9.7209668847655379</v>
+        <v>9.7294774519655913</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17404,7 +17489,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>11.487169580598872</v>
+        <v>11.497263800576702</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17415,7 +17500,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31615160712221435</v>
+        <v>0.31614938451724484</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17442,7 +17527,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.1607954716506641</v>
+        <v>2.1627329331656768</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17454,7 +17539,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>13.334659649884138</v>
+        <v>13.346333953313566</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17466,7 +17551,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>15.495455121534802</v>
+        <v>15.509066886479243</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17476,39 +17561,95 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.7532371449591908E-2</v>
+        <v>7.7529652285611039E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>430</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>2.0246875693639139</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>12.050560654213566</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>14.07524822357748</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.1628293987800582</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39810BCA-C2EE-43D0-A186-76DE4DE63A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D888234F-6003-4F99-9082-D824DE1F388F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2379,15 +2356,63 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
   </si>
   <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
@@ -2400,10 +2425,10 @@
     <t/>
   </si>
   <si>
+    <t>CNS_02</t>
+  </si>
+  <si>
     <t>USD</t>
-  </si>
-  <si>
-    <t>CNS_02</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -3086,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3600,14 +3625,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3665,9 +3684,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3675,7 +3691,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3767,9 +3782,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3784,9 +3796,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3794,6 +3803,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4106,10 +4142,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4124,11 +4160,11 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>434</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4183,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>435</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4173,9 +4209,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4196,20 +4232,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4225,17 +4261,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4249,14 +4285,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>USD/HKD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4271,29 +4307,29 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4301,286 +4337,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
+        <v>448</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D22" s="32" t="str">
+      <c r="C24" s="291" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>449</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>439</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (HKD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>7.4604610446780413</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (HKD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>16.812537036996542</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.12006981785810078</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>1910.HK (HKD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>432</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>7.4604610446780413</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>427</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>11.497263800576702</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>15.509066886479243</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>439</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>14.07524822357748</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>553.11898834421322</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>7.0318719500546489</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>7.0318719500546489</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-152</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>-144.96812804994536</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-32.451765153160977</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-102.03771507356697</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4588,1080 +4676,1109 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-32.451765153160977</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>342.23187195005454</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-102.03771507356697</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>273.66138006753994</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>342.23187195005454</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>273.66138006753994</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.11059408175537334</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>6.0029532188841196E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>19.326315786751493</v>
       </c>
-      <c r="D82" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>2323</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>13.124257887333194</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>2.2875080906148866</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>1.5035598705501618</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>4.1998196571663646</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>676.3</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>326.61948530720883</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8453027792509011</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>0</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>326.61948530720883</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.8453027792509011</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>8.0473606786692038</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>0</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>-12.221661486093266</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>8.0473606786692038</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>-12.221661486093266</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.25</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>86.83 HKD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.15</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>21.21 HKD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.06</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>12.18 HKD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>9.3 HKD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>8.05 HKD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
         <v>16.812537036996542</v>
       </c>
-      <c r="D122" s="236" t="str">
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>0.83921285999999995</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>1910.HK</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>1.3334431740524777</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
         <v>6.1270178706255631</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
         <v>7.4604610446780413</v>
       </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C140" s="340" t="str">
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.556256082692276</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>1.7677863486111107</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
         <v>9.7294774519655913</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>11.497263800576702</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C148" s="340" t="str">
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
         <v>0.31614938451724484</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>2.1627329331656768</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
         <v>13.346333953313566</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>15.509066886479243</v>
       </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C156" s="340" t="str">
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>7.7529652285611039E-2</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>2.0246875693639139</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
         <v>12.050560654213566</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>14.07524822357748</v>
       </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C164" s="340" t="str">
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
         <v>0.1628293987800582</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5675,17 +5792,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>USD</v>
       </c>
       <c r="C1" s="104">
@@ -6116,7 +6233,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>56480</v>
@@ -6142,7 +6259,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-11150</v>
@@ -6168,7 +6285,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-45970</v>
@@ -6226,7 +6343,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7481,7 +7598,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7929,11 +8046,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -7963,11 +8080,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8099,15 +8216,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8164,7 +8281,7 @@
       <c r="C4" s="19">
         <v>325.3</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8174,7 +8291,7 @@
       <c r="G4" s="19">
         <v>676.3</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8185,7 +8302,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8195,7 +8312,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8206,7 +8323,7 @@
       <c r="C6" s="19">
         <v>651.4</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8216,7 +8333,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8227,7 +8344,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8237,7 +8354,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8248,7 +8365,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8258,7 +8375,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8269,7 +8386,7 @@
       <c r="C9" s="19">
         <v>89.6</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8279,7 +8396,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8290,10 +8407,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8302,10 +8419,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8363,7 +8480,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8372,7 +8489,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8383,7 +8500,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8392,7 +8509,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8403,7 +8520,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8412,7 +8529,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8423,7 +8540,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8432,7 +8549,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8444,7 +8561,7 @@
         <f>262.1+499.2</f>
         <v>761.3</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8453,7 +8570,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8464,7 +8581,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8473,7 +8590,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8484,7 +8601,7 @@
       <c r="C21" s="19">
         <v>1519.8</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8493,7 +8610,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8504,10 +8621,10 @@
       <c r="C22" s="19">
         <v>165.7</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8517,10 +8634,10 @@
         <f>819.6+70.2</f>
         <v>889.80000000000007</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -8854,13 +8971,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -8876,7 +8993,7 @@
         <f>H29</f>
         <v>-2163.2399999999998</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -8891,23 +9008,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-12.221661486093266</v>
       </c>
-      <c r="F47" s="283"/>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -8921,7 +9038,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>3.6733080328905765</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -8932,22 +9049,22 @@
         <f>G29/G32</f>
         <v>0.29063632068042211</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -8961,7 +9078,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.14363260578255238</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -8975,22 +9092,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9012,22 +9129,22 @@
         <f>G39/G32</f>
         <v>0.14988580878878563</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9041,7 +9158,7 @@
         <f>G28/G29</f>
         <v>4.6606150928058525E-2</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9060,13 +9177,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9094,7 +9211,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9104,7 +9221,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9114,7 +9231,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9124,26 +9241,26 @@
         <f>SUM(C66:C69)</f>
         <v>676.3</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9154,65 +9271,65 @@
         <v>-349.68051469279112</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>1.9712961803428783</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>1.9340511454982203</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>349.68051469279112</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9226,7 +9343,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9240,7 +9357,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9254,7 +9371,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9268,11 +9385,11 @@
         <f>SUM(D79:D81)</f>
         <v>0</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9283,15 +9400,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9301,14 +9418,14 @@
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-13.124257887333194</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9318,13 +9435,13 @@
         <f>C87*scaling_factor/Common_Shares</f>
         <v>1.8453027792509011</v>
       </c>
-      <c r="E87" s="269" t="str">
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
@@ -9335,24 +9452,24 @@
         <f>C88*scaling_factor/Common_Shares</f>
         <v>0</v>
       </c>
-      <c r="E88" s="269" t="str">
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-15599.517703758</v>
       </c>
-      <c r="D89" s="271">
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
         <v>-11.278955108082293</v>
       </c>
-      <c r="E89" s="269" t="str">
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9371,22 +9488,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9473,7 +9590,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9487,7 +9604,7 @@
         <v>3588.6</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9543,7 +9660,7 @@
         <f>C25</f>
         <v>-2808.2810116557866</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-2725.5</v>
@@ -9598,7 +9715,7 @@
         <f>C4+C5</f>
         <v>780.31898834421327</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>863.09999999999991</v>
@@ -9653,7 +9770,7 @@
         <f>C35</f>
         <v>-227.20000000000005</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-230.70000000000005</v>
@@ -9709,7 +9826,7 @@
         <v>553.11898834421322</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9765,7 +9882,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -9820,7 +9937,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>0</v>
@@ -9876,7 +9993,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -9932,7 +10049,7 @@
         <f>C50</f>
         <v>-144.96812804994536</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-144.96812804994536</v>
@@ -9987,7 +10104,7 @@
         <f>SUM(C8:C12)</f>
         <v>408.15086029426789</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>487.43187195005453</v>
@@ -10042,7 +10159,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-102.03771507356697</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-118.3</v>
@@ -10098,7 +10215,7 @@
         <v>-32.451765153160977</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10155,7 +10272,7 @@
         <v>273.66138006753994</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10212,8 +10329,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10237,8 +10354,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10263,7 +10380,7 @@
         <v>273.66138006753994</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10359,7 +10476,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10383,7 +10500,7 @@
         <v>-1529.5625032102973</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10440,7 +10557,7 @@
         <v>-1278.7185084454891</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10497,7 +10614,7 @@
         <v>-2808.2810116557866</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10546,14 +10663,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10565,8 +10682,8 @@
         <v>0.42622819573379517</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10625,8 +10742,8 @@
         <v>0.35632795754486124</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10683,7 +10800,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.78255615327865646</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.75948837986958706</v>
@@ -10731,14 +10848,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10749,8 +10866,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-227.20000000000005</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10807,8 +10924,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10866,7 +10983,7 @@
         <v>-227.20000000000005</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -10915,14 +11032,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -10935,7 +11052,7 @@
         <v>6.331159783759685E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -10993,7 +11110,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11049,7 +11166,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>6.331159783759685E-2</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>6.4286908543721794E-2</v>
@@ -11097,26 +11214,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11195,7 +11312,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11206,7 +11323,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-152</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-152</v>
@@ -11255,111 +11372,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>7.0318719500546489</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>7.0318719500546489</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>7.3938065357192277</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>4.5500347912118322</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>1.8613778691321132</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="328" t="str">
+      <c r="L48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="328" t="str">
+      <c r="M48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="328" t="str">
+      <c r="N48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="328" t="str">
+      <c r="O48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="328" t="str">
+      <c r="P48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>13.6</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>13.6</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>14.3</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>3.6</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="324" t="str">
+      <c r="L49" s="320" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="324" t="str">
+      <c r="M49" s="320" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="324" t="str">
+      <c r="N49" s="320" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="324" t="str">
+      <c r="O49" s="320" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="324" t="str">
+      <c r="P49" s="320" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11373,7 +11490,7 @@
         <f>C47+C48</f>
         <v>-144.96812804994536</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-144.96812804994536</v>
@@ -11421,14 +11538,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11442,8 +11559,8 @@
         <f>G53</f>
         <v>2.0109418896939228E-2</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11469,8 +11586,8 @@
         <f>G54</f>
         <v>6.5432630219543694E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11496,7 +11613,7 @@
         <f>-C8/C47</f>
         <v>3.6389407127908764</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>4.1605263157894727</v>
@@ -11544,14 +11661,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11565,7 +11682,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11620,7 +11737,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11675,7 +11792,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11730,7 +11847,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11781,11 +11898,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11841,7 +11958,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-3.0999999999997954</v>
@@ -11889,14 +12006,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -11910,7 +12027,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -11935,7 +12052,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -11960,7 +12077,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -11986,7 +12103,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12014,7 +12131,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12036,7 +12153,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12060,7 +12177,7 @@
         <v>0.78255615327865646</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12117,7 +12234,7 @@
         <v>0.21744384672134351</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12174,7 +12291,7 @@
         <v>6.331159783759685E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12231,7 +12348,7 @@
         <v>0.15413224888374666</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12288,7 +12405,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12345,8 +12462,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>442</v>
+      <c r="E78" s="296" t="s">
+        <v>452</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12404,7 +12521,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12461,7 +12578,7 @@
         <v>4.0396847809715593E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12518,7 +12635,7 @@
         <v>0.11373540107403107</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12575,7 +12692,7 @@
         <v>2.8433850268507768E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12628,12 +12745,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>9.0430154247230065E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12690,7 +12807,7 @@
         <v>7.6258535380800296E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12742,26 +12859,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12771,7 +12888,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12797,7 +12914,7 @@
         <v>7.6258535380800296E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -12846,14 +12963,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -12865,7 +12982,7 @@
         <f>G90</f>
         <v>0.83921285999999995</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.83921285999999995</v>
@@ -12921,7 +13038,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>1160.6851646577072</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1160.6851646577072</v>
@@ -12976,7 +13093,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>4.2413188312185257</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>3.3915168626582455</v>
@@ -13025,13 +13142,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>6.0029532188841196E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>6.0029532188841196E-2</v>
@@ -13079,7 +13196,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13088,7 +13205,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13112,7 +13229,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13169,7 +13286,7 @@
         <v>-0.16265044659186811</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13247,7 +13364,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13262,7 +13379,7 @@
         <v>5079.2</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13319,7 +13436,7 @@
         <v>325.3</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13376,7 +13493,7 @@
         <v>651.4</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13433,7 +13550,7 @@
         <v>3534.2</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13490,7 +13607,7 @@
         <v>1545</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13539,7 +13656,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13548,7 +13665,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13574,7 +13691,7 @@
         <v>9.0648163629270473E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13631,7 +13748,7 @@
         <v>0.18151925541994093</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13688,7 +13805,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13707,63 +13824,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>151.5834675254965</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>118.63202309571396</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>82.086905113804306</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1647.2340425531916</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>8.866459627329192</v>
       </c>
-      <c r="L113" s="334" t="str">
+      <c r="L113" s="329" t="str">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v/>
       </c>
-      <c r="M113" s="334" t="str">
+      <c r="M113" s="329" t="str">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v/>
       </c>
-      <c r="N113" s="334" t="str">
+      <c r="N113" s="329" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v/>
       </c>
-      <c r="O113" s="334" t="str">
+      <c r="O113" s="329" t="str">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v/>
       </c>
-      <c r="P113" s="334" t="str">
+      <c r="P113" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13771,58 +13888,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>165.03430752423526</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>161.88182608881075</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>117.39588212071452</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-5920.2075338253017</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>52.578268876611439</v>
       </c>
-      <c r="L114" s="334" t="str">
+      <c r="L114" s="329" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v/>
       </c>
-      <c r="M114" s="334" t="str">
+      <c r="M114" s="329" t="str">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v/>
       </c>
-      <c r="N114" s="334" t="str">
+      <c r="N114" s="329" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="334" t="str">
+      <c r="O114" s="329" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="334" t="str">
+      <c r="P114" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -13831,7 +13948,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -13887,7 +14004,7 @@
         <f>C81</f>
         <v>0.11373540107403107</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.13582786377697556</v>
@@ -13941,7 +14058,7 @@
         <f>C4/C101</f>
         <v>0.70652858717908329</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.70652858717908329</v>
@@ -13996,7 +14113,7 @@
         <v>3.2875080906148866</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14053,7 +14170,7 @@
         <v>0.35800581769851986</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14149,7 +14266,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14174,7 +14291,7 @@
         <v>1.5461052629401195</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14231,7 +14348,7 @@
         <v>0.11059408175537334</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14280,7 +14397,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15031,13 +15148,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15081,7 +15198,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15091,7 +15208,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15109,10 +15226,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15127,8 +15244,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15143,8 +15260,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15159,8 +15276,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15224,7 +15341,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15234,7 +15351,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15244,7 +15361,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
@@ -16505,7 +16622,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16558,12 +16675,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16576,19 +16693,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-13.98</v>
       </c>
@@ -16605,19 +16722,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.83921285999999995</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>0.83921285999999995</v>
       </c>
@@ -16631,13 +16748,13 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
         <v>17.651749896996542</v>
       </c>
@@ -16654,15 +16771,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 新秀麗(1910.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16679,12 +16796,12 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16701,37 +16818,37 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16745,12 +16862,12 @@
         <v>0.21097145624674352</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16763,12 +16880,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.77230247224880189</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16781,8 +16898,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-4.7406298706450745</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16798,7 +16915,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16808,25 +16925,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16836,12 +16953,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16851,8 +16968,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16872,8 +16989,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16883,8 +17000,8 @@
         <v>0.06</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16898,8 +17015,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16909,8 +17026,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16930,8 +17047,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16941,8 +17058,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16956,8 +17073,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16967,8 +17084,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16988,8 +17105,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16999,8 +17116,8 @@
         <v>0.15</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17014,8 +17131,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17026,8 +17143,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17089,8 +17206,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17100,8 +17217,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17115,8 +17232,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17126,12 +17243,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17147,8 +17264,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17158,8 +17275,8 @@
         <v>0.25</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17173,8 +17290,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17184,8 +17301,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17200,16 +17317,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17218,10 +17335,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17233,8 +17350,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17245,8 +17362,8 @@
         <v>0.111211776070739</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17261,23 +17378,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17285,38 +17402,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
         <v>-0.67086574044491798</v>
       </c>
@@ -17336,10 +17453,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17360,15 +17477,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17409,7 +17526,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.556256082692276</v>
       </c>
@@ -17419,14 +17536,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>13.98</v>
       </c>
@@ -17437,9 +17554,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.12006981785810078</v>
       </c>
@@ -17449,15 +17566,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17498,28 +17615,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
         <v>0.31614938451724484</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17531,7 +17648,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17543,23 +17660,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>15.509066886479243</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>7.7529652285611039E-2</v>
       </c>
@@ -17569,15 +17686,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17603,19 +17720,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>14.07524822357748</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
         <v>0.1628293987800582</v>
       </c>
@@ -17624,33 +17741,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D888234F-6003-4F99-9082-D824DE1F388F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5966819-CD33-489D-893D-48472F93B7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3830,29 +3830,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4302,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>7.8139000000000003</v>
+        <v>7.8137999999999996</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4312,13 +4312,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4390,14 +4390,14 @@
       </c>
       <c r="C26" s="341">
         <f>C127</f>
-        <v>16.812537036996542</v>
+        <v>16.812326952049464</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12006981785810078</v>
+        <v>0.12006488109359492</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C29" s="339">
         <f>C144</f>
-        <v>7.4604610446780413</v>
+        <v>7.4603674180938295</v>
       </c>
       <c r="D29" s="339" t="str">
         <f>D144</f>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>11.497263800576702</v>
+        <v>11.038812906388786</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4458,7 +4458,7 @@
         <v>440</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="C31" s="148">
         <f>C160</f>
-        <v>15.509066886479243</v>
+        <v>15.508872436253256</v>
       </c>
       <c r="D31" s="148" t="str">
         <f>D160</f>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C32" s="148">
         <f>C168</f>
-        <v>14.07524822357748</v>
+        <v>14.075071731650674</v>
       </c>
       <c r="D32" s="148" t="str">
         <f>D168</f>
@@ -4514,22 +4514,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4541,13 +4541,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4567,13 +4567,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4602,13 +4602,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="C51" s="318">
         <f>Normalized_FCF!C48</f>
-        <v>7.0318719500546489</v>
+        <v>7.03184705776422</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-144.96812804994536</v>
+        <v>-144.96815294223578</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="C59" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-102.03771507356697</v>
+        <v>-102.03770885049437</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4716,7 +4716,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4738,22 +4738,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C67" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>342.23187195005454</v>
+        <v>342.23184705776413</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C68" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>273.66138006753994</v>
+        <v>273.66136139832213</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11059408175537334</v>
+        <v>0.11059265886011045</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.0029532188841196E-2</v>
+        <v>6.0028763948497849E-2</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
@@ -4814,22 +4814,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4873,22 +4873,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.326315786751493</v>
+        <v>19.326067135804305</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4925,13 +4925,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4944,13 +4944,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.124257887333194</v>
+        <v>13.12408992693074</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="C104" s="188">
         <f>Valuation_Model!C8</f>
-        <v>326.61948530720883</v>
+        <v>326.62072314956305</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8453027792509011</v>
+        <v>1.8452861569582497</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5081,13 +5081,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.0473606786692038</v>
+        <v>8.0472633658318138</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>-12.221661486093266</v>
+        <v>-12.221505076854779</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5126,13 +5126,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>86.83 HKD</v>
+        <v>86.82 HKD</v>
       </c>
       <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>9.3 HKD</v>
+        <v>9.29 HKD</v>
       </c>
       <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>16.812537036996542</v>
+        <v>16.812326952049464</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5275,13 +5275,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,22 +5294,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="C138" s="237">
         <f>Scenarios!C77</f>
-        <v>0.83921285999999995</v>
+        <v>0.83920211999999994</v>
       </c>
       <c r="D138" s="236" t="str">
         <f>Market_currency</f>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="C142" s="240">
         <f>Scenarios!C81</f>
-        <v>1.3334431740524777</v>
+        <v>1.3334261090379005</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>6.1270178706255631</v>
+        <v>6.1269413090559288</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>7.4604610446780413</v>
+        <v>7.4603674180938295</v>
       </c>
       <c r="D144" s="336" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.556256082692276</v>
+        <v>0.55625610664296576</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>1.7677863486111107</v>
+        <v>1.7207007182372014</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>9.7294774519655913</v>
+        <v>9.3181121881515843</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>11.497263800576702</v>
+        <v>11.038812906388786</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31614938451724484</v>
+        <v>0.34340957454178422</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C158" s="240">
         <f>Scenarios!C97</f>
-        <v>2.1627329331656768</v>
+        <v>2.1627052551440338</v>
       </c>
     </row>
     <row r="159" spans="2:4">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>13.346333953313566</v>
+        <v>13.346167181109223</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>15.509066886479243</v>
+        <v>15.508872436253256</v>
       </c>
       <c r="D160" s="336" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7529652285611039E-2</v>
+        <v>7.7529691131620115E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C166" s="240">
         <f>Scenarios!C103</f>
-        <v>2.0246875693639139</v>
+        <v>2.024661658006341</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>12.050560654213566</v>
+        <v>12.050410073644333</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>14.07524822357748</v>
+        <v>14.075071731650674</v>
       </c>
       <c r="D168" s="336" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.1628293987800582</v>
+        <v>0.16282943513951242</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5642,13 +5642,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5685,13 +5685,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5699,22 +5699,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,17 +5738,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5765,6 +5754,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6316,11 +6316,11 @@
       </c>
       <c r="C25" s="39">
         <f>0.1074*Exchange_Rate</f>
-        <v>0.83921285999999995</v>
+        <v>0.83920211999999994</v>
       </c>
       <c r="D25" s="39">
         <f>0.1026*Exchange_Rate</f>
-        <v>0.80170613999999996</v>
+        <v>0.80169587999999992</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -7651,11 +7651,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.83921285999999995</v>
+        <v>0.83920211999999994</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.80170613999999996</v>
+        <v>0.80169587999999992</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -9002,11 +9002,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.3400901822131992</v>
+        <v>8.3399834481856043</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-12.221661486093266</v>
+        <v>-12.221505076854779</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>326.61948530720883</v>
+        <v>326.62072314956305</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9264,11 +9264,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-343.07376372147559</v>
+        <v>-343.07252587912132</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-349.68051469279112</v>
+        <v>-349.67927685043691</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>354</v>
@@ -9280,11 +9280,11 @@
       </c>
       <c r="C74" s="285">
         <f>-$C$66/C73</f>
-        <v>1.9712961803428783</v>
+        <v>1.9713032929902656</v>
       </c>
       <c r="D74" s="285">
         <f>-$C$66/D73</f>
-        <v>1.9340511454982203</v>
+        <v>1.9340579919160141</v>
       </c>
       <c r="F74" s="280" t="s">
         <v>322</v>
@@ -9297,7 +9297,7 @@
       <c r="C75" s="289"/>
       <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
-        <v>349.68051469279112</v>
+        <v>349.67927685043691</v>
       </c>
       <c r="F75" s="280" t="s">
         <v>355</v>
@@ -9412,11 +9412,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-18151.689699999999</v>
+        <v>-18151.457399999999</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-13.124257887333194</v>
+        <v>-13.12408992693074</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9429,11 +9429,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2552.1719962419993</v>
+        <v>2552.1490065460557</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8453027792509011</v>
+        <v>1.8452861569582497</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9463,11 +9463,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-15599.517703758</v>
+        <v>-15599.308393453943</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>-11.278955108082293</v>
+        <v>-11.278803769972491</v>
       </c>
       <c r="E89" s="267" t="str">
         <f>Market_currency</f>
@@ -10047,24 +10047,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-144.96812804994536</v>
+        <v>-144.96815294223578</v>
       </c>
       <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-144.96812804994536</v>
+        <v>-144.96815294223578</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-165.60619346428078</v>
+        <v>-165.60621963779204</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-133.74996520878818</v>
+        <v>-133.74998131556433</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-167.13862213086787</v>
+        <v>-167.1386287200036</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -10102,24 +10102,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>408.15086029426789</v>
+        <v>408.15083540197747</v>
       </c>
       <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>487.43187195005453</v>
+        <v>487.43184705776412</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>497.89380653571948</v>
+        <v>497.89378036220819</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>286.45003479121164</v>
+        <v>286.45001868443546</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-53.538622130867736</v>
+        <v>-53.538628720003459</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-102.03771507356697</v>
+        <v>-102.03770885049437</v>
       </c>
       <c r="E14" s="298"/>
       <c r="G14" s="191">
@@ -10269,26 +10269,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>273.66138006753994</v>
+        <v>273.66136139832213</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>342.23187195005454</v>
+        <v>342.23184705776413</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>329.99380653571944</v>
+        <v>329.99378036220816</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>236.55003479121163</v>
+        <v>236.55001868443546</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-6.5386221308677328</v>
+        <v>-6.5386287200034552</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10377,26 +10377,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>273.66138006753994</v>
+        <v>273.66136139832213</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>342.23187195005454</v>
+        <v>342.23184705776413</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>329.99380653571944</v>
+        <v>329.99378036220816</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>236.55003479121163</v>
+        <v>236.55001868443546</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-6.5386221308677328</v>
+        <v>-6.5386287200034552</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11238,19 +11238,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.24270058403591999</v>
+        <v>0.24270059643021358</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27033877150738095</v>
+        <v>0.27033878571867492</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>8.4831548432912018E-2</v>
+        <v>8.483155320289866E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>1.0497094950002055</v>
+        <v>1.049709365809778</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11376,24 +11376,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>7.0318719500546489</v>
+        <v>7.03184705776422</v>
       </c>
       <c r="E48" s="298"/>
       <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>7.0318719500546489</v>
+        <v>7.03184705776422</v>
       </c>
       <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>7.3938065357192277</v>
+        <v>7.3937803622079672</v>
       </c>
       <c r="I48" s="324">
         <f t="shared" si="19"/>
-        <v>4.5500347912118322</v>
+        <v>4.5500186844356723</v>
       </c>
       <c r="J48" s="324">
         <f t="shared" si="19"/>
-        <v>1.8613778691321132</v>
+        <v>1.8613712799964113</v>
       </c>
       <c r="K48" s="324">
         <f t="shared" si="19"/>
@@ -11488,24 +11488,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-144.96812804994536</v>
+        <v>-144.96815294223578</v>
       </c>
       <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-144.96812804994536</v>
+        <v>-144.96815294223578</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-165.60619346428078</v>
+        <v>-165.60621963779204</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-133.74996520878818</v>
+        <v>-133.74998131556433</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-167.13862213086787</v>
+        <v>-167.1386287200036</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12575,26 +12575,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.0396847809715593E-2</v>
+        <v>4.0396854746206259E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.0396847809715593E-2</v>
+        <v>4.0396854746206259E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.4972353211025627E-2</v>
+        <v>4.4972360318757343E-2</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6447411171269687E-2</v>
+        <v>4.6447416764677153E-2</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>8.2709136050508641E-2</v>
+        <v>8.2709139311165678E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12632,26 +12632,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.11373540107403107</v>
+        <v>0.1137353941375404</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.13582786377697556</v>
+        <v>0.1358278568404849</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13520905022151844</v>
+        <v>0.1352090431137867</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.9475633696072943E-2</v>
+        <v>9.947562810266547E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6493775797143574E-2</v>
+        <v>-2.6493779057800603E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.8433850268507768E-2</v>
+        <v>2.84338485343851E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="295"/>
@@ -12804,26 +12804,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>7.6258535380800296E-2</v>
+        <v>7.6258530178432302E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.5366402482877602E-2</v>
+        <v>9.5366395546386928E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.9613786263230355E-2</v>
+        <v>8.9613779155498632E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.2146838030008204E-2</v>
+        <v>8.2146832436600731E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>3.2356601993605173E-3</v>
+        <v>3.2356634600175451E-3</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12911,26 +12911,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>7.6258535380800296E-2</v>
+        <v>7.6258530178432302E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.5366402482877602E-2</v>
+        <v>9.5366395546386928E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.9613786263230355E-2</v>
+        <v>8.9613779155498632E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.2146838030008204E-2</v>
+        <v>8.2146832436600731E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>3.2356601993605173E-3</v>
+        <v>3.2356634600175451E-3</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12980,16 +12980,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.83921285999999995</v>
+        <v>0.83920211999999994</v>
       </c>
       <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.83921285999999995</v>
+        <v>0.83920211999999994</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.80170613999999996</v>
+        <v>0.80169587999999992</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -13036,16 +13036,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1160.6851646577072</v>
+        <v>1160.670310549456</v>
       </c>
       <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1160.6851646577072</v>
+        <v>1160.670310549456</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1108.8109673545696</v>
+        <v>1108.7967771170779</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -13091,16 +13091,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.2413188312185257</v>
+        <v>4.2412648414039946</v>
       </c>
       <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.3915168626582455</v>
+        <v>3.3914737056997222</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>3.3600962969423147</v>
+        <v>3.3600535619187708</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -13146,16 +13146,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.0029532188841196E-2</v>
+        <v>6.0028763948497849E-2</v>
       </c>
       <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.0029532188841196E-2</v>
+        <v>6.0028763948497849E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.7346648068669522E-2</v>
+        <v>5.7345914163090123E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -13283,26 +13283,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.16265044659186811</v>
+        <v>-0.16265045489814145</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.1012381452297446E-2</v>
+        <v>-2.1012379983604612E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.73815236887167934</v>
+        <v>0.73815237523411525</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.3503437965030978</v>
+        <v>-6.3503428371786086</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.82818157210889676</v>
+        <v>-0.82818155096276169</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13894,19 +13894,19 @@
       <c r="E114" s="298"/>
       <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>165.03430752423526</v>
+        <v>165.03431952803311</v>
       </c>
       <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>161.88182608881075</v>
+        <v>161.88183892849457</v>
       </c>
       <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>117.39588212071452</v>
+        <v>117.39589011424252</v>
       </c>
       <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-5920.2075338253017</v>
+        <v>-5920.2015678876996</v>
       </c>
       <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -14002,24 +14002,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.11373540107403107</v>
+        <v>0.1137353941375404</v>
       </c>
       <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.13582786377697556</v>
+        <v>0.1358278568404849</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13520905022151844</v>
+        <v>0.1352090431137867</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>9.9475633696072943E-2</v>
+        <v>9.947562810266547E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6493775797143574E-2</v>
+        <v>-2.6493779057800603E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14288,30 +14288,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.5461052629401195</v>
+        <v>1.5460853708643443</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.93350811224163</v>
+        <v>1.9334832271397775</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8643666888495565</v>
+        <v>1.8643426813609343</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3364372190518727</v>
+        <v>1.336420024723064</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-3.6941266927822736E-2</v>
+        <v>-3.6940831390502527E-2</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-1.2271152876146227</v>
+        <v>-1.2270995833531448</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14345,30 +14345,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11059408175537334</v>
+        <v>0.11059265886011045</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13830530130483762</v>
+        <v>0.13830352125463358</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13335956286477513</v>
+        <v>0.13335784559091088</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.559636760027701E-2</v>
+        <v>9.5595137676900144E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-2.6424368331775918E-3</v>
+        <v>-2.6424056788628414E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-8.7776486953835678E-2</v>
+        <v>-8.7775363616104773E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>273.66138006753994</v>
+        <v>273.66136139832213</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3420.7672508442492</v>
+        <v>3420.7670174790264</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>326.61948530720883</v>
+        <v>326.62072314956305</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1424.3867361514581</v>
+        <v>1424.3877406285894</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.8139000000000003</v>
+        <v>7.8137999999999996</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.0473606786692038</v>
+        <v>8.0472633658318138</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.812879242375146</v>
+        <v>16.812669153025286</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>304.09574818682057</v>
+        <v>304.09572744136591</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15414,7 +15414,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>281.57013721001903</v>
+        <v>281.57011800126469</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>337.91477643823708</v>
+        <v>337.91475338564356</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>289.70745579409902</v>
+        <v>289.70743603021566</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>375.49487888648014</v>
+        <v>375.49485327016674</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>298.0799411980517</v>
+        <v>298.07992086299623</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>417.25433127291262</v>
+        <v>417.25430280776351</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>306.69438969421151</v>
+        <v>306.69436877147717</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>463.65792652698173</v>
+        <v>463.65789489617288</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>315.55779396577418</v>
+        <v>315.55777243837719</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>515.22214802532358</v>
+        <v>515.22211287679625</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>324.6773487830298</v>
+        <v>324.67732663349545</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>572.52091817820099</v>
+        <v>572.52087912074353</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>334.06045684363829</v>
+        <v>334.06043405398702</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>636.19198632644895</v>
+        <v>636.19194292534223</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>343.71473478168679</v>
+        <v>343.71471133341925</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>706.94402704778474</v>
+        <v>706.94397881996383</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>353.64801935040856</v>
+        <v>353.64799522449096</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>785.56452787836929</v>
+        <v>785.56447428704689</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>363.86837378358007</v>
+        <v>363.86834896042848</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3801.1968523352571</v>
+        <v>3801.1965930170736</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1760.6896289296901</v>
+        <v>1760.6895088151962</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16085,7 +16085,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4972.2682803341886</v>
+        <v>4972.2679411253484</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16106,7 +16106,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4972.2682803341886</v>
+        <v>4972.2679411253484</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16136,19 +16136,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3420.7672508442483</v>
+        <v>3420.767017479026</v>
       </c>
       <c r="C56" s="124">
-        <v>3531.1391091556479</v>
+        <v>3531.1388682608413</v>
       </c>
       <c r="D56" s="124">
-        <v>3761.9446526782708</v>
+        <v>3761.9443960378781</v>
       </c>
       <c r="E56" s="124">
-        <v>4335.8406022059808</v>
+        <v>4335.8403064143258</v>
       </c>
       <c r="F56" s="124">
-        <v>5077.2524269608612</v>
+        <v>5077.2520805899876</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16157,19 +16157,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3420.7672508442483</v>
+        <v>3420.7670174790246</v>
       </c>
       <c r="C57" s="124">
-        <v>3641.6126025070498</v>
+        <v>3641.6123540757262</v>
       </c>
       <c r="D57" s="124">
-        <v>4152.3563940162576</v>
+        <v>4152.3561107419209</v>
       </c>
       <c r="E57" s="124">
-        <v>5750.9776625187005</v>
+        <v>5750.9772701861966</v>
       </c>
       <c r="F57" s="124">
-        <v>8648.7292225659221</v>
+        <v>8648.7286325483983</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16178,19 +16178,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3420.7672508442474</v>
+        <v>3420.7670174790246</v>
       </c>
       <c r="C58" s="124">
-        <v>3778.3541819587581</v>
+        <v>3778.3539241989047</v>
       </c>
       <c r="D58" s="124">
-        <v>4689.3828067577833</v>
+        <v>4689.3824868474294</v>
       </c>
       <c r="E58" s="124">
-        <v>8276.7880620087344</v>
+        <v>8276.7874973650887</v>
       </c>
       <c r="F58" s="124">
-        <v>17364.612936017496</v>
+        <v>17364.61175140116</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16199,19 +16199,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3420.7672508442474</v>
+        <v>3420.7670174790246</v>
       </c>
       <c r="C59" s="124">
-        <v>3917.6719225088536</v>
+        <v>3917.6716552447242</v>
       </c>
       <c r="D59" s="124">
-        <v>5301.9839723711548</v>
+        <v>5301.9836106690627</v>
       </c>
       <c r="E59" s="124">
-        <v>12134.974714354237</v>
+        <v>12134.973886504557</v>
       </c>
       <c r="F59" s="124">
-        <v>36350.693740772476</v>
+        <v>36350.691260923042</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16220,19 +16220,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3420.7672508442474</v>
+        <v>3420.7670174790242</v>
       </c>
       <c r="C60" s="124">
-        <v>4047.2451519632036</v>
+        <v>4047.2448758595706</v>
       </c>
       <c r="D60" s="124">
-        <v>5943.9713678580911</v>
+        <v>5943.9709623595281</v>
       </c>
       <c r="E60" s="124">
-        <v>17689.082556114754</v>
+        <v>17689.081349363056</v>
       </c>
       <c r="F60" s="124">
-        <v>76385.542873667073</v>
+        <v>76385.537662634611</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16241,19 +16241,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3420.767250844247</v>
+        <v>3420.7670174790242</v>
       </c>
       <c r="C61" s="124">
-        <v>4161.5467650379933</v>
+        <v>4161.5464811366892</v>
       </c>
       <c r="D61" s="124">
-        <v>6585.877179313381</v>
+        <v>6585.8767300239133</v>
       </c>
       <c r="E61" s="124">
-        <v>25477.6403607555</v>
+        <v>25477.638622667288</v>
       </c>
       <c r="F61" s="124">
-        <v>159946.11577999857</v>
+        <v>159946.10486845206</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16303,23 +16303,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.0473606786692038</v>
+        <v>8.0472633658318138</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.0473606786692038</v>
+        <v>8.0472633658318138</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.0473606786692038</v>
+        <v>8.0472633658318138</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.0473606786692038</v>
+        <v>8.0472633658318138</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.0473606786692038</v>
+        <v>8.0472633658318138</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16330,23 +16330,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.0473606786691985</v>
+        <v>8.0472633658318102</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.6709287940299404</v>
+        <v>8.670823458411375</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>9.9749113489231878</v>
+        <v>9.9747892363616728</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>13.21725247767808</v>
+        <v>13.217088649395803</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>17.406008391927472</v>
+        <v>17.405790671421911</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16357,23 +16357,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>8.0473606786691985</v>
+        <v>8.0472633658318049</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>9.295071117085639</v>
+        <v>9.2949577512981847</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>12.180621368536858</v>
+        <v>12.180470877473635</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.212355243699054</v>
+        <v>21.212088551016876</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.583788204302508</v>
+        <v>37.583310877976672</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16384,23 +16384,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>8.0473606786691931</v>
+        <v>8.0472633658318049</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>10.067620300316582</v>
+        <v>10.067496994968566</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>15.214660599328603</v>
+        <v>15.214471072541402</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.482431462991038</v>
+        <v>35.481981172565369</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>86.825934382238671</v>
+        <v>86.824823510108047</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16411,23 +16411,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>8.0473606786691931</v>
+        <v>8.0472633658318049</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>10.854724026214141</v>
+        <v>10.854590594047897</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>18.675674667167947</v>
+        <v>18.675440611230144</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>57.280036543855921</v>
+        <v>57.279305807058073</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>194.09163423215298</v>
+        <v>194.08914328747449</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16438,23 +16438,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>8.0473606786691931</v>
+        <v>8.0472633658318014</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>11.586774167692182</v>
+        <v>11.58663131702305</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>22.302712178484313</v>
+        <v>22.302431457350583</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.659091063582395</v>
+        <v>88.657956606193707</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>420.27660388371834</v>
+        <v>420.27120285997648</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16464,23 +16464,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>8.0473606786691896</v>
+        <v>8.0472633658318014</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>12.23254422663825</v>
+        <v>12.232393067539387</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.929288764328959</v>
+        <v>25.928961383929529</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>132.66212214343895</v>
+        <v>132.66042154631219</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>892.36894483765798</v>
+        <v>892.35746990883047</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>86.825934382238671</v>
+        <v>86.824823510108047</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16537,7 +16537,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.212355243699054</v>
+        <v>21.212088551016876</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.180621368536858</v>
+        <v>12.180470877473635</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.295071117085639</v>
+        <v>9.2949577512981847</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>8.0473606786691931</v>
+        <v>8.0472633658318049</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.83921285999999995</v>
+        <v>0.83920211999999994</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="I5" s="262">
         <f t="shared" si="0"/>
-        <v>0.83921285999999995</v>
+        <v>0.83920211999999994</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16756,7 +16756,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>17.651749896996542</v>
+        <v>17.651529072049463</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>342.23187195005454</v>
+        <v>342.23184705776413</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>273.66138006753994</v>
+        <v>273.66136139832213</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16896,7 +16896,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.7406298706450745</v>
+        <v>-4.7406285234449079</v>
       </c>
       <c r="E14" s="356"/>
       <c r="F14" s="356"/>
@@ -16962,7 +16962,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.0473606786692038</v>
+        <v>8.0472633658318138</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>12.180621368536858</v>
+        <v>12.180470877473635</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>9.295071117085639</v>
+        <v>9.2949577512981847</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>21.212355243699054</v>
+        <v>21.212088551016876</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17152,7 +17152,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.409858093279055</v>
+        <v>13.409691786947192</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>8.0473606786691931</v>
+        <v>8.0472633658318049</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>86.825934382238671</v>
+        <v>86.824823510108047</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>16.812537036996542</v>
+        <v>16.812326952049464</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>16.812879242375146</v>
+        <v>16.812669153025286</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="F72" s="325">
         <f>BS!D89/C60</f>
-        <v>-0.67086574044491798</v>
+        <v>-0.67086512189186143</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.83921285999999995</v>
+        <v>0.83920211999999994</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.3334431740524777</v>
+        <v>1.3334261090379005</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>6.1270178706255631</v>
+        <v>6.1269413090559288</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17517,7 +17517,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>7.4604610446780413</v>
+        <v>7.4603674180938295</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="F83" s="325">
         <f>(1-C83/C60)</f>
-        <v>0.556256082692276</v>
+        <v>0.55625610664296576</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12006981785810078</v>
+        <v>0.12006488109359492</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7677863486111107</v>
+        <v>1.7207007182372014</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>9.7294774519655913</v>
+        <v>9.3181121881515843</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>11.497263800576702</v>
+        <v>11.038812906388786</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.31614938451724484</v>
+        <v>0.34340957454178422</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.1627329331656768</v>
+        <v>2.1627052551440338</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>13.346333953313566</v>
+        <v>13.346167181109223</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>15.509066886479243</v>
+        <v>15.508872436253256</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="F99" s="325">
         <f>(1-C99/C60)</f>
-        <v>7.7529652285611039E-2</v>
+        <v>7.7529691131620115E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.0246875693639139</v>
+        <v>2.024661658006341</v>
       </c>
       <c r="D103" s="117"/>
     </row>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>12.050560654213566</v>
+        <v>12.050410073644333</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -17724,7 +17724,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>14.07524822357748</v>
+        <v>14.075071731650674</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>0.1628293987800582</v>
+        <v>0.16282943513951242</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5966819-CD33-489D-893D-48472F93B7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB56A64C-1E41-46F8-AD9F-7F566DC8845F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3111,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3745,7 +3745,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3809,9 +3808,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3830,29 +3826,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4160,7 +4166,7 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4194,7 +4200,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>445</v>
       </c>
     </row>
@@ -4347,7 +4353,7 @@
       <c r="D22" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>442</v>
       </c>
     </row>
@@ -4378,7 +4384,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4388,14 +4394,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
         <v>16.812326952049464</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
         <v>0.12006488109359492</v>
       </c>
@@ -4408,18 +4414,18 @@
       <c r="B28" s="45" t="s">
         <v>436</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>1910.HK (HKD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>432</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4427,18 +4433,18 @@
       <c r="B29" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
         <v>7.4603674180938295</v>
       </c>
-      <c r="D29" s="339" t="str">
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>427</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4446,18 +4452,18 @@
       <c r="B30" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
         <v>11.038812906388786</v>
       </c>
-      <c r="D30" s="148" t="str">
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4465,18 +4471,18 @@
       <c r="B31" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
         <v>15.508872436253256</v>
       </c>
-      <c r="D31" s="148" t="str">
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>439</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4484,18 +4490,18 @@
       <c r="B32" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
         <v>14.075071731650674</v>
       </c>
-      <c r="D32" s="148" t="str">
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4523,13 +4529,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4636,7 +4642,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>7.03184705776422</v>
       </c>
@@ -4644,14 +4650,14 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-152</v>
       </c>
@@ -4659,8 +4665,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4719,10 +4725,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4823,13 +4829,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4867,7 +4873,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4979,28 +4985,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>2.2875080906148866</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>1.5035598705501618</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>4.1998196571663646</v>
       </c>
@@ -5103,7 +5109,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
@@ -5275,13 +5281,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,13 +5300,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5364,7 +5370,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5397,7 +5403,7 @@
         <f>Scenarios!C83</f>
         <v>7.4603674180938295</v>
       </c>
-      <c r="D144" s="336" t="str">
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5406,11 +5412,11 @@
       <c r="B145" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5433,7 +5439,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5466,7 +5472,7 @@
         <f>Scenarios!C93</f>
         <v>11.038812906388786</v>
       </c>
-      <c r="D152" s="336" t="str">
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5475,11 +5481,11 @@
       <c r="B153" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5535,7 +5541,7 @@
         <f>Scenarios!C99</f>
         <v>15.508872436253256</v>
       </c>
-      <c r="D160" s="336" t="str">
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5544,11 +5550,11 @@
       <c r="B161" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5604,7 +5610,7 @@
         <f>Scenarios!C105</f>
         <v>14.075071731650674</v>
       </c>
-      <c r="D168" s="336" t="str">
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5613,11 +5619,11 @@
       <c r="B169" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5642,7 +5648,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5656,13 +5662,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5699,22 +5705,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,6 +5744,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5754,17 +5771,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8046,11 +8052,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8080,11 +8086,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9308,7 +9314,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
@@ -11379,104 +11385,104 @@
         <v>7.03184705776422</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>7.03184705776422</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>7.3937803622079672</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>4.5500186844356723</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>1.8613712799964113</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="324" t="str">
+      <c r="L48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="324" t="str">
+      <c r="M48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="324" t="str">
+      <c r="N48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="324" t="str">
+      <c r="O48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="324" t="str">
+      <c r="P48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>13.6</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>13.6</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>14.3</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>3.6</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="320" t="str">
+      <c r="L49" s="319" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="320" t="str">
+      <c r="M49" s="319" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="320" t="str">
+      <c r="N49" s="319" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="320" t="str">
+      <c r="O49" s="319" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="320" t="str">
+      <c r="P49" s="319" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -13840,47 +13846,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>151.5834675254965</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>118.63202309571396</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>82.086905113804306</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1647.2340425531916</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>8.866459627329192</v>
       </c>
-      <c r="L113" s="329" t="str">
+      <c r="L113" s="328" t="str">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v/>
       </c>
-      <c r="M113" s="329" t="str">
+      <c r="M113" s="328" t="str">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v/>
       </c>
-      <c r="N113" s="329" t="str">
+      <c r="N113" s="328" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v/>
       </c>
-      <c r="O113" s="329" t="str">
+      <c r="O113" s="328" t="str">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v/>
       </c>
-      <c r="P113" s="329" t="str">
+      <c r="P113" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13892,47 +13898,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>165.03431952803311</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>161.88183892849457</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>117.39589011424252</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-5920.2015678876996</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>52.578268876611439</v>
       </c>
-      <c r="L114" s="329" t="str">
+      <c r="L114" s="328" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v/>
       </c>
-      <c r="M114" s="329" t="str">
+      <c r="M114" s="328" t="str">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v/>
       </c>
-      <c r="N114" s="329" t="str">
+      <c r="N114" s="328" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="329" t="str">
+      <c r="O114" s="328" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="329" t="str">
+      <c r="P114" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -15226,10 +15232,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15244,8 +15250,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15260,8 +15266,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15276,8 +15282,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16771,11 +16777,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 新秀麗(1910.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16796,8 +16802,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16818,8 +16824,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -16829,8 +16835,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -16843,8 +16849,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -16862,8 +16868,8 @@
         <v>0.21097145624674352</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -16880,8 +16886,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.77230247224880189</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -16898,8 +16904,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-4.7406285234449079</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16925,21 +16931,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16953,8 +16959,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16968,8 +16974,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16989,8 +16995,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17000,8 +17006,8 @@
         <v>0.06</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17015,8 +17021,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17026,8 +17032,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17047,8 +17053,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17058,8 +17064,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17073,8 +17079,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17084,8 +17090,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17105,8 +17111,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17116,8 +17122,8 @@
         <v>0.15</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17131,8 +17137,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17143,8 +17149,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17206,8 +17212,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17217,8 +17223,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17232,8 +17238,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17243,8 +17249,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17264,8 +17270,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17275,8 +17281,8 @@
         <v>0.25</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17290,8 +17296,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17301,8 +17307,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17319,7 +17325,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17433,7 +17439,7 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
         <v>-0.67086512189186143</v>
       </c>
@@ -17526,7 +17532,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.55625610664296576</v>
       </c>
@@ -17615,7 +17621,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.34340957454178422</v>
       </c>
@@ -17625,7 +17631,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17636,7 +17642,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17648,7 +17654,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17660,7 +17666,7 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17676,7 +17682,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>7.7529691131620115E-2</v>
       </c>
@@ -17732,7 +17738,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.16282943513951242</v>
       </c>
@@ -17741,32 +17747,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB56A64C-1E41-46F8-AD9F-7F566DC8845F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F3D330-FB92-483D-A223-9377706910DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4909,7 +4909,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>19.326067135804305</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4963,7 +4963,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>2323</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5034,7 +5034,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>326.62072314956305</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5065,7 +5065,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>0</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5100,7 +5100,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>8.0472633658318138</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5159,111 +5159,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.25</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>15</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>86.82 HKD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.15</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>10</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>21.21 HKD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.06</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>10</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>12.18 HKD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0.02</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>10</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>9.29 HKD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>0</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>15</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>8.05 HKD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-18151.457399999999</v>
       </c>
       <c r="D86" s="248">
@@ -9434,7 +9434,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>2552.1490065460557</v>
       </c>
       <c r="D87" s="248">
@@ -9451,7 +9451,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>0</v>
       </c>
       <c r="D88" s="248">
@@ -15411,7 +15411,7 @@
         <v>304.09572744136591</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E21" s="125">
@@ -15433,7 +15433,7 @@
         <v>337.91475338564356</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E22" s="125">
@@ -15455,7 +15455,7 @@
         <v>375.49485327016674</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E23" s="125">
@@ -15477,7 +15477,7 @@
         <v>417.25430280776351</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E24" s="125">
@@ -15499,7 +15499,7 @@
         <v>463.65789489617288</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E25" s="125">
@@ -15521,7 +15521,7 @@
         <v>515.22211287679625</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E26" s="125">
@@ -15543,7 +15543,7 @@
         <v>572.52087912074353</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E27" s="125">
@@ -15565,7 +15565,7 @@
         <v>636.19194292534223</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E28" s="125">
@@ -15587,7 +15587,7 @@
         <v>706.94397881996383</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E29" s="125">
@@ -15609,7 +15609,7 @@
         <v>785.56447428704689</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>0.111211776070739</v>
       </c>
       <c r="E30" s="125">
@@ -15631,7 +15631,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15675,7 +15675,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15697,7 +15697,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15719,7 +15719,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15741,7 +15741,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15763,7 +15763,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -15785,7 +15785,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -15807,7 +15807,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -15829,7 +15829,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -15851,7 +15851,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -15873,7 +15873,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -15895,7 +15895,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -15917,7 +15917,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -15939,7 +15939,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -15961,7 +15961,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -15983,7 +15983,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16005,7 +16005,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16027,7 +16027,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16750,7 +16750,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -16967,7 +16967,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>8.0472633658318138</v>
       </c>
       <c r="D22" t="str">
@@ -17014,7 +17014,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>12.180470877473635</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17072,7 +17072,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>9.2949577512981847</v>
       </c>
       <c r="D33" t="str">
@@ -17130,7 +17130,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>21.212088551016876</v>
       </c>
       <c r="D39" t="str">
@@ -17231,7 +17231,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>8.0472633658318049</v>
       </c>
       <c r="D51" t="str">
@@ -17289,7 +17289,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>86.824823510108047</v>
       </c>
       <c r="D57" t="str">
@@ -17377,7 +17377,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>16.812669153025286</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F3D330-FB92-483D-A223-9377706910DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAD79A7-DCFF-4E21-8B1E-0734F1AFDA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/1910.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1910.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAD79A7-DCFF-4E21-8B1E-0734F1AFDA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B303390B-A353-4E27-B328-85E1C2AB588A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="461">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2407,28 +2402,58 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>新秀麗</t>
+  </si>
+  <si>
+    <t>1910.HK</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CNS_02</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>新秀麗</t>
-  </si>
-  <si>
-    <t>1910.HK</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CNS_02</t>
-  </si>
-  <si>
-    <t>USD</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2444,7 +2469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2463,6 +2488,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3111,7 +3137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3617,9 +3643,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3836,29 +3859,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3877,7 +3907,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3924,8 +3968,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4166,15 +4210,15 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>444</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4189,7 +4233,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4198,10 +4242,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>445</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4215,9 +4259,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4238,20 +4282,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4267,17 +4311,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4291,7 +4335,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4318,73 +4362,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">High Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>448</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>442</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>444</v>
+        <v>435</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>444</v>
+        <v>436</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4394,14 +4442,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>16.812326952049464</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.12006488109359492</v>
       </c>
@@ -4412,96 +4460,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>436</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>434</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>1910.HK (HKD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>432</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>430</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C29" s="345">
+        <v>426</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>7.4603674180938295</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>427</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>425</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C30" s="346">
+        <v>427</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>11.038812906388786</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C31" s="346">
+        <v>428</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>15.508872436253256</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>439</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>437</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C32" s="346">
+        <v>429</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>14.075071731650674</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4510,8 +4558,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4520,22 +4568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4547,13 +4595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4573,13 +4621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4608,13 +4656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4630,19 +4678,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>7.03184705776422</v>
       </c>
@@ -4650,14 +4698,14 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-152</v>
       </c>
@@ -4665,8 +4713,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4700,13 +4748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4722,13 +4770,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4744,22 +4792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4788,26 +4836,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.11059265886011045</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>6.0028763948497849E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>4.2412648414039946</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4820,22 +4876,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4844,7 +4900,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4853,7 +4909,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4864,7 +4920,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4873,42 +4929,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>19.326067135804305</v>
       </c>
@@ -4918,8 +4974,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4931,13 +4987,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4950,13 +5006,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4973,9 +5029,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>13.12408992693074</v>
       </c>
@@ -4985,28 +5041,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>2.2875080906148866</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>1.5035598705501618</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>4.1998196571663646</v>
       </c>
@@ -5044,9 +5100,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.8452861569582497</v>
       </c>
@@ -5075,9 +5131,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0</v>
       </c>
@@ -5087,20 +5143,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>450</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>8.0472633658318138</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5109,10 +5165,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>-12.221505076854779</v>
       </c>
@@ -5122,8 +5178,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5132,49 +5188,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.25</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>15</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>86.82 HKD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5192,11 +5248,11 @@
         <f>DCF!D75</f>
         <v>10</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>21.21 HKD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
@@ -5214,11 +5270,11 @@
         <f>DCF!D76</f>
         <v>10</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>12.18 HKD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
@@ -5236,11 +5292,11 @@
         <f>DCF!D77</f>
         <v>10</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>9.29 HKD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5258,11 +5314,11 @@
         <f>DCF!D78</f>
         <v>15</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>8.05 HKD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5281,17 +5337,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5300,22 +5356,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5326,7 +5382,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5335,7 +5391,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5355,22 +5411,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>1910.HK</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5403,20 +5459,20 @@
         <f>Scenarios!C83</f>
         <v>7.4603674180938295</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5432,14 +5488,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5472,20 +5528,20 @@
         <f>Scenarios!C93</f>
         <v>11.038812906388786</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5501,12 +5557,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5535,26 +5591,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>15.508872436253256</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5570,12 +5626,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5604,26 +5660,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>14.075071731650674</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5638,8 +5694,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5648,113 +5704,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5771,6 +5816,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5783,7 +5839,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6239,7 +6295,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>56480</v>
@@ -6265,7 +6321,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-11150</v>
@@ -6291,7 +6347,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-45970</v>
@@ -6349,7 +6405,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7604,7 +7660,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8052,11 +8108,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8086,11 +8142,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8193,17 +8249,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8287,7 +8343,7 @@
       <c r="C4" s="19">
         <v>325.3</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8297,7 +8353,7 @@
       <c r="G4" s="19">
         <v>676.3</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8308,7 +8364,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8318,7 +8374,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8329,7 +8385,7 @@
       <c r="C6" s="19">
         <v>651.4</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8339,7 +8395,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8350,7 +8406,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8360,7 +8416,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8371,7 +8427,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8381,7 +8437,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8392,7 +8448,7 @@
       <c r="C9" s="19">
         <v>89.6</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8402,7 +8458,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8413,10 +8469,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8425,10 +8481,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8486,7 +8542,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8495,7 +8551,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8506,7 +8562,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8515,7 +8571,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8526,7 +8582,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8535,7 +8591,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8546,7 +8602,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8555,7 +8611,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8567,7 +8623,7 @@
         <f>262.1+499.2</f>
         <v>761.3</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8576,7 +8632,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8587,7 +8643,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8596,7 +8652,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8607,7 +8663,7 @@
       <c r="C21" s="19">
         <v>1519.8</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8616,7 +8672,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8627,10 +8683,10 @@
       <c r="C22" s="19">
         <v>165.7</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8640,10 +8696,10 @@
         <f>819.6+70.2</f>
         <v>889.80000000000007</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -8977,13 +9033,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -8999,7 +9055,7 @@
         <f>H29</f>
         <v>-2163.2399999999998</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9014,23 +9070,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-12.221505076854779</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9044,7 +9100,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>3.6733080328905765</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9055,22 +9111,22 @@
         <f>G29/G32</f>
         <v>0.29063632068042211</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9084,7 +9140,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.14363260578255238</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9098,22 +9154,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9135,22 +9191,22 @@
         <f>G39/G32</f>
         <v>0.14988580878878563</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9164,7 +9220,7 @@
         <f>G28/G29</f>
         <v>4.6606150928058525E-2</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9183,13 +9239,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9217,7 +9273,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9227,7 +9283,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9237,7 +9293,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9247,26 +9303,26 @@
         <f>SUM(C66:C69)</f>
         <v>676.3</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9277,65 +9333,65 @@
         <v>-349.67927685043691</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>1.9713032929902656</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>1.9340579919160141</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>349.67927685043691</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9349,7 +9405,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9363,7 +9419,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9377,7 +9433,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9391,11 +9447,11 @@
         <f>SUM(D79:D81)</f>
         <v>0</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9406,76 +9462,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-18151.457399999999</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-13.12408992693074</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>2552.1490065460557</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>1.8452861569582497</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>0</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>0</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-15599.308393453943</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>-11.278803769972491</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9596,7 +9652,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9610,7 +9666,7 @@
         <v>3588.6</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9666,7 +9722,7 @@
         <f>C25</f>
         <v>-2808.2810116557866</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-2725.5</v>
@@ -9721,7 +9777,7 @@
         <f>C4+C5</f>
         <v>780.31898834421327</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>863.09999999999991</v>
@@ -9776,7 +9832,7 @@
         <f>C35</f>
         <v>-227.20000000000005</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-230.70000000000005</v>
@@ -9832,7 +9888,7 @@
         <v>553.11898834421322</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9888,7 +9944,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -9943,7 +9999,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>0</v>
@@ -9999,7 +10055,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10055,7 +10111,7 @@
         <f>C50</f>
         <v>-144.96815294223578</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-144.96815294223578</v>
@@ -10110,7 +10166,7 @@
         <f>SUM(C8:C12)</f>
         <v>408.15083540197747</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>487.43184705776412</v>
@@ -10165,7 +10221,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-102.03770885049437</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-118.3</v>
@@ -10221,7 +10277,7 @@
         <v>-32.451765153160977</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10278,7 +10334,7 @@
         <v>273.66136139832213</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10335,8 +10391,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10360,8 +10416,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10386,7 +10442,7 @@
         <v>273.66136139832213</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10482,7 +10538,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10506,7 +10562,7 @@
         <v>-1529.5625032102973</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10563,7 +10619,7 @@
         <v>-1278.7185084454891</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10620,7 +10676,7 @@
         <v>-2808.2810116557866</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10669,14 +10725,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10688,8 +10744,8 @@
         <v>0.42622819573379517</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10748,8 +10804,8 @@
         <v>0.35632795754486124</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10806,7 +10862,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.78255615327865646</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.75948837986958706</v>
@@ -10854,14 +10910,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10872,8 +10928,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-227.20000000000005</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10930,8 +10986,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10989,7 +11045,7 @@
         <v>-227.20000000000005</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11038,14 +11094,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11058,7 +11114,7 @@
         <v>6.331159783759685E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11116,7 +11172,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11172,7 +11228,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>6.331159783759685E-2</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>6.4286908543721794E-2</v>
@@ -11220,26 +11276,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11318,7 +11374,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11329,7 +11385,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-152</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-152</v>
@@ -11378,111 +11434,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>7.03184705776422</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>7.03184705776422</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>7.3937803622079672</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>4.5500186844356723</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>1.8613712799964113</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323" t="str">
+      <c r="L48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="323" t="str">
+      <c r="N48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="323" t="str">
+      <c r="O48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="323" t="str">
+      <c r="P48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>13.6</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>13.6</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>14.3</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>3.6</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="319" t="str">
+      <c r="L49" s="318" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="319" t="str">
+      <c r="M49" s="318" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="319" t="str">
+      <c r="N49" s="318" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="319" t="str">
+      <c r="O49" s="318" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="319" t="str">
+      <c r="P49" s="318" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11496,7 +11552,7 @@
         <f>C47+C48</f>
         <v>-144.96815294223578</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-144.96815294223578</v>
@@ -11544,14 +11600,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11565,8 +11621,8 @@
         <f>G53</f>
         <v>2.0109418896939228E-2</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11592,8 +11648,8 @@
         <f>G54</f>
         <v>6.5432630219543694E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11619,7 +11675,7 @@
         <f>-C8/C47</f>
         <v>3.6389407127908764</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>4.1605263157894727</v>
@@ -11667,14 +11723,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11688,7 +11744,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11743,7 +11799,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11798,7 +11854,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11853,7 +11909,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11904,11 +11960,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11964,7 +12020,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-3.0999999999997954</v>
@@ -12012,14 +12068,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12033,7 +12089,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12058,7 +12114,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12083,7 +12139,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12109,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12137,7 +12193,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12159,7 +12215,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12183,7 +12239,7 @@
         <v>0.78255615327865646</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12240,7 +12296,7 @@
         <v>0.21744384672134351</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12297,7 +12353,7 @@
         <v>6.331159783759685E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12354,7 +12410,7 @@
         <v>0.15413224888374666</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12411,7 +12467,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12468,8 +12524,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>452</v>
+      <c r="E78" s="295" t="s">
+        <v>460</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12527,7 +12583,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12584,7 +12640,7 @@
         <v>4.0396854746206259E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12641,7 +12697,7 @@
         <v>0.1137353941375404</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12698,7 +12754,7 @@
         <v>2.84338485343851E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12751,12 +12807,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>9.0430154247230065E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12813,7 +12869,7 @@
         <v>7.6258530178432302E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12865,26 +12921,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12894,7 +12950,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12920,7 +12976,7 @@
         <v>7.6258530178432302E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -12969,14 +13025,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -12988,7 +13044,7 @@
         <f>G90</f>
         <v>0.83920211999999994</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.83920211999999994</v>
@@ -13044,7 +13100,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>1160.670310549456</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1160.670310549456</v>
@@ -13099,7 +13155,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>4.2412648414039946</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>3.3914737056997222</v>
@@ -13148,13 +13204,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>6.0028763948497849E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>6.0028763948497849E-2</v>
@@ -13202,7 +13258,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13211,7 +13267,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13235,7 +13291,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13292,7 +13348,7 @@
         <v>-0.16265045489814145</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13370,7 +13426,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13385,7 +13441,7 @@
         <v>5079.2</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13442,7 +13498,7 @@
         <v>325.3</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13499,7 +13555,7 @@
         <v>651.4</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13556,7 +13612,7 @@
         <v>3534.2</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13613,7 +13669,7 @@
         <v>1545</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13662,7 +13718,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13671,7 +13727,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13697,7 +13753,7 @@
         <v>9.0648163629270473E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13754,7 +13810,7 @@
         <v>0.18151925541994093</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13811,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13830,63 +13886,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>151.5834675254965</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>118.63202309571396</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>82.086905113804306</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1647.2340425531916</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>8.866459627329192</v>
       </c>
-      <c r="L113" s="328" t="str">
+      <c r="L113" s="327" t="str">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v/>
       </c>
-      <c r="M113" s="328" t="str">
+      <c r="M113" s="327" t="str">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v/>
       </c>
-      <c r="N113" s="328" t="str">
+      <c r="N113" s="327" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v/>
       </c>
-      <c r="O113" s="328" t="str">
+      <c r="O113" s="327" t="str">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v/>
       </c>
-      <c r="P113" s="328" t="str">
+      <c r="P113" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13894,58 +13950,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>165.03431952803311</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>161.88183892849457</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>117.39589011424252</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-5920.2015678876996</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>52.578268876611439</v>
       </c>
-      <c r="L114" s="328" t="str">
+      <c r="L114" s="327" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v/>
       </c>
-      <c r="M114" s="328" t="str">
+      <c r="M114" s="327" t="str">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v/>
       </c>
-      <c r="N114" s="328" t="str">
+      <c r="N114" s="327" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="328" t="str">
+      <c r="O114" s="327" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="328" t="str">
+      <c r="P114" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -13954,7 +14010,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14010,7 +14066,7 @@
         <f>C81</f>
         <v>0.1137353941375404</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.1358278568404849</v>
@@ -14064,7 +14120,7 @@
         <f>C4/C101</f>
         <v>0.70652858717908329</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.70652858717908329</v>
@@ -14119,7 +14175,7 @@
         <v>3.2875080906148866</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14176,7 +14232,7 @@
         <v>0.35800581769851986</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14272,7 +14328,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14297,7 +14353,7 @@
         <v>1.5460853708643443</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14354,7 +14410,7 @@
         <v>0.11059265886011045</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14403,7 +14459,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15136,7 +15192,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15204,7 +15260,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15214,7 +15270,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15232,10 +15288,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15250,8 +15306,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15266,8 +15322,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15282,8 +15338,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16628,7 +16684,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16659,12 +16715,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16679,6 +16735,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>1160.670310549456</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>14508.378881868199</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>81.966969065699985</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>15.247814949392454</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>446</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>1289.7505172182371</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>1194.2134418687378</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>1433.1859629262315</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>1228.7259627282506</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>1592.5731193029098</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>1264.2358882847109</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>1769.6860044231034</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>1300.7720433270572</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>1966.4959280625264</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>1338.3640856746515</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>2185.1934328582361</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>1377.0425302516849</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>2428.2126755845156</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>1416.8387738573326</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>2698.2585199137507</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>1457.7851206517541</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>2998.3366422113627</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>1499.9148083786413</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>3331.7869854496639</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>0.111211776070739</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>1543.262035345585</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126